--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -2304,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132341033</v>
+        <v>132341110</v>
       </c>
       <c r="B16" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,21 +2315,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438033</v>
+        <v>437169</v>
       </c>
       <c r="R16" t="n">
-        <v>7010948</v>
+        <v>7010552</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,11 +2375,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132341110</v>
+        <v>132341129</v>
       </c>
       <c r="B17" t="n">
-        <v>92188</v>
+        <v>91888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,21 +2412,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2441,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437169</v>
+        <v>437750</v>
       </c>
       <c r="R17" t="n">
-        <v>7010552</v>
+        <v>7010913</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2503,10 +2498,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132341129</v>
+        <v>132341033</v>
       </c>
       <c r="B18" t="n">
-        <v>91885</v>
+        <v>57948</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2514,21 +2509,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2538,10 +2533,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437750</v>
+        <v>438033</v>
       </c>
       <c r="R18" t="n">
-        <v>7010913</v>
+        <v>7010948</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2574,6 +2569,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,7 +2603,7 @@
         <v>132341126</v>
       </c>
       <c r="B19" t="n">
-        <v>91885</v>
+        <v>91888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>132341137</v>
       </c>
       <c r="B20" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3003,32 +3003,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132341117</v>
+        <v>132340941</v>
       </c>
       <c r="B23" t="n">
-        <v>99095</v>
+        <v>91892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437071</v>
+        <v>437348</v>
       </c>
       <c r="R23" t="n">
-        <v>7010578</v>
+        <v>7010989</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3100,57 +3100,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132341118</v>
+        <v>132341113</v>
       </c>
       <c r="B24" t="n">
-        <v>99095</v>
+        <v>80422</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437059</v>
+        <v>437053</v>
       </c>
       <c r="R24" t="n">
-        <v>7010572</v>
+        <v>7010706</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3185,18 +3173,12 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt över 200</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3215,10 +3197,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132341113</v>
+        <v>132341060</v>
       </c>
       <c r="B25" t="n">
-        <v>80420</v>
+        <v>57948</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3226,21 +3208,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3250,10 +3232,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437053</v>
+        <v>437611</v>
       </c>
       <c r="R25" t="n">
-        <v>7010706</v>
+        <v>7010882</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3286,6 +3268,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3312,7 +3299,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132341060</v>
+        <v>132341064</v>
       </c>
       <c r="B26" t="n">
         <v>57948</v>
@@ -3347,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437611</v>
+        <v>437442</v>
       </c>
       <c r="R26" t="n">
-        <v>7010882</v>
+        <v>7010869</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3414,32 +3401,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132341064</v>
+        <v>132341117</v>
       </c>
       <c r="B27" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3449,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437442</v>
+        <v>437071</v>
       </c>
       <c r="R27" t="n">
-        <v>7010869</v>
+        <v>7010578</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3485,11 +3472,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3516,45 +3498,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132340941</v>
+        <v>132341118</v>
       </c>
       <c r="B28" t="n">
-        <v>91889</v>
+        <v>99098</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437348</v>
+        <v>437059</v>
       </c>
       <c r="R28" t="n">
-        <v>7010989</v>
+        <v>7010572</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,12 +3583,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt över 200</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>132341132</v>
       </c>
       <c r="B29" t="n">
-        <v>91885</v>
+        <v>91888</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132341041</v>
+        <v>132341040</v>
       </c>
       <c r="B30" t="n">
         <v>57948</v>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437973</v>
+        <v>438088</v>
       </c>
       <c r="R30" t="n">
-        <v>7010845</v>
+        <v>7010817</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3812,7 +3812,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132341040</v>
+        <v>132341049</v>
       </c>
       <c r="B31" t="n">
         <v>57948</v>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438088</v>
+        <v>437804</v>
       </c>
       <c r="R31" t="n">
-        <v>7010817</v>
+        <v>7010729</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3914,7 +3914,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132341049</v>
+        <v>132341029</v>
       </c>
       <c r="B32" t="n">
         <v>57948</v>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437804</v>
+        <v>437342</v>
       </c>
       <c r="R32" t="n">
-        <v>7010729</v>
+        <v>7010780</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3979,12 +3979,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4016,7 +4016,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132341029</v>
+        <v>132341041</v>
       </c>
       <c r="B33" t="n">
         <v>57948</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437342</v>
+        <v>437973</v>
       </c>
       <c r="R33" t="n">
-        <v>7010780</v>
+        <v>7010845</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4081,12 +4081,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4121,7 +4121,7 @@
         <v>132341138</v>
       </c>
       <c r="B34" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>132341135</v>
       </c>
       <c r="B36" t="n">
-        <v>91903</v>
+        <v>91906</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>132340936</v>
       </c>
       <c r="B37" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>132341140</v>
       </c>
       <c r="B38" t="n">
-        <v>92585</v>
+        <v>92588</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>132341100</v>
       </c>
       <c r="B39" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>132341128</v>
       </c>
       <c r="B40" t="n">
-        <v>91885</v>
+        <v>91888</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>132340940</v>
       </c>
       <c r="B41" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>132341134</v>
       </c>
       <c r="B42" t="n">
-        <v>91903</v>
+        <v>91906</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>132341105</v>
       </c>
       <c r="B43" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5404,10 +5404,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132341055</v>
+        <v>132340949</v>
       </c>
       <c r="B47" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5415,21 +5415,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437603</v>
+        <v>437092</v>
       </c>
       <c r="R47" t="n">
-        <v>7011097</v>
+        <v>7010575</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5475,11 +5475,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5506,10 +5501,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132340949</v>
+        <v>132341055</v>
       </c>
       <c r="B48" t="n">
-        <v>91889</v>
+        <v>57948</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5517,21 +5512,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5541,10 +5536,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437092</v>
+        <v>437603</v>
       </c>
       <c r="R48" t="n">
-        <v>7010575</v>
+        <v>7011097</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5577,6 +5572,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5606,7 +5606,7 @@
         <v>132341127</v>
       </c>
       <c r="B49" t="n">
-        <v>91885</v>
+        <v>91888</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>132341125</v>
       </c>
       <c r="B50" t="n">
-        <v>91885</v>
+        <v>91888</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>132341108</v>
       </c>
       <c r="B51" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132341136</v>
+        <v>132341112</v>
       </c>
       <c r="B56" t="n">
-        <v>79315</v>
+        <v>80422</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6320,21 +6320,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437640</v>
+        <v>437518</v>
       </c>
       <c r="R56" t="n">
-        <v>7010681</v>
+        <v>7010858</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6374,17 +6374,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6411,10 +6406,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132341103</v>
+        <v>132341052</v>
       </c>
       <c r="B57" t="n">
-        <v>92188</v>
+        <v>57948</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6422,21 +6417,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6446,10 +6441,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437283</v>
+        <v>437740</v>
       </c>
       <c r="R57" t="n">
-        <v>7010896</v>
+        <v>7011055</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6482,6 +6477,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6508,10 +6508,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132340935</v>
+        <v>132341037</v>
       </c>
       <c r="B58" t="n">
-        <v>91889</v>
+        <v>57948</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6519,21 +6519,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437488</v>
+        <v>437926</v>
       </c>
       <c r="R58" t="n">
-        <v>7010535</v>
+        <v>7011061</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6573,12 +6573,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6605,10 +6610,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132341131</v>
+        <v>132341056</v>
       </c>
       <c r="B59" t="n">
-        <v>91885</v>
+        <v>57948</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6616,21 +6621,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6640,10 +6645,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437674</v>
+        <v>437578</v>
       </c>
       <c r="R59" t="n">
-        <v>7011000</v>
+        <v>7011118</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6676,6 +6681,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6702,10 +6712,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341109</v>
+        <v>132341032</v>
       </c>
       <c r="B60" t="n">
-        <v>92188</v>
+        <v>57948</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6713,21 +6723,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6737,10 +6747,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437194</v>
+        <v>438064</v>
       </c>
       <c r="R60" t="n">
-        <v>7010597</v>
+        <v>7010908</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6773,6 +6783,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6799,10 +6814,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132341112</v>
+        <v>132341066</v>
       </c>
       <c r="B61" t="n">
-        <v>80420</v>
+        <v>57948</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6810,21 +6825,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6834,10 +6849,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437518</v>
+        <v>436968</v>
       </c>
       <c r="R61" t="n">
-        <v>7010858</v>
+        <v>7010599</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6870,6 +6885,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6896,7 +6916,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132341052</v>
+        <v>132341051</v>
       </c>
       <c r="B62" t="n">
         <v>57948</v>
@@ -6931,10 +6951,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437740</v>
+        <v>437746</v>
       </c>
       <c r="R62" t="n">
-        <v>7011055</v>
+        <v>7010946</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6998,7 +7018,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132341037</v>
+        <v>132341031</v>
       </c>
       <c r="B63" t="n">
         <v>57948</v>
@@ -7033,10 +7053,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437926</v>
+        <v>438101</v>
       </c>
       <c r="R63" t="n">
-        <v>7011061</v>
+        <v>7010919</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7100,7 +7120,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132341056</v>
+        <v>132341034</v>
       </c>
       <c r="B64" t="n">
         <v>57948</v>
@@ -7135,10 +7155,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>437578</v>
+        <v>437908</v>
       </c>
       <c r="R64" t="n">
-        <v>7011118</v>
+        <v>7011073</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7202,10 +7222,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132341032</v>
+        <v>132341103</v>
       </c>
       <c r="B65" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7213,21 +7233,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7237,10 +7257,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>438064</v>
+        <v>437283</v>
       </c>
       <c r="R65" t="n">
-        <v>7010908</v>
+        <v>7010896</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7273,11 +7293,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7304,10 +7319,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132341066</v>
+        <v>132340935</v>
       </c>
       <c r="B66" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7315,21 +7330,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7339,10 +7354,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436968</v>
+        <v>437488</v>
       </c>
       <c r="R66" t="n">
-        <v>7010599</v>
+        <v>7010535</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7369,17 +7384,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7406,10 +7416,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132341051</v>
+        <v>132341131</v>
       </c>
       <c r="B67" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7417,21 +7427,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7441,10 +7451,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437746</v>
+        <v>437674</v>
       </c>
       <c r="R67" t="n">
-        <v>7010946</v>
+        <v>7011000</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,11 +7487,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7508,10 +7513,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132341031</v>
+        <v>132341109</v>
       </c>
       <c r="B68" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7519,21 +7524,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7543,10 +7548,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438101</v>
+        <v>437194</v>
       </c>
       <c r="R68" t="n">
-        <v>7010919</v>
+        <v>7010597</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,11 +7584,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7610,10 +7610,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132341034</v>
+        <v>132341136</v>
       </c>
       <c r="B69" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7621,21 +7621,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437908</v>
+        <v>437640</v>
       </c>
       <c r="R69" t="n">
-        <v>7011073</v>
+        <v>7010681</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7675,17 +7675,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7712,10 +7712,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132340946</v>
+        <v>132341096</v>
       </c>
       <c r="B70" t="n">
-        <v>91889</v>
+        <v>57945</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7723,21 +7723,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437124</v>
+        <v>437096</v>
       </c>
       <c r="R70" t="n">
-        <v>7010689</v>
+        <v>7010572</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7783,6 +7783,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7809,10 +7814,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132341102</v>
+        <v>132341053</v>
       </c>
       <c r="B71" t="n">
-        <v>92188</v>
+        <v>57948</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7820,21 +7825,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7844,10 +7849,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437474</v>
+        <v>437740</v>
       </c>
       <c r="R71" t="n">
-        <v>7010882</v>
+        <v>7011063</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7880,6 +7885,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7906,10 +7916,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132340944</v>
+        <v>132340946</v>
       </c>
       <c r="B72" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7941,10 +7951,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437304</v>
+        <v>437124</v>
       </c>
       <c r="R72" t="n">
-        <v>7010986</v>
+        <v>7010689</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8003,10 +8013,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132341053</v>
+        <v>132341102</v>
       </c>
       <c r="B73" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8014,21 +8024,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8038,10 +8048,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437740</v>
+        <v>437474</v>
       </c>
       <c r="R73" t="n">
-        <v>7011063</v>
+        <v>7010882</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8074,11 +8084,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8105,10 +8110,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341111</v>
+        <v>132340944</v>
       </c>
       <c r="B74" t="n">
-        <v>80420</v>
+        <v>91892</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8116,21 +8121,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8140,10 +8145,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437156</v>
+        <v>437304</v>
       </c>
       <c r="R74" t="n">
-        <v>7010645</v>
+        <v>7010986</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8170,12 +8175,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8202,10 +8207,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341096</v>
+        <v>132341111</v>
       </c>
       <c r="B75" t="n">
-        <v>57945</v>
+        <v>80422</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8213,21 +8218,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8237,10 +8242,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437096</v>
+        <v>437156</v>
       </c>
       <c r="R75" t="n">
-        <v>7010572</v>
+        <v>7010645</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8267,17 +8272,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8307,7 +8307,7 @@
         <v>132341106</v>
       </c>
       <c r="B76" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8503,10 +8503,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132341065</v>
+        <v>132340942</v>
       </c>
       <c r="B78" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8514,21 +8514,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437074</v>
+        <v>437287</v>
       </c>
       <c r="R78" t="n">
-        <v>7010580</v>
+        <v>7010896</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8574,11 +8574,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8605,7 +8600,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132341045</v>
+        <v>132341065</v>
       </c>
       <c r="B79" t="n">
         <v>57948</v>
@@ -8640,10 +8635,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437901</v>
+        <v>437074</v>
       </c>
       <c r="R79" t="n">
-        <v>7010813</v>
+        <v>7010580</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8680,7 +8675,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8707,7 +8702,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132341030</v>
+        <v>132341045</v>
       </c>
       <c r="B80" t="n">
         <v>57948</v>
@@ -8742,10 +8737,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438101</v>
+        <v>437901</v>
       </c>
       <c r="R80" t="n">
-        <v>7010924</v>
+        <v>7010813</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8782,7 +8777,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8809,7 +8804,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132341063</v>
+        <v>132341030</v>
       </c>
       <c r="B81" t="n">
         <v>57948</v>
@@ -8844,10 +8839,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437505</v>
+        <v>438101</v>
       </c>
       <c r="R81" t="n">
-        <v>7010836</v>
+        <v>7010924</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8911,7 +8906,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132341043</v>
+        <v>132341063</v>
       </c>
       <c r="B82" t="n">
         <v>57948</v>
@@ -8946,10 +8941,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437872</v>
+        <v>437505</v>
       </c>
       <c r="R82" t="n">
-        <v>7010932</v>
+        <v>7010836</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8986,7 +8981,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9013,32 +9008,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341115</v>
+        <v>132341043</v>
       </c>
       <c r="B83" t="n">
-        <v>99095</v>
+        <v>57948</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9048,10 +9043,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437101</v>
+        <v>437872</v>
       </c>
       <c r="R83" t="n">
-        <v>7010646</v>
+        <v>7010932</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9084,6 +9079,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9110,32 +9110,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132340942</v>
+        <v>132341115</v>
       </c>
       <c r="B84" t="n">
-        <v>91889</v>
+        <v>99098</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9145,10 +9145,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437287</v>
+        <v>437101</v>
       </c>
       <c r="R84" t="n">
-        <v>7010896</v>
+        <v>7010646</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9210,7 +9210,7 @@
         <v>132341114</v>
       </c>
       <c r="B85" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9508,10 +9508,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132340948</v>
+        <v>132341028</v>
       </c>
       <c r="B88" t="n">
-        <v>91889</v>
+        <v>57948</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9519,21 +9519,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9543,10 +9543,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437159</v>
+        <v>437583</v>
       </c>
       <c r="R88" t="n">
-        <v>7010541</v>
+        <v>7010708</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9573,12 +9573,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9605,10 +9610,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132340943</v>
+        <v>132340948</v>
       </c>
       <c r="B89" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9640,10 +9645,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437280</v>
+        <v>437159</v>
       </c>
       <c r="R89" t="n">
-        <v>7010923</v>
+        <v>7010541</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9702,10 +9707,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132340938</v>
+        <v>132340943</v>
       </c>
       <c r="B90" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9737,10 +9742,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437465</v>
+        <v>437280</v>
       </c>
       <c r="R90" t="n">
-        <v>7010897</v>
+        <v>7010923</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9799,10 +9804,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132340947</v>
+        <v>132340938</v>
       </c>
       <c r="B91" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9834,10 +9839,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437023</v>
+        <v>437465</v>
       </c>
       <c r="R91" t="n">
-        <v>7010700</v>
+        <v>7010897</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9896,10 +9901,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132340939</v>
+        <v>132340947</v>
       </c>
       <c r="B92" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9931,10 +9936,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437481</v>
+        <v>437023</v>
       </c>
       <c r="R92" t="n">
-        <v>7010828</v>
+        <v>7010700</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9993,10 +9998,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132341101</v>
+        <v>132340939</v>
       </c>
       <c r="B93" t="n">
-        <v>92188</v>
+        <v>91892</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10004,21 +10009,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10028,10 +10033,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>437486</v>
+        <v>437481</v>
       </c>
       <c r="R93" t="n">
-        <v>7010537</v>
+        <v>7010828</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10058,12 +10063,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10090,10 +10095,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132341097</v>
+        <v>132341101</v>
       </c>
       <c r="B94" t="n">
-        <v>80421</v>
+        <v>92191</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10101,21 +10106,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10125,10 +10130,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437011</v>
+        <v>437486</v>
       </c>
       <c r="R94" t="n">
-        <v>7010575</v>
+        <v>7010537</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10155,12 +10160,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10187,10 +10192,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132341028</v>
+        <v>132341097</v>
       </c>
       <c r="B95" t="n">
-        <v>57948</v>
+        <v>80423</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10198,21 +10203,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10222,10 +10227,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>437583</v>
+        <v>437011</v>
       </c>
       <c r="R95" t="n">
-        <v>7010708</v>
+        <v>7010575</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10252,17 +10257,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10292,7 +10292,7 @@
         <v>132341116</v>
       </c>
       <c r="B96" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>132341107</v>
       </c>
       <c r="B97" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>132341104</v>
       </c>
       <c r="B98" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -2304,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132341110</v>
+        <v>132341033</v>
       </c>
       <c r="B16" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,21 +2315,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437169</v>
+        <v>438033</v>
       </c>
       <c r="R16" t="n">
-        <v>7010552</v>
+        <v>7010948</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,6 +2375,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132341129</v>
+        <v>132341110</v>
       </c>
       <c r="B17" t="n">
-        <v>91888</v>
+        <v>92191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2412,21 +2417,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2436,10 +2441,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437750</v>
+        <v>437169</v>
       </c>
       <c r="R17" t="n">
-        <v>7010913</v>
+        <v>7010552</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2498,10 +2503,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132341033</v>
+        <v>132341129</v>
       </c>
       <c r="B18" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,21 +2514,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2533,10 +2538,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438033</v>
+        <v>437750</v>
       </c>
       <c r="R18" t="n">
-        <v>7010948</v>
+        <v>7010913</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2569,11 +2574,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -5797,10 +5797,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132341108</v>
+        <v>132341027</v>
       </c>
       <c r="B51" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5808,21 +5808,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437099</v>
+        <v>437678</v>
       </c>
       <c r="R51" t="n">
-        <v>7010647</v>
+        <v>7010630</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5862,12 +5862,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5894,7 +5899,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132341027</v>
+        <v>132341062</v>
       </c>
       <c r="B52" t="n">
         <v>57948</v>
@@ -5929,10 +5934,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437678</v>
+        <v>437538</v>
       </c>
       <c r="R52" t="n">
-        <v>7010630</v>
+        <v>7010940</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5959,12 +5964,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -5996,10 +6001,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132341062</v>
+        <v>132341108</v>
       </c>
       <c r="B53" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6007,21 +6012,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6031,10 +6036,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>437538</v>
+        <v>437099</v>
       </c>
       <c r="R53" t="n">
-        <v>7010940</v>
+        <v>7010647</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6067,11 +6072,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7712,10 +7712,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132341096</v>
+        <v>132340946</v>
       </c>
       <c r="B70" t="n">
-        <v>57945</v>
+        <v>91892</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7723,21 +7723,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437096</v>
+        <v>437124</v>
       </c>
       <c r="R70" t="n">
-        <v>7010572</v>
+        <v>7010689</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7783,11 +7783,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7814,10 +7809,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132341053</v>
+        <v>132341102</v>
       </c>
       <c r="B71" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7825,21 +7820,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7849,10 +7844,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437740</v>
+        <v>437474</v>
       </c>
       <c r="R71" t="n">
-        <v>7011063</v>
+        <v>7010882</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7885,11 +7880,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7916,7 +7906,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132340946</v>
+        <v>132340944</v>
       </c>
       <c r="B72" t="n">
         <v>91892</v>
@@ -7951,10 +7941,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437124</v>
+        <v>437304</v>
       </c>
       <c r="R72" t="n">
-        <v>7010689</v>
+        <v>7010986</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8013,10 +8003,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132341102</v>
+        <v>132341111</v>
       </c>
       <c r="B73" t="n">
-        <v>92191</v>
+        <v>80422</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8024,21 +8014,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8048,10 +8038,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437474</v>
+        <v>437156</v>
       </c>
       <c r="R73" t="n">
-        <v>7010882</v>
+        <v>7010645</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8078,12 +8068,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8110,10 +8100,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132340944</v>
+        <v>132341053</v>
       </c>
       <c r="B74" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8121,21 +8111,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8145,10 +8135,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437304</v>
+        <v>437740</v>
       </c>
       <c r="R74" t="n">
-        <v>7010986</v>
+        <v>7011063</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8181,6 +8171,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8207,10 +8202,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341111</v>
+        <v>132341096</v>
       </c>
       <c r="B75" t="n">
-        <v>80422</v>
+        <v>57945</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8218,21 +8213,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8242,10 +8237,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437156</v>
+        <v>437096</v>
       </c>
       <c r="R75" t="n">
-        <v>7010645</v>
+        <v>7010572</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8272,12 +8267,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8304,10 +8304,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341106</v>
+        <v>132341059</v>
       </c>
       <c r="B76" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8315,21 +8315,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437009</v>
+        <v>437567</v>
       </c>
       <c r="R76" t="n">
-        <v>7010701</v>
+        <v>7010953</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8375,6 +8375,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8401,10 +8406,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341059</v>
+        <v>132341106</v>
       </c>
       <c r="B77" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8412,21 +8417,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8436,10 +8441,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437567</v>
+        <v>437009</v>
       </c>
       <c r="R77" t="n">
-        <v>7010953</v>
+        <v>7010701</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8472,11 +8477,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -3710,7 +3710,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132341040</v>
+        <v>132341041</v>
       </c>
       <c r="B30" t="n">
         <v>57948</v>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438088</v>
+        <v>437973</v>
       </c>
       <c r="R30" t="n">
-        <v>7010817</v>
+        <v>7010845</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3812,7 +3812,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132341049</v>
+        <v>132341040</v>
       </c>
       <c r="B31" t="n">
         <v>57948</v>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437804</v>
+        <v>438088</v>
       </c>
       <c r="R31" t="n">
-        <v>7010729</v>
+        <v>7010817</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3914,7 +3914,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132341029</v>
+        <v>132341049</v>
       </c>
       <c r="B32" t="n">
         <v>57948</v>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437342</v>
+        <v>437804</v>
       </c>
       <c r="R32" t="n">
-        <v>7010780</v>
+        <v>7010729</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3979,12 +3979,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4016,7 +4016,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132341041</v>
+        <v>132341029</v>
       </c>
       <c r="B33" t="n">
         <v>57948</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437973</v>
+        <v>437342</v>
       </c>
       <c r="R33" t="n">
-        <v>7010845</v>
+        <v>7010780</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4081,12 +4081,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4118,10 +4118,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132341138</v>
+        <v>132341047</v>
       </c>
       <c r="B34" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4129,21 +4129,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437710</v>
+        <v>437918</v>
       </c>
       <c r="R34" t="n">
-        <v>7010507</v>
+        <v>7010791</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4220,10 +4220,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132341047</v>
+        <v>132341138</v>
       </c>
       <c r="B35" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437918</v>
+        <v>437710</v>
       </c>
       <c r="R35" t="n">
-        <v>7010791</v>
+        <v>7010507</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5200,10 +5200,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132341095</v>
+        <v>132341057</v>
       </c>
       <c r="B45" t="n">
-        <v>57945</v>
+        <v>57948</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5211,16 +5211,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437922</v>
+        <v>437606</v>
       </c>
       <c r="R45" t="n">
         <v>7011053</v>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5302,10 +5302,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132341057</v>
+        <v>132341095</v>
       </c>
       <c r="B46" t="n">
-        <v>57948</v>
+        <v>57945</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5313,16 +5313,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437606</v>
+        <v>437922</v>
       </c>
       <c r="R46" t="n">
         <v>7011053</v>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6309,10 +6309,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132341112</v>
+        <v>132341103</v>
       </c>
       <c r="B56" t="n">
-        <v>80422</v>
+        <v>92191</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6320,21 +6320,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437518</v>
+        <v>437283</v>
       </c>
       <c r="R56" t="n">
-        <v>7010858</v>
+        <v>7010896</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132341052</v>
+        <v>132340935</v>
       </c>
       <c r="B57" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6417,21 +6417,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437740</v>
+        <v>437488</v>
       </c>
       <c r="R57" t="n">
-        <v>7011055</v>
+        <v>7010535</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6471,17 +6471,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6508,10 +6503,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132341037</v>
+        <v>132341131</v>
       </c>
       <c r="B58" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6519,21 +6514,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6543,10 +6538,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437926</v>
+        <v>437674</v>
       </c>
       <c r="R58" t="n">
-        <v>7011061</v>
+        <v>7011000</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6579,11 +6574,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6610,10 +6600,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132341056</v>
+        <v>132341109</v>
       </c>
       <c r="B59" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6621,21 +6611,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6645,10 +6635,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437578</v>
+        <v>437194</v>
       </c>
       <c r="R59" t="n">
-        <v>7011118</v>
+        <v>7010597</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6681,11 +6671,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6712,10 +6697,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341032</v>
+        <v>132341112</v>
       </c>
       <c r="B60" t="n">
-        <v>57948</v>
+        <v>80422</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6723,21 +6708,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6747,10 +6732,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>438064</v>
+        <v>437518</v>
       </c>
       <c r="R60" t="n">
-        <v>7010908</v>
+        <v>7010858</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6783,11 +6768,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6814,10 +6794,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132341066</v>
+        <v>132341136</v>
       </c>
       <c r="B61" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6825,21 +6805,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6849,10 +6829,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436968</v>
+        <v>437640</v>
       </c>
       <c r="R61" t="n">
-        <v>7010599</v>
+        <v>7010681</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6879,17 +6859,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6916,7 +6896,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132341051</v>
+        <v>132341052</v>
       </c>
       <c r="B62" t="n">
         <v>57948</v>
@@ -6951,10 +6931,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437746</v>
+        <v>437740</v>
       </c>
       <c r="R62" t="n">
-        <v>7010946</v>
+        <v>7011055</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7018,7 +6998,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132341031</v>
+        <v>132341037</v>
       </c>
       <c r="B63" t="n">
         <v>57948</v>
@@ -7053,10 +7033,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>438101</v>
+        <v>437926</v>
       </c>
       <c r="R63" t="n">
-        <v>7010919</v>
+        <v>7011061</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7120,7 +7100,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132341034</v>
+        <v>132341056</v>
       </c>
       <c r="B64" t="n">
         <v>57948</v>
@@ -7155,10 +7135,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>437908</v>
+        <v>437578</v>
       </c>
       <c r="R64" t="n">
-        <v>7011073</v>
+        <v>7011118</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7222,10 +7202,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132341103</v>
+        <v>132341032</v>
       </c>
       <c r="B65" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7233,21 +7213,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7257,10 +7237,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>437283</v>
+        <v>438064</v>
       </c>
       <c r="R65" t="n">
-        <v>7010896</v>
+        <v>7010908</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7293,6 +7273,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7319,10 +7304,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132340935</v>
+        <v>132341066</v>
       </c>
       <c r="B66" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7330,21 +7315,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7354,10 +7339,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>437488</v>
+        <v>436968</v>
       </c>
       <c r="R66" t="n">
-        <v>7010535</v>
+        <v>7010599</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7384,12 +7369,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7416,10 +7406,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132341131</v>
+        <v>132341051</v>
       </c>
       <c r="B67" t="n">
-        <v>91888</v>
+        <v>57948</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7427,21 +7417,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7451,10 +7441,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437674</v>
+        <v>437746</v>
       </c>
       <c r="R67" t="n">
-        <v>7011000</v>
+        <v>7010946</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7487,6 +7477,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7513,10 +7508,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132341109</v>
+        <v>132341031</v>
       </c>
       <c r="B68" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7524,21 +7519,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7548,10 +7543,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437194</v>
+        <v>438101</v>
       </c>
       <c r="R68" t="n">
-        <v>7010597</v>
+        <v>7010919</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7584,6 +7579,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7610,10 +7610,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132341136</v>
+        <v>132341034</v>
       </c>
       <c r="B69" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7621,21 +7621,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437640</v>
+        <v>437908</v>
       </c>
       <c r="R69" t="n">
-        <v>7010681</v>
+        <v>7011073</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7675,17 +7675,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7712,10 +7712,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132340946</v>
+        <v>132341096</v>
       </c>
       <c r="B70" t="n">
-        <v>91892</v>
+        <v>57945</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7723,21 +7723,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437124</v>
+        <v>437096</v>
       </c>
       <c r="R70" t="n">
-        <v>7010689</v>
+        <v>7010572</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7783,6 +7783,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7809,10 +7814,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132341102</v>
+        <v>132341053</v>
       </c>
       <c r="B71" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7820,21 +7825,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7844,10 +7849,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437474</v>
+        <v>437740</v>
       </c>
       <c r="R71" t="n">
-        <v>7010882</v>
+        <v>7011063</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7880,6 +7885,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7906,7 +7916,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132340944</v>
+        <v>132340946</v>
       </c>
       <c r="B72" t="n">
         <v>91892</v>
@@ -7941,10 +7951,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437304</v>
+        <v>437124</v>
       </c>
       <c r="R72" t="n">
-        <v>7010986</v>
+        <v>7010689</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8003,10 +8013,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132341111</v>
+        <v>132341102</v>
       </c>
       <c r="B73" t="n">
-        <v>80422</v>
+        <v>92191</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8014,21 +8024,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8038,10 +8048,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437156</v>
+        <v>437474</v>
       </c>
       <c r="R73" t="n">
-        <v>7010645</v>
+        <v>7010882</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8068,12 +8078,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8100,10 +8110,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341053</v>
+        <v>132340944</v>
       </c>
       <c r="B74" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8111,21 +8121,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8135,10 +8145,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437740</v>
+        <v>437304</v>
       </c>
       <c r="R74" t="n">
-        <v>7011063</v>
+        <v>7010986</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8171,11 +8181,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8202,10 +8207,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341096</v>
+        <v>132341111</v>
       </c>
       <c r="B75" t="n">
-        <v>57945</v>
+        <v>80422</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8213,21 +8218,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8237,10 +8242,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437096</v>
+        <v>437156</v>
       </c>
       <c r="R75" t="n">
-        <v>7010572</v>
+        <v>7010645</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8267,17 +8272,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10289,57 +10289,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132341116</v>
+        <v>132341107</v>
       </c>
       <c r="B96" t="n">
-        <v>99098</v>
+        <v>92191</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>437089</v>
+        <v>436990</v>
       </c>
       <c r="R96" t="n">
-        <v>7010576</v>
+        <v>7010703</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10374,18 +10362,12 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Rikligt, över 200</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10404,7 +10386,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132341107</v>
+        <v>132341104</v>
       </c>
       <c r="B97" t="n">
         <v>92191</v>
@@ -10439,10 +10421,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436990</v>
+        <v>437280</v>
       </c>
       <c r="R97" t="n">
-        <v>7010703</v>
+        <v>7010923</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10501,45 +10483,57 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132341104</v>
+        <v>132341116</v>
       </c>
       <c r="B98" t="n">
-        <v>92191</v>
+        <v>99098</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437280</v>
+        <v>437089</v>
       </c>
       <c r="R98" t="n">
-        <v>7010923</v>
+        <v>7010576</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10574,12 +10568,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rikligt, över 200</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -2304,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132341033</v>
+        <v>132341110</v>
       </c>
       <c r="B16" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,21 +2315,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438033</v>
+        <v>437169</v>
       </c>
       <c r="R16" t="n">
-        <v>7010948</v>
+        <v>7010552</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,11 +2375,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132341110</v>
+        <v>132341129</v>
       </c>
       <c r="B17" t="n">
-        <v>92191</v>
+        <v>91888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,21 +2412,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2441,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437169</v>
+        <v>437750</v>
       </c>
       <c r="R17" t="n">
-        <v>7010552</v>
+        <v>7010913</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2503,10 +2498,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132341129</v>
+        <v>132341033</v>
       </c>
       <c r="B18" t="n">
-        <v>91888</v>
+        <v>57948</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2514,21 +2509,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2538,10 +2533,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437750</v>
+        <v>438033</v>
       </c>
       <c r="R18" t="n">
-        <v>7010913</v>
+        <v>7010948</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2574,6 +2569,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3613,10 +3613,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132341132</v>
+        <v>132341041</v>
       </c>
       <c r="B29" t="n">
-        <v>91888</v>
+        <v>57948</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,21 +3624,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437384</v>
+        <v>437973</v>
       </c>
       <c r="R29" t="n">
-        <v>7010958</v>
+        <v>7010845</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,6 +3684,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3710,7 +3715,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132341041</v>
+        <v>132341040</v>
       </c>
       <c r="B30" t="n">
         <v>57948</v>
@@ -3745,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437973</v>
+        <v>438088</v>
       </c>
       <c r="R30" t="n">
-        <v>7010845</v>
+        <v>7010817</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,7 +3790,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3812,7 +3817,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132341040</v>
+        <v>132341049</v>
       </c>
       <c r="B31" t="n">
         <v>57948</v>
@@ -3847,10 +3852,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438088</v>
+        <v>437804</v>
       </c>
       <c r="R31" t="n">
-        <v>7010817</v>
+        <v>7010729</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3887,7 +3892,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3914,7 +3919,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132341049</v>
+        <v>132341029</v>
       </c>
       <c r="B32" t="n">
         <v>57948</v>
@@ -3949,10 +3954,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437804</v>
+        <v>437342</v>
       </c>
       <c r="R32" t="n">
-        <v>7010729</v>
+        <v>7010780</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3979,12 +3984,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4016,10 +4021,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132341029</v>
+        <v>132341132</v>
       </c>
       <c r="B33" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4027,21 +4032,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4051,10 +4056,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437342</v>
+        <v>437384</v>
       </c>
       <c r="R33" t="n">
-        <v>7010780</v>
+        <v>7010958</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4081,17 +4086,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5200,10 +5200,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132341057</v>
+        <v>132341095</v>
       </c>
       <c r="B45" t="n">
-        <v>57948</v>
+        <v>57945</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5211,16 +5211,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437606</v>
+        <v>437922</v>
       </c>
       <c r="R45" t="n">
         <v>7011053</v>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5302,10 +5302,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132341095</v>
+        <v>132341057</v>
       </c>
       <c r="B46" t="n">
-        <v>57945</v>
+        <v>57948</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5313,16 +5313,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437922</v>
+        <v>437606</v>
       </c>
       <c r="R46" t="n">
         <v>7011053</v>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6098,10 +6098,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132341094</v>
+        <v>132341119</v>
       </c>
       <c r="B54" t="n">
-        <v>57945</v>
+        <v>57127</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6109,16 +6109,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6126,17 +6126,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>438128</v>
+        <v>437582</v>
       </c>
       <c r="R54" t="n">
-        <v>7010852</v>
+        <v>7010573</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6163,17 +6175,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6200,10 +6207,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132341119</v>
+        <v>132341094</v>
       </c>
       <c r="B55" t="n">
-        <v>57127</v>
+        <v>57945</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6211,16 +6218,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6228,29 +6235,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437582</v>
+        <v>438128</v>
       </c>
       <c r="R55" t="n">
-        <v>7010573</v>
+        <v>7010852</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6277,12 +6272,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6309,10 +6309,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132341103</v>
+        <v>132341112</v>
       </c>
       <c r="B56" t="n">
-        <v>92191</v>
+        <v>80422</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6320,21 +6320,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437283</v>
+        <v>437518</v>
       </c>
       <c r="R56" t="n">
-        <v>7010896</v>
+        <v>7010858</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132340935</v>
+        <v>132341136</v>
       </c>
       <c r="B57" t="n">
-        <v>91892</v>
+        <v>79317</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6417,21 +6417,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437488</v>
+        <v>437640</v>
       </c>
       <c r="R57" t="n">
-        <v>7010535</v>
+        <v>7010681</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6477,6 +6477,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6503,10 +6508,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132341131</v>
+        <v>132341103</v>
       </c>
       <c r="B58" t="n">
-        <v>91888</v>
+        <v>92191</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6514,21 +6519,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6538,10 +6543,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437674</v>
+        <v>437283</v>
       </c>
       <c r="R58" t="n">
-        <v>7011000</v>
+        <v>7010896</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6600,10 +6605,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132341109</v>
+        <v>132340935</v>
       </c>
       <c r="B59" t="n">
-        <v>92191</v>
+        <v>91892</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6611,21 +6616,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6635,10 +6640,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437194</v>
+        <v>437488</v>
       </c>
       <c r="R59" t="n">
-        <v>7010597</v>
+        <v>7010535</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6665,12 +6670,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6697,10 +6702,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341112</v>
+        <v>132341131</v>
       </c>
       <c r="B60" t="n">
-        <v>80422</v>
+        <v>91888</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6708,21 +6713,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6732,10 +6737,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437518</v>
+        <v>437674</v>
       </c>
       <c r="R60" t="n">
-        <v>7010858</v>
+        <v>7011000</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6794,10 +6799,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132341136</v>
+        <v>132341109</v>
       </c>
       <c r="B61" t="n">
-        <v>79317</v>
+        <v>92191</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6805,21 +6810,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6829,10 +6834,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437640</v>
+        <v>437194</v>
       </c>
       <c r="R61" t="n">
-        <v>7010681</v>
+        <v>7010597</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6859,17 +6864,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7712,10 +7712,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132341096</v>
+        <v>132340946</v>
       </c>
       <c r="B70" t="n">
-        <v>57945</v>
+        <v>91892</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7723,21 +7723,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437096</v>
+        <v>437124</v>
       </c>
       <c r="R70" t="n">
-        <v>7010572</v>
+        <v>7010689</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7783,11 +7783,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7814,10 +7809,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132341053</v>
+        <v>132341102</v>
       </c>
       <c r="B71" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7825,21 +7820,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7849,10 +7844,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437740</v>
+        <v>437474</v>
       </c>
       <c r="R71" t="n">
-        <v>7011063</v>
+        <v>7010882</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7885,11 +7880,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7916,7 +7906,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132340946</v>
+        <v>132340944</v>
       </c>
       <c r="B72" t="n">
         <v>91892</v>
@@ -7951,10 +7941,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437124</v>
+        <v>437304</v>
       </c>
       <c r="R72" t="n">
-        <v>7010689</v>
+        <v>7010986</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8013,10 +8003,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132341102</v>
+        <v>132341096</v>
       </c>
       <c r="B73" t="n">
-        <v>92191</v>
+        <v>57945</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8024,21 +8014,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8048,10 +8038,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437474</v>
+        <v>437096</v>
       </c>
       <c r="R73" t="n">
-        <v>7010882</v>
+        <v>7010572</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8084,6 +8074,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8110,10 +8105,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132340944</v>
+        <v>132341053</v>
       </c>
       <c r="B74" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8121,21 +8116,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8145,10 +8140,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437304</v>
+        <v>437740</v>
       </c>
       <c r="R74" t="n">
-        <v>7010986</v>
+        <v>7011063</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8181,6 +8176,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8304,10 +8304,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341059</v>
+        <v>132341106</v>
       </c>
       <c r="B76" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8315,21 +8315,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437567</v>
+        <v>437009</v>
       </c>
       <c r="R76" t="n">
-        <v>7010953</v>
+        <v>7010701</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8375,11 +8375,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8406,10 +8401,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341106</v>
+        <v>132341059</v>
       </c>
       <c r="B77" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8417,21 +8412,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8441,10 +8436,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437009</v>
+        <v>437567</v>
       </c>
       <c r="R77" t="n">
-        <v>7010701</v>
+        <v>7010953</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8477,6 +8472,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8503,10 +8503,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132340942</v>
+        <v>132341065</v>
       </c>
       <c r="B78" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8514,21 +8514,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437287</v>
+        <v>437074</v>
       </c>
       <c r="R78" t="n">
-        <v>7010896</v>
+        <v>7010580</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8574,6 +8574,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8600,7 +8605,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132341065</v>
+        <v>132341045</v>
       </c>
       <c r="B79" t="n">
         <v>57948</v>
@@ -8635,10 +8640,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437074</v>
+        <v>437901</v>
       </c>
       <c r="R79" t="n">
-        <v>7010580</v>
+        <v>7010813</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8675,7 +8680,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8702,7 +8707,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132341045</v>
+        <v>132341030</v>
       </c>
       <c r="B80" t="n">
         <v>57948</v>
@@ -8737,10 +8742,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437901</v>
+        <v>438101</v>
       </c>
       <c r="R80" t="n">
-        <v>7010813</v>
+        <v>7010924</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8777,7 +8782,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8804,7 +8809,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132341030</v>
+        <v>132341063</v>
       </c>
       <c r="B81" t="n">
         <v>57948</v>
@@ -8839,10 +8844,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438101</v>
+        <v>437505</v>
       </c>
       <c r="R81" t="n">
-        <v>7010924</v>
+        <v>7010836</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8906,7 +8911,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132341063</v>
+        <v>132341043</v>
       </c>
       <c r="B82" t="n">
         <v>57948</v>
@@ -8941,10 +8946,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437505</v>
+        <v>437872</v>
       </c>
       <c r="R82" t="n">
-        <v>7010836</v>
+        <v>7010932</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8981,7 +8986,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9008,10 +9013,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341043</v>
+        <v>132340942</v>
       </c>
       <c r="B83" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9019,21 +9024,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9043,10 +9048,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437872</v>
+        <v>437287</v>
       </c>
       <c r="R83" t="n">
-        <v>7010932</v>
+        <v>7010896</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9079,11 +9084,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9207,10 +9207,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132341114</v>
+        <v>132341046</v>
       </c>
       <c r="B85" t="n">
-        <v>80422</v>
+        <v>57948</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9218,21 +9218,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437012</v>
+        <v>437902</v>
       </c>
       <c r="R85" t="n">
-        <v>7010575</v>
+        <v>7010811</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9278,6 +9278,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9304,7 +9309,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132341046</v>
+        <v>132341061</v>
       </c>
       <c r="B86" t="n">
         <v>57948</v>
@@ -9339,10 +9344,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>437902</v>
+        <v>437535</v>
       </c>
       <c r="R86" t="n">
-        <v>7010811</v>
+        <v>7010929</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9379,7 +9384,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9406,10 +9411,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132341061</v>
+        <v>132341114</v>
       </c>
       <c r="B87" t="n">
-        <v>57948</v>
+        <v>80422</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9417,21 +9422,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9441,10 +9446,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437535</v>
+        <v>437012</v>
       </c>
       <c r="R87" t="n">
-        <v>7010929</v>
+        <v>7010575</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9477,11 +9482,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -3401,7 +3401,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132341117</v>
+        <v>132341118</v>
       </c>
       <c r="B27" t="n">
         <v>99098</v>
@@ -3429,17 +3429,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437071</v>
+        <v>437059</v>
       </c>
       <c r="R27" t="n">
-        <v>7010578</v>
+        <v>7010572</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3474,12 +3486,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt över 200</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3498,7 +3516,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132341118</v>
+        <v>132341117</v>
       </c>
       <c r="B28" t="n">
         <v>99098</v>
@@ -3526,29 +3544,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437059</v>
+        <v>437071</v>
       </c>
       <c r="R28" t="n">
-        <v>7010572</v>
+        <v>7010578</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3583,18 +3589,12 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt över 200</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -5404,10 +5404,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132340949</v>
+        <v>132341055</v>
       </c>
       <c r="B47" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5415,21 +5415,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437092</v>
+        <v>437603</v>
       </c>
       <c r="R47" t="n">
-        <v>7010575</v>
+        <v>7011097</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5475,6 +5475,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5501,10 +5506,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132341055</v>
+        <v>132340949</v>
       </c>
       <c r="B48" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5512,21 +5517,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5536,10 +5541,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437603</v>
+        <v>437092</v>
       </c>
       <c r="R48" t="n">
-        <v>7011097</v>
+        <v>7010575</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5572,11 +5577,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5797,10 +5797,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132341027</v>
+        <v>132341108</v>
       </c>
       <c r="B51" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5808,21 +5808,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437678</v>
+        <v>437099</v>
       </c>
       <c r="R51" t="n">
-        <v>7010630</v>
+        <v>7010647</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5862,17 +5862,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5899,7 +5894,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132341062</v>
+        <v>132341027</v>
       </c>
       <c r="B52" t="n">
         <v>57948</v>
@@ -5934,10 +5929,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437538</v>
+        <v>437678</v>
       </c>
       <c r="R52" t="n">
-        <v>7010940</v>
+        <v>7010630</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5964,12 +5959,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6001,10 +5996,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132341108</v>
+        <v>132341062</v>
       </c>
       <c r="B53" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6012,21 +6007,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6036,10 +6031,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>437099</v>
+        <v>437538</v>
       </c>
       <c r="R53" t="n">
-        <v>7010647</v>
+        <v>7010940</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6072,6 +6067,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -9013,32 +9013,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132340942</v>
+        <v>132341115</v>
       </c>
       <c r="B83" t="n">
-        <v>91892</v>
+        <v>99098</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437287</v>
+        <v>437101</v>
       </c>
       <c r="R83" t="n">
-        <v>7010896</v>
+        <v>7010646</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9110,32 +9110,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132341115</v>
+        <v>132340942</v>
       </c>
       <c r="B84" t="n">
-        <v>99098</v>
+        <v>91892</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9145,10 +9145,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437101</v>
+        <v>437287</v>
       </c>
       <c r="R84" t="n">
-        <v>7010646</v>
+        <v>7010896</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9207,10 +9207,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132341046</v>
+        <v>132341114</v>
       </c>
       <c r="B85" t="n">
-        <v>57948</v>
+        <v>80422</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9218,21 +9218,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437902</v>
+        <v>437012</v>
       </c>
       <c r="R85" t="n">
-        <v>7010811</v>
+        <v>7010575</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9278,11 +9278,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9309,7 +9304,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132341061</v>
+        <v>132341046</v>
       </c>
       <c r="B86" t="n">
         <v>57948</v>
@@ -9344,10 +9339,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>437535</v>
+        <v>437902</v>
       </c>
       <c r="R86" t="n">
-        <v>7010929</v>
+        <v>7010811</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9384,7 +9379,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9411,10 +9406,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132341114</v>
+        <v>132341061</v>
       </c>
       <c r="B87" t="n">
-        <v>80422</v>
+        <v>57948</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9422,21 +9417,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9446,10 +9441,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437012</v>
+        <v>437535</v>
       </c>
       <c r="R87" t="n">
-        <v>7010575</v>
+        <v>7010929</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9482,6 +9477,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9508,10 +9508,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132341028</v>
+        <v>132340948</v>
       </c>
       <c r="B88" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9519,21 +9519,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9543,10 +9543,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437583</v>
+        <v>437159</v>
       </c>
       <c r="R88" t="n">
-        <v>7010708</v>
+        <v>7010541</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9573,17 +9573,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9610,7 +9605,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132340948</v>
+        <v>132340943</v>
       </c>
       <c r="B89" t="n">
         <v>91892</v>
@@ -9645,10 +9640,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437159</v>
+        <v>437280</v>
       </c>
       <c r="R89" t="n">
-        <v>7010541</v>
+        <v>7010923</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9707,7 +9702,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132340943</v>
+        <v>132340938</v>
       </c>
       <c r="B90" t="n">
         <v>91892</v>
@@ -9742,10 +9737,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437280</v>
+        <v>437465</v>
       </c>
       <c r="R90" t="n">
-        <v>7010923</v>
+        <v>7010897</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9804,7 +9799,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132340938</v>
+        <v>132340947</v>
       </c>
       <c r="B91" t="n">
         <v>91892</v>
@@ -9839,10 +9834,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437465</v>
+        <v>437023</v>
       </c>
       <c r="R91" t="n">
-        <v>7010897</v>
+        <v>7010700</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9901,7 +9896,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132340947</v>
+        <v>132340939</v>
       </c>
       <c r="B92" t="n">
         <v>91892</v>
@@ -9936,10 +9931,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437023</v>
+        <v>437481</v>
       </c>
       <c r="R92" t="n">
-        <v>7010700</v>
+        <v>7010828</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9998,10 +9993,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132340939</v>
+        <v>132341101</v>
       </c>
       <c r="B93" t="n">
-        <v>91892</v>
+        <v>92191</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10009,21 +10004,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10033,10 +10028,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>437481</v>
+        <v>437486</v>
       </c>
       <c r="R93" t="n">
-        <v>7010828</v>
+        <v>7010537</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10063,12 +10058,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10095,10 +10090,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132341101</v>
+        <v>132341097</v>
       </c>
       <c r="B94" t="n">
-        <v>92191</v>
+        <v>80423</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10106,21 +10101,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10130,10 +10125,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437486</v>
+        <v>437011</v>
       </c>
       <c r="R94" t="n">
-        <v>7010537</v>
+        <v>7010575</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10160,12 +10155,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10192,10 +10187,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132341097</v>
+        <v>132341028</v>
       </c>
       <c r="B95" t="n">
-        <v>80423</v>
+        <v>57948</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10203,21 +10198,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10227,10 +10222,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>437011</v>
+        <v>437583</v>
       </c>
       <c r="R95" t="n">
-        <v>7010575</v>
+        <v>7010708</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10257,12 +10252,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD95" t="b">

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -5404,10 +5404,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132341055</v>
+        <v>132340949</v>
       </c>
       <c r="B47" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5415,21 +5415,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437603</v>
+        <v>437092</v>
       </c>
       <c r="R47" t="n">
-        <v>7011097</v>
+        <v>7010575</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5475,11 +5475,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5506,10 +5501,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132340949</v>
+        <v>132341055</v>
       </c>
       <c r="B48" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5517,21 +5512,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5541,10 +5536,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437092</v>
+        <v>437603</v>
       </c>
       <c r="R48" t="n">
-        <v>7010575</v>
+        <v>7011097</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5577,6 +5572,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6098,10 +6098,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132341119</v>
+        <v>132341094</v>
       </c>
       <c r="B54" t="n">
-        <v>57127</v>
+        <v>57945</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6109,16 +6109,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6126,29 +6126,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437582</v>
+        <v>438128</v>
       </c>
       <c r="R54" t="n">
-        <v>7010573</v>
+        <v>7010852</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6175,12 +6163,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6207,10 +6200,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132341094</v>
+        <v>132341119</v>
       </c>
       <c r="B55" t="n">
-        <v>57945</v>
+        <v>57127</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6218,16 +6211,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6235,17 +6228,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>438128</v>
+        <v>437582</v>
       </c>
       <c r="R55" t="n">
-        <v>7010852</v>
+        <v>7010573</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6272,17 +6277,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -9013,32 +9013,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341115</v>
+        <v>132340942</v>
       </c>
       <c r="B83" t="n">
-        <v>99098</v>
+        <v>91892</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437101</v>
+        <v>437287</v>
       </c>
       <c r="R83" t="n">
-        <v>7010646</v>
+        <v>7010896</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9110,32 +9110,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132340942</v>
+        <v>132341115</v>
       </c>
       <c r="B84" t="n">
-        <v>91892</v>
+        <v>99098</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9145,10 +9145,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437287</v>
+        <v>437101</v>
       </c>
       <c r="R84" t="n">
-        <v>7010896</v>
+        <v>7010646</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9508,10 +9508,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132340948</v>
+        <v>132341028</v>
       </c>
       <c r="B88" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9519,21 +9519,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9543,10 +9543,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437159</v>
+        <v>437583</v>
       </c>
       <c r="R88" t="n">
-        <v>7010541</v>
+        <v>7010708</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9573,12 +9573,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9605,7 +9610,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132340943</v>
+        <v>132340948</v>
       </c>
       <c r="B89" t="n">
         <v>91892</v>
@@ -9640,10 +9645,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437280</v>
+        <v>437159</v>
       </c>
       <c r="R89" t="n">
-        <v>7010923</v>
+        <v>7010541</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9702,7 +9707,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132340938</v>
+        <v>132340943</v>
       </c>
       <c r="B90" t="n">
         <v>91892</v>
@@ -9737,10 +9742,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437465</v>
+        <v>437280</v>
       </c>
       <c r="R90" t="n">
-        <v>7010897</v>
+        <v>7010923</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9799,7 +9804,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132340947</v>
+        <v>132340938</v>
       </c>
       <c r="B91" t="n">
         <v>91892</v>
@@ -9834,10 +9839,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437023</v>
+        <v>437465</v>
       </c>
       <c r="R91" t="n">
-        <v>7010700</v>
+        <v>7010897</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9896,7 +9901,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132340939</v>
+        <v>132340947</v>
       </c>
       <c r="B92" t="n">
         <v>91892</v>
@@ -9931,10 +9936,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437481</v>
+        <v>437023</v>
       </c>
       <c r="R92" t="n">
-        <v>7010828</v>
+        <v>7010700</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9993,10 +9998,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132341101</v>
+        <v>132340939</v>
       </c>
       <c r="B93" t="n">
-        <v>92191</v>
+        <v>91892</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10004,21 +10009,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10028,10 +10033,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>437486</v>
+        <v>437481</v>
       </c>
       <c r="R93" t="n">
-        <v>7010537</v>
+        <v>7010828</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10058,12 +10063,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10090,10 +10095,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132341097</v>
+        <v>132341101</v>
       </c>
       <c r="B94" t="n">
-        <v>80423</v>
+        <v>92191</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10101,21 +10106,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10125,10 +10130,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437011</v>
+        <v>437486</v>
       </c>
       <c r="R94" t="n">
-        <v>7010575</v>
+        <v>7010537</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10155,12 +10160,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10187,10 +10192,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132341028</v>
+        <v>132341097</v>
       </c>
       <c r="B95" t="n">
-        <v>57948</v>
+        <v>80423</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10198,21 +10203,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10222,10 +10227,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>437583</v>
+        <v>437011</v>
       </c>
       <c r="R95" t="n">
-        <v>7010708</v>
+        <v>7010575</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10252,17 +10257,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD95" t="b">

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -5404,10 +5404,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132340949</v>
+        <v>132341055</v>
       </c>
       <c r="B47" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5415,21 +5415,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437092</v>
+        <v>437603</v>
       </c>
       <c r="R47" t="n">
-        <v>7010575</v>
+        <v>7011097</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5475,6 +5475,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5501,10 +5506,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132341055</v>
+        <v>132340949</v>
       </c>
       <c r="B48" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5512,21 +5517,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5536,10 +5541,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437603</v>
+        <v>437092</v>
       </c>
       <c r="R48" t="n">
-        <v>7011097</v>
+        <v>7010575</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5572,11 +5577,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5797,10 +5797,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132341108</v>
+        <v>132341027</v>
       </c>
       <c r="B51" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5808,21 +5808,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437099</v>
+        <v>437678</v>
       </c>
       <c r="R51" t="n">
-        <v>7010647</v>
+        <v>7010630</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5862,12 +5862,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5894,7 +5899,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132341027</v>
+        <v>132341062</v>
       </c>
       <c r="B52" t="n">
         <v>57948</v>
@@ -5929,10 +5934,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437678</v>
+        <v>437538</v>
       </c>
       <c r="R52" t="n">
-        <v>7010630</v>
+        <v>7010940</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5959,12 +5964,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -5996,10 +6001,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132341062</v>
+        <v>132341108</v>
       </c>
       <c r="B53" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6007,21 +6012,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6031,10 +6036,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>437538</v>
+        <v>437099</v>
       </c>
       <c r="R53" t="n">
-        <v>7010940</v>
+        <v>7010647</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6067,11 +6072,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -8304,10 +8304,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341106</v>
+        <v>132341059</v>
       </c>
       <c r="B76" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8315,21 +8315,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437009</v>
+        <v>437567</v>
       </c>
       <c r="R76" t="n">
-        <v>7010701</v>
+        <v>7010953</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8375,6 +8375,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8401,10 +8406,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341059</v>
+        <v>132341106</v>
       </c>
       <c r="B77" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8412,21 +8417,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8436,10 +8441,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437567</v>
+        <v>437009</v>
       </c>
       <c r="R77" t="n">
-        <v>7010953</v>
+        <v>7010701</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8472,11 +8477,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9013,32 +9013,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132340942</v>
+        <v>132341115</v>
       </c>
       <c r="B83" t="n">
-        <v>91892</v>
+        <v>99098</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437287</v>
+        <v>437101</v>
       </c>
       <c r="R83" t="n">
-        <v>7010896</v>
+        <v>7010646</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9110,32 +9110,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132341115</v>
+        <v>132340942</v>
       </c>
       <c r="B84" t="n">
-        <v>99098</v>
+        <v>91892</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9145,10 +9145,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437101</v>
+        <v>437287</v>
       </c>
       <c r="R84" t="n">
-        <v>7010646</v>
+        <v>7010896</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -2307,7 +2307,7 @@
         <v>132341110</v>
       </c>
       <c r="B16" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>132341129</v>
       </c>
       <c r="B17" t="n">
-        <v>91888</v>
+        <v>91894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>132341033</v>
       </c>
       <c r="B18" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>132341126</v>
       </c>
       <c r="B19" t="n">
-        <v>91888</v>
+        <v>91894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>132341137</v>
       </c>
       <c r="B20" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>132341048</v>
       </c>
       <c r="B21" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>132341058</v>
       </c>
       <c r="B22" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132340941</v>
+        <v>132341064</v>
       </c>
       <c r="B23" t="n">
-        <v>91892</v>
+        <v>57949</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437348</v>
+        <v>437442</v>
       </c>
       <c r="R23" t="n">
-        <v>7010989</v>
+        <v>7010869</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,6 +3074,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3100,10 +3105,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132341113</v>
+        <v>132341060</v>
       </c>
       <c r="B24" t="n">
-        <v>80422</v>
+        <v>57949</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3111,21 +3116,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3135,10 +3140,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437053</v>
+        <v>437611</v>
       </c>
       <c r="R24" t="n">
-        <v>7010706</v>
+        <v>7010882</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3171,6 +3176,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3197,10 +3207,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132341060</v>
+        <v>132340941</v>
       </c>
       <c r="B25" t="n">
-        <v>57948</v>
+        <v>91898</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3208,21 +3218,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3232,10 +3242,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437611</v>
+        <v>437348</v>
       </c>
       <c r="R25" t="n">
-        <v>7010882</v>
+        <v>7010989</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3268,11 +3278,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3299,10 +3304,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132341064</v>
+        <v>132341113</v>
       </c>
       <c r="B26" t="n">
-        <v>57948</v>
+        <v>80424</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3310,21 +3315,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3334,10 +3339,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437442</v>
+        <v>437053</v>
       </c>
       <c r="R26" t="n">
-        <v>7010869</v>
+        <v>7010706</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3370,11 +3375,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3401,10 +3401,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132341118</v>
+        <v>132341117</v>
       </c>
       <c r="B27" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3429,29 +3429,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437059</v>
+        <v>437071</v>
       </c>
       <c r="R27" t="n">
-        <v>7010572</v>
+        <v>7010578</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3486,18 +3474,12 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt över 200</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3516,10 +3498,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132341117</v>
+        <v>132341118</v>
       </c>
       <c r="B28" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3544,17 +3526,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437071</v>
+        <v>437059</v>
       </c>
       <c r="R28" t="n">
-        <v>7010578</v>
+        <v>7010572</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,12 +3583,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt över 200</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3613,10 +3613,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132341041</v>
+        <v>132341132</v>
       </c>
       <c r="B29" t="n">
-        <v>57948</v>
+        <v>91894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,21 +3624,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437973</v>
+        <v>437384</v>
       </c>
       <c r="R29" t="n">
-        <v>7010845</v>
+        <v>7010958</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,11 +3684,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3718,7 +3713,7 @@
         <v>132341040</v>
       </c>
       <c r="B30" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3820,7 +3815,7 @@
         <v>132341049</v>
       </c>
       <c r="B31" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3922,7 +3917,7 @@
         <v>132341029</v>
       </c>
       <c r="B32" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4021,10 +4016,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132341132</v>
+        <v>132341041</v>
       </c>
       <c r="B33" t="n">
-        <v>91888</v>
+        <v>57949</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4032,21 +4027,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4056,10 +4051,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437384</v>
+        <v>437973</v>
       </c>
       <c r="R33" t="n">
-        <v>7010958</v>
+        <v>7010845</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4092,6 +4087,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4118,10 +4118,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132341047</v>
+        <v>132341138</v>
       </c>
       <c r="B34" t="n">
-        <v>57948</v>
+        <v>79319</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4129,21 +4129,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437918</v>
+        <v>437710</v>
       </c>
       <c r="R34" t="n">
-        <v>7010791</v>
+        <v>7010507</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4220,10 +4220,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132341138</v>
+        <v>132341047</v>
       </c>
       <c r="B35" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437710</v>
+        <v>437918</v>
       </c>
       <c r="R35" t="n">
-        <v>7010507</v>
+        <v>7010791</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4325,7 +4325,7 @@
         <v>132341135</v>
       </c>
       <c r="B36" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>132340936</v>
       </c>
       <c r="B37" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>132341140</v>
       </c>
       <c r="B38" t="n">
-        <v>92588</v>
+        <v>92594</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>132341100</v>
       </c>
       <c r="B39" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>132341128</v>
       </c>
       <c r="B40" t="n">
-        <v>91888</v>
+        <v>91894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>132340940</v>
       </c>
       <c r="B41" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>132341134</v>
       </c>
       <c r="B42" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>132341105</v>
       </c>
       <c r="B43" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>132341054</v>
       </c>
       <c r="B44" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>132341095</v>
       </c>
       <c r="B45" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>132341057</v>
       </c>
       <c r="B46" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5404,10 +5404,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132341055</v>
+        <v>132340949</v>
       </c>
       <c r="B47" t="n">
-        <v>57948</v>
+        <v>91898</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5415,21 +5415,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437603</v>
+        <v>437092</v>
       </c>
       <c r="R47" t="n">
-        <v>7011097</v>
+        <v>7010575</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5475,11 +5475,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5506,10 +5501,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132340949</v>
+        <v>132341055</v>
       </c>
       <c r="B48" t="n">
-        <v>91892</v>
+        <v>57949</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5517,21 +5512,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5541,10 +5536,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437092</v>
+        <v>437603</v>
       </c>
       <c r="R48" t="n">
-        <v>7010575</v>
+        <v>7011097</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5577,6 +5572,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5606,7 +5606,7 @@
         <v>132341127</v>
       </c>
       <c r="B49" t="n">
-        <v>91888</v>
+        <v>91894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>132341125</v>
       </c>
       <c r="B50" t="n">
-        <v>91888</v>
+        <v>91894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132341027</v>
+        <v>132341062</v>
       </c>
       <c r="B51" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437678</v>
+        <v>437538</v>
       </c>
       <c r="R51" t="n">
-        <v>7010630</v>
+        <v>7010940</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5862,12 +5862,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -5899,10 +5899,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132341062</v>
+        <v>132341108</v>
       </c>
       <c r="B52" t="n">
-        <v>57948</v>
+        <v>92197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5910,21 +5910,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437538</v>
+        <v>437099</v>
       </c>
       <c r="R52" t="n">
-        <v>7010940</v>
+        <v>7010647</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5970,11 +5970,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6001,10 +5996,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132341108</v>
+        <v>132341027</v>
       </c>
       <c r="B53" t="n">
-        <v>92191</v>
+        <v>57949</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6012,21 +6007,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6036,10 +6031,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>437099</v>
+        <v>437678</v>
       </c>
       <c r="R53" t="n">
-        <v>7010647</v>
+        <v>7010630</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6066,12 +6061,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6098,10 +6098,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132341094</v>
+        <v>132341119</v>
       </c>
       <c r="B54" t="n">
-        <v>57945</v>
+        <v>57128</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6109,16 +6109,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6126,17 +6126,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>438128</v>
+        <v>437582</v>
       </c>
       <c r="R54" t="n">
-        <v>7010852</v>
+        <v>7010573</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6163,17 +6175,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6200,10 +6207,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132341119</v>
+        <v>132341094</v>
       </c>
       <c r="B55" t="n">
-        <v>57127</v>
+        <v>57946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6211,16 +6218,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6228,29 +6235,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437582</v>
+        <v>438128</v>
       </c>
       <c r="R55" t="n">
-        <v>7010573</v>
+        <v>7010852</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6277,12 +6272,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6309,10 +6309,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132341112</v>
+        <v>132341103</v>
       </c>
       <c r="B56" t="n">
-        <v>80422</v>
+        <v>92197</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6320,21 +6320,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437518</v>
+        <v>437283</v>
       </c>
       <c r="R56" t="n">
-        <v>7010858</v>
+        <v>7010896</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132341136</v>
+        <v>132340935</v>
       </c>
       <c r="B57" t="n">
-        <v>79317</v>
+        <v>91898</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6417,21 +6417,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437640</v>
+        <v>437488</v>
       </c>
       <c r="R57" t="n">
-        <v>7010681</v>
+        <v>7010535</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6477,11 +6477,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6508,10 +6503,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132341103</v>
+        <v>132341131</v>
       </c>
       <c r="B58" t="n">
-        <v>92191</v>
+        <v>91894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6519,21 +6514,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6543,10 +6538,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437283</v>
+        <v>437674</v>
       </c>
       <c r="R58" t="n">
-        <v>7010896</v>
+        <v>7011000</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6605,10 +6600,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132340935</v>
+        <v>132341109</v>
       </c>
       <c r="B59" t="n">
-        <v>91892</v>
+        <v>92197</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6616,21 +6611,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6640,10 +6635,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437488</v>
+        <v>437194</v>
       </c>
       <c r="R59" t="n">
-        <v>7010535</v>
+        <v>7010597</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6670,12 +6665,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6702,10 +6697,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341131</v>
+        <v>132341136</v>
       </c>
       <c r="B60" t="n">
-        <v>91888</v>
+        <v>79319</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6713,21 +6708,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6737,10 +6732,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437674</v>
+        <v>437640</v>
       </c>
       <c r="R60" t="n">
-        <v>7011000</v>
+        <v>7010681</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6767,12 +6762,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6799,10 +6799,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132341109</v>
+        <v>132341112</v>
       </c>
       <c r="B61" t="n">
-        <v>92191</v>
+        <v>80424</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6810,21 +6810,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437194</v>
+        <v>437518</v>
       </c>
       <c r="R61" t="n">
-        <v>7010597</v>
+        <v>7010858</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6896,10 +6896,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132341052</v>
+        <v>132341051</v>
       </c>
       <c r="B62" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6931,10 +6931,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437740</v>
+        <v>437746</v>
       </c>
       <c r="R62" t="n">
-        <v>7011055</v>
+        <v>7010946</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6998,10 +6998,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132341037</v>
+        <v>132341031</v>
       </c>
       <c r="B63" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437926</v>
+        <v>438101</v>
       </c>
       <c r="R63" t="n">
-        <v>7011061</v>
+        <v>7010919</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7103,7 +7103,7 @@
         <v>132341056</v>
       </c>
       <c r="B64" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7202,10 +7202,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132341032</v>
+        <v>132341052</v>
       </c>
       <c r="B65" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>438064</v>
+        <v>437740</v>
       </c>
       <c r="R65" t="n">
-        <v>7010908</v>
+        <v>7011055</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7304,10 +7304,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132341066</v>
+        <v>132341032</v>
       </c>
       <c r="B66" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436968</v>
+        <v>438064</v>
       </c>
       <c r="R66" t="n">
-        <v>7010599</v>
+        <v>7010908</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7406,10 +7406,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132341051</v>
+        <v>132341037</v>
       </c>
       <c r="B67" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437746</v>
+        <v>437926</v>
       </c>
       <c r="R67" t="n">
-        <v>7010946</v>
+        <v>7011061</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7508,10 +7508,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132341031</v>
+        <v>132341066</v>
       </c>
       <c r="B68" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7543,10 +7543,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438101</v>
+        <v>436968</v>
       </c>
       <c r="R68" t="n">
-        <v>7010919</v>
+        <v>7010599</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7613,7 +7613,7 @@
         <v>132341034</v>
       </c>
       <c r="B69" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>132340946</v>
       </c>
       <c r="B70" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>132341102</v>
       </c>
       <c r="B71" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>132340944</v>
       </c>
       <c r="B72" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132341096</v>
+        <v>132341111</v>
       </c>
       <c r="B73" t="n">
-        <v>57945</v>
+        <v>80424</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8014,21 +8014,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437096</v>
+        <v>437156</v>
       </c>
       <c r="R73" t="n">
-        <v>7010572</v>
+        <v>7010645</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8068,17 +8068,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8105,10 +8100,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341053</v>
+        <v>132341096</v>
       </c>
       <c r="B74" t="n">
-        <v>57948</v>
+        <v>57946</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8116,16 +8111,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8140,10 +8135,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437740</v>
+        <v>437096</v>
       </c>
       <c r="R74" t="n">
-        <v>7011063</v>
+        <v>7010572</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8180,7 +8175,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8207,10 +8202,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341111</v>
+        <v>132341053</v>
       </c>
       <c r="B75" t="n">
-        <v>80422</v>
+        <v>57949</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8218,21 +8213,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8242,10 +8237,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437156</v>
+        <v>437740</v>
       </c>
       <c r="R75" t="n">
-        <v>7010645</v>
+        <v>7011063</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8272,12 +8267,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8304,10 +8304,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341059</v>
+        <v>132341106</v>
       </c>
       <c r="B76" t="n">
-        <v>57948</v>
+        <v>92197</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8315,21 +8315,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437567</v>
+        <v>437009</v>
       </c>
       <c r="R76" t="n">
-        <v>7010953</v>
+        <v>7010701</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8375,11 +8375,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8406,10 +8401,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341106</v>
+        <v>132341059</v>
       </c>
       <c r="B77" t="n">
-        <v>92191</v>
+        <v>57949</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8417,21 +8412,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8441,10 +8436,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437009</v>
+        <v>437567</v>
       </c>
       <c r="R77" t="n">
-        <v>7010701</v>
+        <v>7010953</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8477,6 +8472,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8503,32 +8503,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132341065</v>
+        <v>132341115</v>
       </c>
       <c r="B78" t="n">
-        <v>57948</v>
+        <v>99106</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437074</v>
+        <v>437101</v>
       </c>
       <c r="R78" t="n">
-        <v>7010580</v>
+        <v>7010646</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8574,11 +8574,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8605,10 +8600,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132341045</v>
+        <v>132340942</v>
       </c>
       <c r="B79" t="n">
-        <v>57948</v>
+        <v>91898</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8616,21 +8611,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8640,10 +8635,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437901</v>
+        <v>437287</v>
       </c>
       <c r="R79" t="n">
-        <v>7010813</v>
+        <v>7010896</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8676,11 +8671,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8707,10 +8697,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132341030</v>
+        <v>132341063</v>
       </c>
       <c r="B80" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8742,10 +8732,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438101</v>
+        <v>437505</v>
       </c>
       <c r="R80" t="n">
-        <v>7010924</v>
+        <v>7010836</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8809,10 +8799,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132341063</v>
+        <v>132341045</v>
       </c>
       <c r="B81" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8844,10 +8834,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437505</v>
+        <v>437901</v>
       </c>
       <c r="R81" t="n">
-        <v>7010836</v>
+        <v>7010813</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8884,7 +8874,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8911,10 +8901,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132341043</v>
+        <v>132341065</v>
       </c>
       <c r="B82" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8946,10 +8936,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437872</v>
+        <v>437074</v>
       </c>
       <c r="R82" t="n">
-        <v>7010932</v>
+        <v>7010580</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8986,7 +8976,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9013,32 +9003,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341115</v>
+        <v>132341043</v>
       </c>
       <c r="B83" t="n">
-        <v>99098</v>
+        <v>57949</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9048,10 +9038,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437101</v>
+        <v>437872</v>
       </c>
       <c r="R83" t="n">
-        <v>7010646</v>
+        <v>7010932</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9084,6 +9074,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9110,10 +9105,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132340942</v>
+        <v>132341030</v>
       </c>
       <c r="B84" t="n">
-        <v>91892</v>
+        <v>57949</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9121,21 +9116,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9145,10 +9140,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437287</v>
+        <v>438101</v>
       </c>
       <c r="R84" t="n">
-        <v>7010896</v>
+        <v>7010924</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9181,6 +9176,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9210,7 +9210,7 @@
         <v>132341114</v>
       </c>
       <c r="B85" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>132341046</v>
       </c>
       <c r="B86" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>132341061</v>
       </c>
       <c r="B87" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9508,10 +9508,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132341028</v>
+        <v>132340948</v>
       </c>
       <c r="B88" t="n">
-        <v>57948</v>
+        <v>91898</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9519,21 +9519,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9543,10 +9543,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437583</v>
+        <v>437159</v>
       </c>
       <c r="R88" t="n">
-        <v>7010708</v>
+        <v>7010541</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9573,17 +9573,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9610,10 +9605,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132340948</v>
+        <v>132340943</v>
       </c>
       <c r="B89" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9645,10 +9640,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437159</v>
+        <v>437280</v>
       </c>
       <c r="R89" t="n">
-        <v>7010541</v>
+        <v>7010923</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9707,10 +9702,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132340943</v>
+        <v>132340938</v>
       </c>
       <c r="B90" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9742,10 +9737,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437280</v>
+        <v>437465</v>
       </c>
       <c r="R90" t="n">
-        <v>7010923</v>
+        <v>7010897</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9804,10 +9799,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132340938</v>
+        <v>132340947</v>
       </c>
       <c r="B91" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9839,10 +9834,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437465</v>
+        <v>437023</v>
       </c>
       <c r="R91" t="n">
-        <v>7010897</v>
+        <v>7010700</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9901,10 +9896,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132340947</v>
+        <v>132340939</v>
       </c>
       <c r="B92" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9936,10 +9931,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437023</v>
+        <v>437481</v>
       </c>
       <c r="R92" t="n">
-        <v>7010700</v>
+        <v>7010828</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9998,10 +9993,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132340939</v>
+        <v>132341101</v>
       </c>
       <c r="B93" t="n">
-        <v>91892</v>
+        <v>92197</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10009,21 +10004,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10033,10 +10028,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>437481</v>
+        <v>437486</v>
       </c>
       <c r="R93" t="n">
-        <v>7010828</v>
+        <v>7010537</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10063,12 +10058,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10095,10 +10090,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132341101</v>
+        <v>132341097</v>
       </c>
       <c r="B94" t="n">
-        <v>92191</v>
+        <v>80425</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10106,21 +10101,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10130,10 +10125,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437486</v>
+        <v>437011</v>
       </c>
       <c r="R94" t="n">
-        <v>7010537</v>
+        <v>7010575</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10160,12 +10155,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10192,10 +10187,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132341097</v>
+        <v>132341028</v>
       </c>
       <c r="B95" t="n">
-        <v>80423</v>
+        <v>57949</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10203,21 +10198,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10227,10 +10222,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>437011</v>
+        <v>437583</v>
       </c>
       <c r="R95" t="n">
-        <v>7010575</v>
+        <v>7010708</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10257,12 +10252,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10292,7 +10292,7 @@
         <v>132341107</v>
       </c>
       <c r="B96" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>132341104</v>
       </c>
       <c r="B97" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>132341116</v>
       </c>
       <c r="B98" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -3003,10 +3003,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132341064</v>
+        <v>132340941</v>
       </c>
       <c r="B23" t="n">
-        <v>57949</v>
+        <v>91898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437442</v>
+        <v>437348</v>
       </c>
       <c r="R23" t="n">
-        <v>7010869</v>
+        <v>7010989</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,11 +3074,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3105,10 +3100,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132341060</v>
+        <v>132341113</v>
       </c>
       <c r="B24" t="n">
-        <v>57949</v>
+        <v>80424</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3116,21 +3111,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3140,10 +3135,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437611</v>
+        <v>437053</v>
       </c>
       <c r="R24" t="n">
-        <v>7010882</v>
+        <v>7010706</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3176,11 +3171,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3207,10 +3197,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132340941</v>
+        <v>132341064</v>
       </c>
       <c r="B25" t="n">
-        <v>91898</v>
+        <v>57949</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3218,21 +3208,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3242,10 +3232,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437348</v>
+        <v>437442</v>
       </c>
       <c r="R25" t="n">
-        <v>7010989</v>
+        <v>7010869</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3278,6 +3268,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3304,10 +3299,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132341113</v>
+        <v>132341060</v>
       </c>
       <c r="B26" t="n">
-        <v>80424</v>
+        <v>57949</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3315,21 +3310,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3339,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437053</v>
+        <v>437611</v>
       </c>
       <c r="R26" t="n">
-        <v>7010706</v>
+        <v>7010882</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,6 +3370,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -5797,10 +5797,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132341062</v>
+        <v>132341108</v>
       </c>
       <c r="B51" t="n">
-        <v>57949</v>
+        <v>92197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5808,21 +5808,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437538</v>
+        <v>437099</v>
       </c>
       <c r="R51" t="n">
-        <v>7010940</v>
+        <v>7010647</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5868,11 +5868,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5899,10 +5894,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132341108</v>
+        <v>132341027</v>
       </c>
       <c r="B52" t="n">
-        <v>92197</v>
+        <v>57949</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5910,21 +5905,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5934,10 +5929,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437099</v>
+        <v>437678</v>
       </c>
       <c r="R52" t="n">
-        <v>7010647</v>
+        <v>7010630</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5964,12 +5959,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5996,7 +5996,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132341027</v>
+        <v>132341062</v>
       </c>
       <c r="B53" t="n">
         <v>57949</v>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>437678</v>
+        <v>437538</v>
       </c>
       <c r="R53" t="n">
-        <v>7010630</v>
+        <v>7010940</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6098,10 +6098,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132341119</v>
+        <v>132341094</v>
       </c>
       <c r="B54" t="n">
-        <v>57128</v>
+        <v>57946</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6109,16 +6109,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6126,29 +6126,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437582</v>
+        <v>438128</v>
       </c>
       <c r="R54" t="n">
-        <v>7010573</v>
+        <v>7010852</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6175,12 +6163,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6207,10 +6200,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132341094</v>
+        <v>132341119</v>
       </c>
       <c r="B55" t="n">
-        <v>57946</v>
+        <v>57128</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6218,16 +6211,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6235,17 +6228,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>438128</v>
+        <v>437582</v>
       </c>
       <c r="R55" t="n">
-        <v>7010852</v>
+        <v>7010573</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6272,17 +6277,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -10289,45 +10289,57 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132341107</v>
+        <v>132341116</v>
       </c>
       <c r="B96" t="n">
-        <v>92197</v>
+        <v>99106</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436990</v>
+        <v>437089</v>
       </c>
       <c r="R96" t="n">
-        <v>7010703</v>
+        <v>7010576</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10362,12 +10374,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Rikligt, över 200</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10386,7 +10404,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132341104</v>
+        <v>132341107</v>
       </c>
       <c r="B97" t="n">
         <v>92197</v>
@@ -10421,10 +10439,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>437280</v>
+        <v>436990</v>
       </c>
       <c r="R97" t="n">
-        <v>7010923</v>
+        <v>7010703</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10483,57 +10501,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132341116</v>
+        <v>132341104</v>
       </c>
       <c r="B98" t="n">
-        <v>99106</v>
+        <v>92197</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437089</v>
+        <v>437280</v>
       </c>
       <c r="R98" t="n">
-        <v>7010576</v>
+        <v>7010923</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10568,18 +10574,12 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Rikligt, över 200</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -2307,7 +2307,7 @@
         <v>132341110</v>
       </c>
       <c r="B16" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>132341129</v>
       </c>
       <c r="B17" t="n">
-        <v>91894</v>
+        <v>91904</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>132341033</v>
       </c>
       <c r="B18" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2600,10 +2600,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132341126</v>
+        <v>132341137</v>
       </c>
       <c r="B19" t="n">
-        <v>91894</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2611,21 +2611,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437525</v>
+        <v>437632</v>
       </c>
       <c r="R19" t="n">
-        <v>7010475</v>
+        <v>7010619</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2665,12 +2665,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2697,10 +2702,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132341137</v>
+        <v>132341058</v>
       </c>
       <c r="B20" t="n">
-        <v>79319</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,21 +2713,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2732,10 +2737,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437632</v>
+        <v>437635</v>
       </c>
       <c r="R20" t="n">
-        <v>7010619</v>
+        <v>7011011</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2762,17 +2767,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2802,7 +2807,7 @@
         <v>132341048</v>
       </c>
       <c r="B21" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,10 +2906,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132341058</v>
+        <v>132341126</v>
       </c>
       <c r="B22" t="n">
-        <v>57949</v>
+        <v>91904</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2912,21 +2917,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2936,10 +2941,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437635</v>
+        <v>437525</v>
       </c>
       <c r="R22" t="n">
-        <v>7011011</v>
+        <v>7010475</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2972,11 +2977,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3003,10 +3003,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132340941</v>
+        <v>132341060</v>
       </c>
       <c r="B23" t="n">
-        <v>91898</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437348</v>
+        <v>437611</v>
       </c>
       <c r="R23" t="n">
-        <v>7010989</v>
+        <v>7010882</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,6 +3074,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3100,10 +3105,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132341113</v>
+        <v>132341064</v>
       </c>
       <c r="B24" t="n">
-        <v>80424</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3111,21 +3116,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3135,10 +3140,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437053</v>
+        <v>437442</v>
       </c>
       <c r="R24" t="n">
-        <v>7010706</v>
+        <v>7010869</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3171,6 +3176,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3197,10 +3207,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132341064</v>
+        <v>132340941</v>
       </c>
       <c r="B25" t="n">
-        <v>57949</v>
+        <v>91908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3208,21 +3218,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3232,10 +3242,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437442</v>
+        <v>437348</v>
       </c>
       <c r="R25" t="n">
-        <v>7010869</v>
+        <v>7010989</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3268,11 +3278,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3299,10 +3304,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132341060</v>
+        <v>132341113</v>
       </c>
       <c r="B26" t="n">
-        <v>57949</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3310,21 +3315,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3334,10 +3339,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437611</v>
+        <v>437053</v>
       </c>
       <c r="R26" t="n">
-        <v>7010882</v>
+        <v>7010706</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3370,11 +3375,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3404,7 +3404,7 @@
         <v>132341117</v>
       </c>
       <c r="B27" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>132341118</v>
       </c>
       <c r="B28" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132341132</v>
+        <v>132341029</v>
       </c>
       <c r="B29" t="n">
-        <v>91894</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,21 +3624,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437384</v>
+        <v>437342</v>
       </c>
       <c r="R29" t="n">
-        <v>7010958</v>
+        <v>7010780</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,12 +3678,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3710,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132341040</v>
+        <v>132341132</v>
       </c>
       <c r="B30" t="n">
-        <v>57949</v>
+        <v>91904</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3721,21 +3726,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438088</v>
+        <v>437384</v>
       </c>
       <c r="R30" t="n">
-        <v>7010817</v>
+        <v>7010958</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3781,11 +3786,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3812,10 +3812,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132341049</v>
+        <v>132341041</v>
       </c>
       <c r="B31" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437804</v>
+        <v>437973</v>
       </c>
       <c r="R31" t="n">
-        <v>7010729</v>
+        <v>7010845</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3914,10 +3914,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132341029</v>
+        <v>132341040</v>
       </c>
       <c r="B32" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437342</v>
+        <v>438088</v>
       </c>
       <c r="R32" t="n">
-        <v>7010780</v>
+        <v>7010817</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3979,17 +3979,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4016,10 +4016,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132341041</v>
+        <v>132341049</v>
       </c>
       <c r="B33" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437973</v>
+        <v>437804</v>
       </c>
       <c r="R33" t="n">
-        <v>7010845</v>
+        <v>7010729</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4118,10 +4118,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132341138</v>
+        <v>132341047</v>
       </c>
       <c r="B34" t="n">
-        <v>79319</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4129,21 +4129,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437710</v>
+        <v>437918</v>
       </c>
       <c r="R34" t="n">
-        <v>7010507</v>
+        <v>7010791</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4220,10 +4220,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132341047</v>
+        <v>132341138</v>
       </c>
       <c r="B35" t="n">
-        <v>57949</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437918</v>
+        <v>437710</v>
       </c>
       <c r="R35" t="n">
-        <v>7010791</v>
+        <v>7010507</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4325,7 +4325,7 @@
         <v>132341135</v>
       </c>
       <c r="B36" t="n">
-        <v>91912</v>
+        <v>91922</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>132340936</v>
       </c>
       <c r="B37" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>132341140</v>
       </c>
       <c r="B38" t="n">
-        <v>92594</v>
+        <v>92604</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>132341100</v>
       </c>
       <c r="B39" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>132341128</v>
       </c>
       <c r="B40" t="n">
-        <v>91894</v>
+        <v>91904</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4807,10 +4807,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132340940</v>
+        <v>132341134</v>
       </c>
       <c r="B41" t="n">
-        <v>91898</v>
+        <v>91922</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4818,21 +4818,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437350</v>
+        <v>437611</v>
       </c>
       <c r="R41" t="n">
-        <v>7010948</v>
+        <v>7011053</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4904,10 +4904,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132341134</v>
+        <v>132341105</v>
       </c>
       <c r="B42" t="n">
-        <v>91912</v>
+        <v>92207</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4915,21 +4915,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437611</v>
+        <v>437027</v>
       </c>
       <c r="R42" t="n">
-        <v>7011053</v>
+        <v>7010698</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132341105</v>
+        <v>132341054</v>
       </c>
       <c r="B43" t="n">
-        <v>92197</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5012,21 +5012,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437027</v>
+        <v>437637</v>
       </c>
       <c r="R43" t="n">
-        <v>7010698</v>
+        <v>7011098</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5072,6 +5072,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5098,10 +5103,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132341054</v>
+        <v>132340940</v>
       </c>
       <c r="B44" t="n">
-        <v>57949</v>
+        <v>91908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5109,21 +5114,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5133,10 +5138,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437637</v>
+        <v>437350</v>
       </c>
       <c r="R44" t="n">
-        <v>7011098</v>
+        <v>7010948</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5169,11 +5174,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5203,7 +5203,7 @@
         <v>132341095</v>
       </c>
       <c r="B45" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>132341057</v>
       </c>
       <c r="B46" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>132340949</v>
       </c>
       <c r="B47" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>132341055</v>
       </c>
       <c r="B48" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>132341127</v>
       </c>
       <c r="B49" t="n">
-        <v>91894</v>
+        <v>91904</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>132341125</v>
       </c>
       <c r="B50" t="n">
-        <v>91894</v>
+        <v>91904</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>132341108</v>
       </c>
       <c r="B51" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>132341027</v>
       </c>
       <c r="B52" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>132341062</v>
       </c>
       <c r="B53" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>132341094</v>
       </c>
       <c r="B54" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>132341119</v>
       </c>
       <c r="B55" t="n">
-        <v>57128</v>
+        <v>57132</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>132341103</v>
       </c>
       <c r="B56" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>132340935</v>
       </c>
       <c r="B57" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>132341131</v>
       </c>
       <c r="B58" t="n">
-        <v>91894</v>
+        <v>91904</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>132341109</v>
       </c>
       <c r="B59" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6697,10 +6697,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341136</v>
+        <v>132341112</v>
       </c>
       <c r="B60" t="n">
-        <v>79319</v>
+        <v>80432</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6708,21 +6708,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437640</v>
+        <v>437518</v>
       </c>
       <c r="R60" t="n">
-        <v>7010681</v>
+        <v>7010858</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6762,17 +6762,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6799,10 +6794,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132341112</v>
+        <v>132341136</v>
       </c>
       <c r="B61" t="n">
-        <v>80424</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6810,21 +6805,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6834,10 +6829,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437518</v>
+        <v>437640</v>
       </c>
       <c r="R61" t="n">
-        <v>7010858</v>
+        <v>7010681</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6864,12 +6859,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6896,10 +6896,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132341051</v>
+        <v>132341052</v>
       </c>
       <c r="B62" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6931,10 +6931,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437746</v>
+        <v>437740</v>
       </c>
       <c r="R62" t="n">
-        <v>7010946</v>
+        <v>7011055</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6998,10 +6998,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132341031</v>
+        <v>132341037</v>
       </c>
       <c r="B63" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>438101</v>
+        <v>437926</v>
       </c>
       <c r="R63" t="n">
-        <v>7010919</v>
+        <v>7011061</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7103,7 +7103,7 @@
         <v>132341056</v>
       </c>
       <c r="B64" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7202,10 +7202,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132341052</v>
+        <v>132341066</v>
       </c>
       <c r="B65" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>437740</v>
+        <v>436968</v>
       </c>
       <c r="R65" t="n">
-        <v>7011055</v>
+        <v>7010599</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7304,10 +7304,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132341032</v>
+        <v>132341031</v>
       </c>
       <c r="B66" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>438064</v>
+        <v>438101</v>
       </c>
       <c r="R66" t="n">
-        <v>7010908</v>
+        <v>7010919</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7406,10 +7406,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132341037</v>
+        <v>132341034</v>
       </c>
       <c r="B67" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437926</v>
+        <v>437908</v>
       </c>
       <c r="R67" t="n">
-        <v>7011061</v>
+        <v>7011073</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7508,10 +7508,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132341066</v>
+        <v>132341032</v>
       </c>
       <c r="B68" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7543,10 +7543,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436968</v>
+        <v>438064</v>
       </c>
       <c r="R68" t="n">
-        <v>7010599</v>
+        <v>7010908</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7610,10 +7610,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132341034</v>
+        <v>132341051</v>
       </c>
       <c r="B69" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437908</v>
+        <v>437746</v>
       </c>
       <c r="R69" t="n">
-        <v>7011073</v>
+        <v>7010946</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7715,7 +7715,7 @@
         <v>132340946</v>
       </c>
       <c r="B70" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>132341102</v>
       </c>
       <c r="B71" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>132340944</v>
       </c>
       <c r="B72" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>132341111</v>
       </c>
       <c r="B73" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>132341096</v>
       </c>
       <c r="B74" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>132341053</v>
       </c>
       <c r="B75" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341106</v>
+        <v>132341059</v>
       </c>
       <c r="B76" t="n">
-        <v>92197</v>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8315,21 +8315,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437009</v>
+        <v>437567</v>
       </c>
       <c r="R76" t="n">
-        <v>7010701</v>
+        <v>7010953</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8375,6 +8375,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8401,10 +8406,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341059</v>
+        <v>132341106</v>
       </c>
       <c r="B77" t="n">
-        <v>57949</v>
+        <v>92207</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8412,21 +8417,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8436,10 +8441,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437567</v>
+        <v>437009</v>
       </c>
       <c r="R77" t="n">
-        <v>7010953</v>
+        <v>7010701</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8472,11 +8477,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8503,32 +8503,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132341115</v>
+        <v>132341043</v>
       </c>
       <c r="B78" t="n">
-        <v>99106</v>
+        <v>57953</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437101</v>
+        <v>437872</v>
       </c>
       <c r="R78" t="n">
-        <v>7010646</v>
+        <v>7010932</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8574,6 +8574,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8603,7 +8608,7 @@
         <v>132340942</v>
       </c>
       <c r="B79" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8697,10 +8702,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132341063</v>
+        <v>132341065</v>
       </c>
       <c r="B80" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8732,10 +8737,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437505</v>
+        <v>437074</v>
       </c>
       <c r="R80" t="n">
-        <v>7010836</v>
+        <v>7010580</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8772,7 +8777,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8799,10 +8804,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132341045</v>
+        <v>132341030</v>
       </c>
       <c r="B81" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8834,10 +8839,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437901</v>
+        <v>438101</v>
       </c>
       <c r="R81" t="n">
-        <v>7010813</v>
+        <v>7010924</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8874,7 +8879,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8901,10 +8906,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132341065</v>
+        <v>132341063</v>
       </c>
       <c r="B82" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8936,10 +8941,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437074</v>
+        <v>437505</v>
       </c>
       <c r="R82" t="n">
-        <v>7010580</v>
+        <v>7010836</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8976,7 +8981,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9003,10 +9008,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341043</v>
+        <v>132341045</v>
       </c>
       <c r="B83" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9038,10 +9043,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437872</v>
+        <v>437901</v>
       </c>
       <c r="R83" t="n">
-        <v>7010932</v>
+        <v>7010813</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9105,32 +9110,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132341030</v>
+        <v>132341115</v>
       </c>
       <c r="B84" t="n">
-        <v>57949</v>
+        <v>99116</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9140,10 +9145,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438101</v>
+        <v>437101</v>
       </c>
       <c r="R84" t="n">
-        <v>7010924</v>
+        <v>7010646</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9176,11 +9181,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9207,10 +9207,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132341114</v>
+        <v>132341061</v>
       </c>
       <c r="B85" t="n">
-        <v>80424</v>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9218,21 +9218,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437012</v>
+        <v>437535</v>
       </c>
       <c r="R85" t="n">
-        <v>7010575</v>
+        <v>7010929</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9278,6 +9278,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9307,7 +9312,7 @@
         <v>132341046</v>
       </c>
       <c r="B86" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9406,10 +9411,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132341061</v>
+        <v>132341114</v>
       </c>
       <c r="B87" t="n">
-        <v>57949</v>
+        <v>80432</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9417,21 +9422,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9441,10 +9446,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437535</v>
+        <v>437012</v>
       </c>
       <c r="R87" t="n">
-        <v>7010929</v>
+        <v>7010575</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9477,11 +9482,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9508,10 +9508,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132340948</v>
+        <v>132340939</v>
       </c>
       <c r="B88" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9543,10 +9543,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437159</v>
+        <v>437481</v>
       </c>
       <c r="R88" t="n">
-        <v>7010541</v>
+        <v>7010828</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9605,10 +9605,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132340943</v>
+        <v>132341101</v>
       </c>
       <c r="B89" t="n">
-        <v>91898</v>
+        <v>92207</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9616,21 +9616,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9640,10 +9640,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437280</v>
+        <v>437486</v>
       </c>
       <c r="R89" t="n">
-        <v>7010923</v>
+        <v>7010537</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9702,10 +9702,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132340938</v>
+        <v>132341097</v>
       </c>
       <c r="B90" t="n">
-        <v>91898</v>
+        <v>80433</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9713,21 +9713,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437465</v>
+        <v>437011</v>
       </c>
       <c r="R90" t="n">
-        <v>7010897</v>
+        <v>7010575</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9799,10 +9799,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132340947</v>
+        <v>132341028</v>
       </c>
       <c r="B91" t="n">
-        <v>91898</v>
+        <v>57953</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9810,21 +9810,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9834,10 +9834,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437023</v>
+        <v>437583</v>
       </c>
       <c r="R91" t="n">
-        <v>7010700</v>
+        <v>7010708</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9864,12 +9864,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9896,10 +9901,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132340939</v>
+        <v>132340948</v>
       </c>
       <c r="B92" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9931,10 +9936,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437481</v>
+        <v>437159</v>
       </c>
       <c r="R92" t="n">
-        <v>7010828</v>
+        <v>7010541</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9993,10 +9998,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132341101</v>
+        <v>132340943</v>
       </c>
       <c r="B93" t="n">
-        <v>92197</v>
+        <v>91908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10004,21 +10009,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10028,10 +10033,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>437486</v>
+        <v>437280</v>
       </c>
       <c r="R93" t="n">
-        <v>7010537</v>
+        <v>7010923</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10058,12 +10063,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10090,10 +10095,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132341097</v>
+        <v>132340938</v>
       </c>
       <c r="B94" t="n">
-        <v>80425</v>
+        <v>91908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10101,21 +10106,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10125,10 +10130,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437011</v>
+        <v>437465</v>
       </c>
       <c r="R94" t="n">
-        <v>7010575</v>
+        <v>7010897</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10187,10 +10192,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132341028</v>
+        <v>132340947</v>
       </c>
       <c r="B95" t="n">
-        <v>57949</v>
+        <v>91908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10198,21 +10203,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10222,10 +10227,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>437583</v>
+        <v>437023</v>
       </c>
       <c r="R95" t="n">
-        <v>7010708</v>
+        <v>7010700</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10252,17 +10257,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10289,57 +10289,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132341116</v>
+        <v>132341107</v>
       </c>
       <c r="B96" t="n">
-        <v>99106</v>
+        <v>92207</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>437089</v>
+        <v>436990</v>
       </c>
       <c r="R96" t="n">
-        <v>7010576</v>
+        <v>7010703</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10374,18 +10362,12 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Rikligt, över 200</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10404,10 +10386,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132341107</v>
+        <v>132341104</v>
       </c>
       <c r="B97" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10439,10 +10421,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436990</v>
+        <v>437280</v>
       </c>
       <c r="R97" t="n">
-        <v>7010703</v>
+        <v>7010923</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10501,45 +10483,57 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132341104</v>
+        <v>132341116</v>
       </c>
       <c r="B98" t="n">
-        <v>92197</v>
+        <v>99116</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437280</v>
+        <v>437089</v>
       </c>
       <c r="R98" t="n">
-        <v>7010923</v>
+        <v>7010576</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10574,12 +10568,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rikligt, över 200</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -2307,7 +2307,7 @@
         <v>132341110</v>
       </c>
       <c r="B16" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>132341129</v>
       </c>
       <c r="B17" t="n">
-        <v>91904</v>
+        <v>91905</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2702,10 +2702,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132341058</v>
+        <v>132341126</v>
       </c>
       <c r="B20" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2713,21 +2713,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437635</v>
+        <v>437525</v>
       </c>
       <c r="R20" t="n">
-        <v>7011011</v>
+        <v>7010475</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2773,11 +2773,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2906,10 +2901,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132341126</v>
+        <v>132341058</v>
       </c>
       <c r="B22" t="n">
-        <v>91904</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2917,21 +2912,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2941,10 +2936,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437525</v>
+        <v>437635</v>
       </c>
       <c r="R22" t="n">
-        <v>7010475</v>
+        <v>7011011</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2977,6 +2972,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3003,7 +3003,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132341060</v>
+        <v>132341064</v>
       </c>
       <c r="B23" t="n">
         <v>57953</v>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437611</v>
+        <v>437442</v>
       </c>
       <c r="R23" t="n">
-        <v>7010882</v>
+        <v>7010869</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3105,7 +3105,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132341064</v>
+        <v>132341060</v>
       </c>
       <c r="B24" t="n">
         <v>57953</v>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437442</v>
+        <v>437611</v>
       </c>
       <c r="R24" t="n">
-        <v>7010869</v>
+        <v>7010882</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3207,45 +3207,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132340941</v>
+        <v>132341118</v>
       </c>
       <c r="B25" t="n">
-        <v>91908</v>
+        <v>99117</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437348</v>
+        <v>437059</v>
       </c>
       <c r="R25" t="n">
-        <v>7010989</v>
+        <v>7010572</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3280,12 +3292,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt över 200</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3304,32 +3322,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132341113</v>
+        <v>132341117</v>
       </c>
       <c r="B26" t="n">
-        <v>80432</v>
+        <v>99117</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3339,10 +3357,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437053</v>
+        <v>437071</v>
       </c>
       <c r="R26" t="n">
-        <v>7010706</v>
+        <v>7010578</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3401,32 +3419,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132341117</v>
+        <v>132341113</v>
       </c>
       <c r="B27" t="n">
-        <v>99116</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3436,10 +3454,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437071</v>
+        <v>437053</v>
       </c>
       <c r="R27" t="n">
-        <v>7010578</v>
+        <v>7010706</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3498,57 +3516,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132341118</v>
+        <v>132340941</v>
       </c>
       <c r="B28" t="n">
-        <v>99116</v>
+        <v>91909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437059</v>
+        <v>437348</v>
       </c>
       <c r="R28" t="n">
-        <v>7010572</v>
+        <v>7010989</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3583,18 +3589,12 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt över 200</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3613,10 +3613,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132341029</v>
+        <v>132341132</v>
       </c>
       <c r="B29" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,21 +3624,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437342</v>
+        <v>437384</v>
       </c>
       <c r="R29" t="n">
-        <v>7010780</v>
+        <v>7010958</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,17 +3678,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3715,10 +3710,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132341132</v>
+        <v>132341029</v>
       </c>
       <c r="B30" t="n">
-        <v>91904</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,21 +3721,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3750,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437384</v>
+        <v>437342</v>
       </c>
       <c r="R30" t="n">
-        <v>7010958</v>
+        <v>7010780</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3780,12 +3775,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3812,7 +3812,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132341041</v>
+        <v>132341040</v>
       </c>
       <c r="B31" t="n">
         <v>57953</v>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437973</v>
+        <v>438088</v>
       </c>
       <c r="R31" t="n">
-        <v>7010845</v>
+        <v>7010817</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3914,7 +3914,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132341040</v>
+        <v>132341049</v>
       </c>
       <c r="B32" t="n">
         <v>57953</v>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438088</v>
+        <v>437804</v>
       </c>
       <c r="R32" t="n">
-        <v>7010817</v>
+        <v>7010729</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4016,7 +4016,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132341049</v>
+        <v>132341041</v>
       </c>
       <c r="B33" t="n">
         <v>57953</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437804</v>
+        <v>437973</v>
       </c>
       <c r="R33" t="n">
-        <v>7010729</v>
+        <v>7010845</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4118,10 +4118,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132341047</v>
+        <v>132341138</v>
       </c>
       <c r="B34" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4129,21 +4129,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437918</v>
+        <v>437710</v>
       </c>
       <c r="R34" t="n">
-        <v>7010791</v>
+        <v>7010507</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4220,10 +4220,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132341138</v>
+        <v>132341047</v>
       </c>
       <c r="B35" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437710</v>
+        <v>437918</v>
       </c>
       <c r="R35" t="n">
-        <v>7010507</v>
+        <v>7010791</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4325,7 +4325,7 @@
         <v>132341135</v>
       </c>
       <c r="B36" t="n">
-        <v>91922</v>
+        <v>91923</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>132340936</v>
       </c>
       <c r="B37" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>132341140</v>
       </c>
       <c r="B38" t="n">
-        <v>92604</v>
+        <v>92605</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>132341100</v>
       </c>
       <c r="B39" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>132341128</v>
       </c>
       <c r="B40" t="n">
-        <v>91904</v>
+        <v>91905</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4807,10 +4807,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132341134</v>
+        <v>132340940</v>
       </c>
       <c r="B41" t="n">
-        <v>91922</v>
+        <v>91909</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4818,21 +4818,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437611</v>
+        <v>437350</v>
       </c>
       <c r="R41" t="n">
-        <v>7011053</v>
+        <v>7010948</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4904,10 +4904,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132341105</v>
+        <v>132341134</v>
       </c>
       <c r="B42" t="n">
-        <v>92207</v>
+        <v>91923</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4915,21 +4915,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437027</v>
+        <v>437611</v>
       </c>
       <c r="R42" t="n">
-        <v>7010698</v>
+        <v>7011053</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132341054</v>
+        <v>132341105</v>
       </c>
       <c r="B43" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5012,21 +5012,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437637</v>
+        <v>437027</v>
       </c>
       <c r="R43" t="n">
-        <v>7011098</v>
+        <v>7010698</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5072,11 +5072,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5103,10 +5098,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132340940</v>
+        <v>132341054</v>
       </c>
       <c r="B44" t="n">
-        <v>91908</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5114,21 +5109,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5138,10 +5133,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437350</v>
+        <v>437637</v>
       </c>
       <c r="R44" t="n">
-        <v>7010948</v>
+        <v>7011098</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5174,6 +5169,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5200,10 +5200,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132341095</v>
+        <v>132341057</v>
       </c>
       <c r="B45" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5211,16 +5211,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437922</v>
+        <v>437606</v>
       </c>
       <c r="R45" t="n">
         <v>7011053</v>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5302,10 +5302,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132341057</v>
+        <v>132341095</v>
       </c>
       <c r="B46" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5313,16 +5313,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437606</v>
+        <v>437922</v>
       </c>
       <c r="R46" t="n">
         <v>7011053</v>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5407,7 +5407,7 @@
         <v>132340949</v>
       </c>
       <c r="B47" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>132341127</v>
       </c>
       <c r="B49" t="n">
-        <v>91904</v>
+        <v>91905</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>132341125</v>
       </c>
       <c r="B50" t="n">
-        <v>91904</v>
+        <v>91905</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>132341108</v>
       </c>
       <c r="B51" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132341103</v>
+        <v>132341051</v>
       </c>
       <c r="B56" t="n">
-        <v>92207</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6320,21 +6320,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437283</v>
+        <v>437746</v>
       </c>
       <c r="R56" t="n">
-        <v>7010896</v>
+        <v>7010946</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6380,6 +6380,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6406,10 +6411,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132340935</v>
+        <v>132341031</v>
       </c>
       <c r="B57" t="n">
-        <v>91908</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6417,21 +6422,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6441,10 +6446,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437488</v>
+        <v>438101</v>
       </c>
       <c r="R57" t="n">
-        <v>7010535</v>
+        <v>7010919</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6471,12 +6476,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6503,10 +6513,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132341131</v>
+        <v>132341056</v>
       </c>
       <c r="B58" t="n">
-        <v>91904</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6514,21 +6524,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6538,10 +6548,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437674</v>
+        <v>437578</v>
       </c>
       <c r="R58" t="n">
-        <v>7011000</v>
+        <v>7011118</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6574,6 +6584,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6600,10 +6615,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132341109</v>
+        <v>132341052</v>
       </c>
       <c r="B59" t="n">
-        <v>92207</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6611,21 +6626,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6635,10 +6650,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437194</v>
+        <v>437740</v>
       </c>
       <c r="R59" t="n">
-        <v>7010597</v>
+        <v>7011055</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6671,6 +6686,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6697,10 +6717,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341112</v>
+        <v>132341032</v>
       </c>
       <c r="B60" t="n">
-        <v>80432</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6708,21 +6728,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6732,10 +6752,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437518</v>
+        <v>438064</v>
       </c>
       <c r="R60" t="n">
-        <v>7010858</v>
+        <v>7010908</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6768,6 +6788,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6794,10 +6819,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132341136</v>
+        <v>132341037</v>
       </c>
       <c r="B61" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6805,21 +6830,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6829,10 +6854,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437640</v>
+        <v>437926</v>
       </c>
       <c r="R61" t="n">
-        <v>7010681</v>
+        <v>7011061</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6859,17 +6884,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6896,7 +6921,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132341052</v>
+        <v>132341066</v>
       </c>
       <c r="B62" t="n">
         <v>57953</v>
@@ -6931,10 +6956,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437740</v>
+        <v>436968</v>
       </c>
       <c r="R62" t="n">
-        <v>7011055</v>
+        <v>7010599</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6998,7 +7023,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132341037</v>
+        <v>132341034</v>
       </c>
       <c r="B63" t="n">
         <v>57953</v>
@@ -7033,10 +7058,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437926</v>
+        <v>437908</v>
       </c>
       <c r="R63" t="n">
-        <v>7011061</v>
+        <v>7011073</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7100,10 +7125,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132341056</v>
+        <v>132341112</v>
       </c>
       <c r="B64" t="n">
-        <v>57953</v>
+        <v>80432</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7111,21 +7136,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7135,10 +7160,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>437578</v>
+        <v>437518</v>
       </c>
       <c r="R64" t="n">
-        <v>7011118</v>
+        <v>7010858</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7171,11 +7196,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7202,10 +7222,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132341066</v>
+        <v>132341136</v>
       </c>
       <c r="B65" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7213,21 +7233,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7237,10 +7257,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436968</v>
+        <v>437640</v>
       </c>
       <c r="R65" t="n">
-        <v>7010599</v>
+        <v>7010681</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7267,17 +7287,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7304,10 +7324,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132341031</v>
+        <v>132341103</v>
       </c>
       <c r="B66" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7315,21 +7335,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7339,10 +7359,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>438101</v>
+        <v>437283</v>
       </c>
       <c r="R66" t="n">
-        <v>7010919</v>
+        <v>7010896</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7375,11 +7395,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7406,10 +7421,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132341034</v>
+        <v>132340935</v>
       </c>
       <c r="B67" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7417,21 +7432,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7441,10 +7456,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437908</v>
+        <v>437488</v>
       </c>
       <c r="R67" t="n">
-        <v>7011073</v>
+        <v>7010535</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7471,17 +7486,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7508,10 +7518,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132341032</v>
+        <v>132341131</v>
       </c>
       <c r="B68" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7519,21 +7529,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7543,10 +7553,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438064</v>
+        <v>437674</v>
       </c>
       <c r="R68" t="n">
-        <v>7010908</v>
+        <v>7011000</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,11 +7589,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7610,10 +7615,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132341051</v>
+        <v>132341109</v>
       </c>
       <c r="B69" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7621,21 +7626,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7645,10 +7650,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437746</v>
+        <v>437194</v>
       </c>
       <c r="R69" t="n">
-        <v>7010946</v>
+        <v>7010597</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,11 +7686,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7712,10 +7712,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132340946</v>
+        <v>132341111</v>
       </c>
       <c r="B70" t="n">
-        <v>91908</v>
+        <v>80432</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7723,21 +7723,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437124</v>
+        <v>437156</v>
       </c>
       <c r="R70" t="n">
-        <v>7010689</v>
+        <v>7010645</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7777,12 +7777,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7809,10 +7809,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132341102</v>
+        <v>132340946</v>
       </c>
       <c r="B71" t="n">
-        <v>92207</v>
+        <v>91909</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7820,21 +7820,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7844,10 +7844,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437474</v>
+        <v>437124</v>
       </c>
       <c r="R71" t="n">
-        <v>7010882</v>
+        <v>7010689</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7906,10 +7906,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132340944</v>
+        <v>132341102</v>
       </c>
       <c r="B72" t="n">
-        <v>91908</v>
+        <v>92208</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7917,21 +7917,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437304</v>
+        <v>437474</v>
       </c>
       <c r="R72" t="n">
-        <v>7010986</v>
+        <v>7010882</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132341111</v>
+        <v>132340944</v>
       </c>
       <c r="B73" t="n">
-        <v>80432</v>
+        <v>91909</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8014,21 +8014,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437156</v>
+        <v>437304</v>
       </c>
       <c r="R73" t="n">
-        <v>7010645</v>
+        <v>7010986</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8068,12 +8068,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8304,10 +8304,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341059</v>
+        <v>132341106</v>
       </c>
       <c r="B76" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8315,21 +8315,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437567</v>
+        <v>437009</v>
       </c>
       <c r="R76" t="n">
-        <v>7010953</v>
+        <v>7010701</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8375,11 +8375,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8406,10 +8401,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341106</v>
+        <v>132341059</v>
       </c>
       <c r="B77" t="n">
-        <v>92207</v>
+        <v>57953</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8417,21 +8412,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8441,10 +8436,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437009</v>
+        <v>437567</v>
       </c>
       <c r="R77" t="n">
-        <v>7010701</v>
+        <v>7010953</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8477,6 +8472,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8503,10 +8503,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132341043</v>
+        <v>132340942</v>
       </c>
       <c r="B78" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8514,21 +8514,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437872</v>
+        <v>437287</v>
       </c>
       <c r="R78" t="n">
-        <v>7010932</v>
+        <v>7010896</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8574,11 +8574,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8605,32 +8600,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132340942</v>
+        <v>132341115</v>
       </c>
       <c r="B79" t="n">
-        <v>91908</v>
+        <v>99117</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8640,10 +8635,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437287</v>
+        <v>437101</v>
       </c>
       <c r="R79" t="n">
-        <v>7010896</v>
+        <v>7010646</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8702,7 +8697,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132341065</v>
+        <v>132341063</v>
       </c>
       <c r="B80" t="n">
         <v>57953</v>
@@ -8737,10 +8732,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437074</v>
+        <v>437505</v>
       </c>
       <c r="R80" t="n">
-        <v>7010580</v>
+        <v>7010836</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8777,7 +8772,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8804,7 +8799,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132341030</v>
+        <v>132341045</v>
       </c>
       <c r="B81" t="n">
         <v>57953</v>
@@ -8839,10 +8834,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438101</v>
+        <v>437901</v>
       </c>
       <c r="R81" t="n">
-        <v>7010924</v>
+        <v>7010813</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8879,7 +8874,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8906,7 +8901,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132341063</v>
+        <v>132341065</v>
       </c>
       <c r="B82" t="n">
         <v>57953</v>
@@ -8941,10 +8936,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437505</v>
+        <v>437074</v>
       </c>
       <c r="R82" t="n">
-        <v>7010836</v>
+        <v>7010580</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8981,7 +8976,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9008,7 +9003,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341045</v>
+        <v>132341043</v>
       </c>
       <c r="B83" t="n">
         <v>57953</v>
@@ -9043,10 +9038,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437901</v>
+        <v>437872</v>
       </c>
       <c r="R83" t="n">
-        <v>7010813</v>
+        <v>7010932</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9110,32 +9105,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132341115</v>
+        <v>132341030</v>
       </c>
       <c r="B84" t="n">
-        <v>99116</v>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9145,10 +9140,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437101</v>
+        <v>438101</v>
       </c>
       <c r="R84" t="n">
-        <v>7010646</v>
+        <v>7010924</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9181,6 +9176,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9207,10 +9207,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132341061</v>
+        <v>132341114</v>
       </c>
       <c r="B85" t="n">
-        <v>57953</v>
+        <v>80432</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9218,21 +9218,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437535</v>
+        <v>437012</v>
       </c>
       <c r="R85" t="n">
-        <v>7010929</v>
+        <v>7010575</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9278,11 +9278,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9411,10 +9406,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132341114</v>
+        <v>132341061</v>
       </c>
       <c r="B87" t="n">
-        <v>80432</v>
+        <v>57953</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9422,21 +9417,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9446,10 +9441,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437012</v>
+        <v>437535</v>
       </c>
       <c r="R87" t="n">
-        <v>7010575</v>
+        <v>7010929</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9482,6 +9477,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9508,10 +9508,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132340939</v>
+        <v>132341028</v>
       </c>
       <c r="B88" t="n">
-        <v>91908</v>
+        <v>57953</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9519,21 +9519,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9543,10 +9543,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437481</v>
+        <v>437583</v>
       </c>
       <c r="R88" t="n">
-        <v>7010828</v>
+        <v>7010708</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9573,12 +9573,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9605,10 +9610,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132341101</v>
+        <v>132340948</v>
       </c>
       <c r="B89" t="n">
-        <v>92207</v>
+        <v>91909</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9616,21 +9621,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9640,10 +9645,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437486</v>
+        <v>437159</v>
       </c>
       <c r="R89" t="n">
-        <v>7010537</v>
+        <v>7010541</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9670,12 +9675,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9702,10 +9707,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132341097</v>
+        <v>132340943</v>
       </c>
       <c r="B90" t="n">
-        <v>80433</v>
+        <v>91909</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9713,21 +9718,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9737,10 +9742,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437011</v>
+        <v>437280</v>
       </c>
       <c r="R90" t="n">
-        <v>7010575</v>
+        <v>7010923</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9799,10 +9804,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132341028</v>
+        <v>132340938</v>
       </c>
       <c r="B91" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9810,21 +9815,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9834,10 +9839,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437583</v>
+        <v>437465</v>
       </c>
       <c r="R91" t="n">
-        <v>7010708</v>
+        <v>7010897</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9864,17 +9869,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9901,10 +9901,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132340948</v>
+        <v>132340947</v>
       </c>
       <c r="B92" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9936,10 +9936,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437159</v>
+        <v>437023</v>
       </c>
       <c r="R92" t="n">
-        <v>7010541</v>
+        <v>7010700</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9998,10 +9998,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132340943</v>
+        <v>132340939</v>
       </c>
       <c r="B93" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10033,10 +10033,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>437280</v>
+        <v>437481</v>
       </c>
       <c r="R93" t="n">
-        <v>7010923</v>
+        <v>7010828</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10095,10 +10095,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132340938</v>
+        <v>132341101</v>
       </c>
       <c r="B94" t="n">
-        <v>91908</v>
+        <v>92208</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10106,21 +10106,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10130,10 +10130,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437465</v>
+        <v>437486</v>
       </c>
       <c r="R94" t="n">
-        <v>7010897</v>
+        <v>7010537</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10160,12 +10160,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10192,10 +10192,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132340947</v>
+        <v>132341097</v>
       </c>
       <c r="B95" t="n">
-        <v>91908</v>
+        <v>80433</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10203,21 +10203,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10227,10 +10227,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>437023</v>
+        <v>437011</v>
       </c>
       <c r="R95" t="n">
-        <v>7010700</v>
+        <v>7010575</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10292,7 +10292,7 @@
         <v>132341107</v>
       </c>
       <c r="B96" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>132341104</v>
       </c>
       <c r="B97" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>132341116</v>
       </c>
       <c r="B98" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -3003,10 +3003,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132341064</v>
+        <v>132340941</v>
       </c>
       <c r="B23" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437442</v>
+        <v>437348</v>
       </c>
       <c r="R23" t="n">
-        <v>7010869</v>
+        <v>7010989</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,11 +3074,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3105,10 +3100,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132341060</v>
+        <v>132341113</v>
       </c>
       <c r="B24" t="n">
-        <v>57953</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3116,21 +3111,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3140,10 +3135,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437611</v>
+        <v>437053</v>
       </c>
       <c r="R24" t="n">
-        <v>7010882</v>
+        <v>7010706</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3176,11 +3171,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3207,57 +3197,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132341118</v>
+        <v>132341060</v>
       </c>
       <c r="B25" t="n">
-        <v>99117</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437059</v>
+        <v>437611</v>
       </c>
       <c r="R25" t="n">
-        <v>7010572</v>
+        <v>7010882</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3294,7 +3272,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt över 200</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3303,7 +3281,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3322,32 +3299,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132341117</v>
+        <v>132341064</v>
       </c>
       <c r="B26" t="n">
-        <v>99117</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3357,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437071</v>
+        <v>437442</v>
       </c>
       <c r="R26" t="n">
-        <v>7010578</v>
+        <v>7010869</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3393,6 +3370,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3419,32 +3401,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132341113</v>
+        <v>132341117</v>
       </c>
       <c r="B27" t="n">
-        <v>80432</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3454,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437053</v>
+        <v>437071</v>
       </c>
       <c r="R27" t="n">
-        <v>7010706</v>
+        <v>7010578</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,45 +3498,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132340941</v>
+        <v>132341118</v>
       </c>
       <c r="B28" t="n">
-        <v>91909</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437348</v>
+        <v>437059</v>
       </c>
       <c r="R28" t="n">
-        <v>7010989</v>
+        <v>7010572</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,12 +3583,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt över 200</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3710,7 +3710,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132341029</v>
+        <v>132341041</v>
       </c>
       <c r="B30" t="n">
         <v>57953</v>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437342</v>
+        <v>437973</v>
       </c>
       <c r="R30" t="n">
-        <v>7010780</v>
+        <v>7010845</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3775,12 +3775,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4016,7 +4016,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132341041</v>
+        <v>132341029</v>
       </c>
       <c r="B33" t="n">
         <v>57953</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437973</v>
+        <v>437342</v>
       </c>
       <c r="R33" t="n">
-        <v>7010845</v>
+        <v>7010780</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4081,12 +4081,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4118,10 +4118,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132341138</v>
+        <v>132341047</v>
       </c>
       <c r="B34" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4129,21 +4129,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437710</v>
+        <v>437918</v>
       </c>
       <c r="R34" t="n">
-        <v>7010507</v>
+        <v>7010791</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4220,10 +4220,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132341047</v>
+        <v>132341138</v>
       </c>
       <c r="B35" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437918</v>
+        <v>437710</v>
       </c>
       <c r="R35" t="n">
-        <v>7010791</v>
+        <v>7010507</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4807,10 +4807,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132340940</v>
+        <v>132341054</v>
       </c>
       <c r="B41" t="n">
-        <v>91909</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4818,21 +4818,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437350</v>
+        <v>437637</v>
       </c>
       <c r="R41" t="n">
-        <v>7010948</v>
+        <v>7011098</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4878,6 +4878,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4904,10 +4909,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132341134</v>
+        <v>132340940</v>
       </c>
       <c r="B42" t="n">
-        <v>91923</v>
+        <v>91909</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4915,21 +4920,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4939,10 +4944,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437611</v>
+        <v>437350</v>
       </c>
       <c r="R42" t="n">
-        <v>7011053</v>
+        <v>7010948</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5001,10 +5006,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132341105</v>
+        <v>132341134</v>
       </c>
       <c r="B43" t="n">
-        <v>92208</v>
+        <v>91923</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5012,21 +5017,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5036,10 +5041,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437027</v>
+        <v>437611</v>
       </c>
       <c r="R43" t="n">
-        <v>7010698</v>
+        <v>7011053</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5098,10 +5103,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132341054</v>
+        <v>132341105</v>
       </c>
       <c r="B44" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5109,21 +5114,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5133,10 +5138,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437637</v>
+        <v>437027</v>
       </c>
       <c r="R44" t="n">
-        <v>7011098</v>
+        <v>7010698</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5169,11 +5174,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5200,10 +5200,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132341057</v>
+        <v>132341095</v>
       </c>
       <c r="B45" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5211,16 +5211,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437606</v>
+        <v>437922</v>
       </c>
       <c r="R45" t="n">
         <v>7011053</v>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5302,10 +5302,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132341095</v>
+        <v>132341057</v>
       </c>
       <c r="B46" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5313,16 +5313,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437922</v>
+        <v>437606</v>
       </c>
       <c r="R46" t="n">
         <v>7011053</v>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5404,10 +5404,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132340949</v>
+        <v>132341055</v>
       </c>
       <c r="B47" t="n">
-        <v>91909</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5415,21 +5415,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437092</v>
+        <v>437603</v>
       </c>
       <c r="R47" t="n">
-        <v>7010575</v>
+        <v>7011097</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5475,6 +5475,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5501,10 +5506,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132341055</v>
+        <v>132340949</v>
       </c>
       <c r="B48" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5512,21 +5517,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5536,10 +5541,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437603</v>
+        <v>437092</v>
       </c>
       <c r="R48" t="n">
-        <v>7011097</v>
+        <v>7010575</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5572,11 +5577,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5797,10 +5797,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132341108</v>
+        <v>132341027</v>
       </c>
       <c r="B51" t="n">
-        <v>92208</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5808,21 +5808,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437099</v>
+        <v>437678</v>
       </c>
       <c r="R51" t="n">
-        <v>7010647</v>
+        <v>7010630</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5862,12 +5862,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5894,7 +5899,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132341027</v>
+        <v>132341062</v>
       </c>
       <c r="B52" t="n">
         <v>57953</v>
@@ -5929,10 +5934,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437678</v>
+        <v>437538</v>
       </c>
       <c r="R52" t="n">
-        <v>7010630</v>
+        <v>7010940</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5959,12 +5964,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -5996,10 +6001,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132341062</v>
+        <v>132341108</v>
       </c>
       <c r="B53" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6007,21 +6012,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6031,10 +6036,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>437538</v>
+        <v>437099</v>
       </c>
       <c r="R53" t="n">
-        <v>7010940</v>
+        <v>7010647</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6067,11 +6072,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6098,10 +6098,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132341094</v>
+        <v>132341119</v>
       </c>
       <c r="B54" t="n">
-        <v>57950</v>
+        <v>57132</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6109,16 +6109,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6126,17 +6126,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>438128</v>
+        <v>437582</v>
       </c>
       <c r="R54" t="n">
-        <v>7010852</v>
+        <v>7010573</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6163,17 +6175,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6200,10 +6207,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132341119</v>
+        <v>132341094</v>
       </c>
       <c r="B55" t="n">
-        <v>57132</v>
+        <v>57950</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6211,16 +6218,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6228,29 +6235,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437582</v>
+        <v>438128</v>
       </c>
       <c r="R55" t="n">
-        <v>7010573</v>
+        <v>7010852</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6277,12 +6272,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6309,10 +6309,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132341051</v>
+        <v>132341112</v>
       </c>
       <c r="B56" t="n">
-        <v>57953</v>
+        <v>80432</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6320,21 +6320,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437746</v>
+        <v>437518</v>
       </c>
       <c r="R56" t="n">
-        <v>7010946</v>
+        <v>7010858</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6380,11 +6380,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6411,10 +6406,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132341031</v>
+        <v>132341136</v>
       </c>
       <c r="B57" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6422,21 +6417,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6446,10 +6441,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>438101</v>
+        <v>437640</v>
       </c>
       <c r="R57" t="n">
-        <v>7010919</v>
+        <v>7010681</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6476,17 +6471,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6513,10 +6508,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132341056</v>
+        <v>132341103</v>
       </c>
       <c r="B58" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6524,21 +6519,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6548,10 +6543,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437578</v>
+        <v>437283</v>
       </c>
       <c r="R58" t="n">
-        <v>7011118</v>
+        <v>7010896</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6584,11 +6579,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6615,10 +6605,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132341052</v>
+        <v>132340935</v>
       </c>
       <c r="B59" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6626,21 +6616,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6650,10 +6640,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437740</v>
+        <v>437488</v>
       </c>
       <c r="R59" t="n">
-        <v>7011055</v>
+        <v>7010535</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6680,17 +6670,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6717,10 +6702,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341032</v>
+        <v>132341131</v>
       </c>
       <c r="B60" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6728,21 +6713,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6752,10 +6737,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>438064</v>
+        <v>437674</v>
       </c>
       <c r="R60" t="n">
-        <v>7010908</v>
+        <v>7011000</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6788,11 +6773,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6819,10 +6799,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132341037</v>
+        <v>132341109</v>
       </c>
       <c r="B61" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6830,21 +6810,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6854,10 +6834,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437926</v>
+        <v>437194</v>
       </c>
       <c r="R61" t="n">
-        <v>7011061</v>
+        <v>7010597</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6890,11 +6870,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6921,7 +6896,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132341066</v>
+        <v>132341052</v>
       </c>
       <c r="B62" t="n">
         <v>57953</v>
@@ -6956,10 +6931,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436968</v>
+        <v>437740</v>
       </c>
       <c r="R62" t="n">
-        <v>7010599</v>
+        <v>7011055</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7023,7 +6998,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132341034</v>
+        <v>132341037</v>
       </c>
       <c r="B63" t="n">
         <v>57953</v>
@@ -7058,10 +7033,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437908</v>
+        <v>437926</v>
       </c>
       <c r="R63" t="n">
-        <v>7011073</v>
+        <v>7011061</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7125,10 +7100,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132341112</v>
+        <v>132341056</v>
       </c>
       <c r="B64" t="n">
-        <v>80432</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7136,21 +7111,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7160,10 +7135,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>437518</v>
+        <v>437578</v>
       </c>
       <c r="R64" t="n">
-        <v>7010858</v>
+        <v>7011118</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7196,6 +7171,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7222,10 +7202,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132341136</v>
+        <v>132341032</v>
       </c>
       <c r="B65" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7233,21 +7213,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7257,10 +7237,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>437640</v>
+        <v>438064</v>
       </c>
       <c r="R65" t="n">
-        <v>7010681</v>
+        <v>7010908</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7287,17 +7267,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7324,10 +7304,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132341103</v>
+        <v>132341066</v>
       </c>
       <c r="B66" t="n">
-        <v>92208</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7335,21 +7315,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7359,10 +7339,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>437283</v>
+        <v>436968</v>
       </c>
       <c r="R66" t="n">
-        <v>7010896</v>
+        <v>7010599</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7395,6 +7375,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7421,10 +7406,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132340935</v>
+        <v>132341051</v>
       </c>
       <c r="B67" t="n">
-        <v>91909</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7432,21 +7417,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7456,10 +7441,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437488</v>
+        <v>437746</v>
       </c>
       <c r="R67" t="n">
-        <v>7010535</v>
+        <v>7010946</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7486,12 +7471,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7518,10 +7508,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132341131</v>
+        <v>132341031</v>
       </c>
       <c r="B68" t="n">
-        <v>91905</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7529,21 +7519,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7553,10 +7543,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437674</v>
+        <v>438101</v>
       </c>
       <c r="R68" t="n">
-        <v>7011000</v>
+        <v>7010919</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7589,6 +7579,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7615,10 +7610,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132341109</v>
+        <v>132341034</v>
       </c>
       <c r="B69" t="n">
-        <v>92208</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7626,21 +7621,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7650,10 +7645,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437194</v>
+        <v>437908</v>
       </c>
       <c r="R69" t="n">
-        <v>7010597</v>
+        <v>7011073</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7686,6 +7681,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7712,10 +7712,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132341111</v>
+        <v>132340946</v>
       </c>
       <c r="B70" t="n">
-        <v>80432</v>
+        <v>91909</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7723,21 +7723,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437156</v>
+        <v>437124</v>
       </c>
       <c r="R70" t="n">
-        <v>7010645</v>
+        <v>7010689</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7777,12 +7777,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7809,10 +7809,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132340946</v>
+        <v>132341102</v>
       </c>
       <c r="B71" t="n">
-        <v>91909</v>
+        <v>92208</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7820,21 +7820,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7844,10 +7844,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437124</v>
+        <v>437474</v>
       </c>
       <c r="R71" t="n">
-        <v>7010689</v>
+        <v>7010882</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7906,10 +7906,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132341102</v>
+        <v>132340944</v>
       </c>
       <c r="B72" t="n">
-        <v>92208</v>
+        <v>91909</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7917,21 +7917,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437474</v>
+        <v>437304</v>
       </c>
       <c r="R72" t="n">
-        <v>7010882</v>
+        <v>7010986</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132340944</v>
+        <v>132341111</v>
       </c>
       <c r="B73" t="n">
-        <v>91909</v>
+        <v>80432</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8014,21 +8014,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437304</v>
+        <v>437156</v>
       </c>
       <c r="R73" t="n">
-        <v>7010986</v>
+        <v>7010645</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8068,12 +8068,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8100,10 +8100,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341096</v>
+        <v>132341053</v>
       </c>
       <c r="B74" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8111,16 +8111,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437096</v>
+        <v>437740</v>
       </c>
       <c r="R74" t="n">
-        <v>7010572</v>
+        <v>7011063</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8202,10 +8202,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341053</v>
+        <v>132341096</v>
       </c>
       <c r="B75" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8213,16 +8213,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8237,10 +8237,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437740</v>
+        <v>437096</v>
       </c>
       <c r="R75" t="n">
-        <v>7011063</v>
+        <v>7010572</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8304,10 +8304,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341106</v>
+        <v>132341059</v>
       </c>
       <c r="B76" t="n">
-        <v>92208</v>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8315,21 +8315,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437009</v>
+        <v>437567</v>
       </c>
       <c r="R76" t="n">
-        <v>7010701</v>
+        <v>7010953</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8375,6 +8375,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8401,10 +8406,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341059</v>
+        <v>132341106</v>
       </c>
       <c r="B77" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8412,21 +8417,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8436,10 +8441,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437567</v>
+        <v>437009</v>
       </c>
       <c r="R77" t="n">
-        <v>7010953</v>
+        <v>7010701</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8472,11 +8477,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8600,32 +8600,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132341115</v>
+        <v>132341065</v>
       </c>
       <c r="B79" t="n">
-        <v>99117</v>
+        <v>57953</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8635,10 +8635,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437101</v>
+        <v>437074</v>
       </c>
       <c r="R79" t="n">
-        <v>7010646</v>
+        <v>7010580</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8671,6 +8671,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8697,7 +8702,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132341063</v>
+        <v>132341045</v>
       </c>
       <c r="B80" t="n">
         <v>57953</v>
@@ -8732,10 +8737,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437505</v>
+        <v>437901</v>
       </c>
       <c r="R80" t="n">
-        <v>7010836</v>
+        <v>7010813</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8772,7 +8777,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8799,7 +8804,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132341045</v>
+        <v>132341030</v>
       </c>
       <c r="B81" t="n">
         <v>57953</v>
@@ -8834,10 +8839,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437901</v>
+        <v>438101</v>
       </c>
       <c r="R81" t="n">
-        <v>7010813</v>
+        <v>7010924</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8874,7 +8879,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8901,7 +8906,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132341065</v>
+        <v>132341063</v>
       </c>
       <c r="B82" t="n">
         <v>57953</v>
@@ -8936,10 +8941,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437074</v>
+        <v>437505</v>
       </c>
       <c r="R82" t="n">
-        <v>7010580</v>
+        <v>7010836</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8976,7 +8981,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9105,32 +9110,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132341030</v>
+        <v>132341115</v>
       </c>
       <c r="B84" t="n">
-        <v>57953</v>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9140,10 +9145,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438101</v>
+        <v>437101</v>
       </c>
       <c r="R84" t="n">
-        <v>7010924</v>
+        <v>7010646</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9176,11 +9181,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10289,45 +10289,57 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132341107</v>
+        <v>132341116</v>
       </c>
       <c r="B96" t="n">
-        <v>92208</v>
+        <v>99118</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436990</v>
+        <v>437089</v>
       </c>
       <c r="R96" t="n">
-        <v>7010703</v>
+        <v>7010576</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10362,12 +10374,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Rikligt, över 200</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10386,7 +10404,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132341104</v>
+        <v>132341107</v>
       </c>
       <c r="B97" t="n">
         <v>92208</v>
@@ -10421,10 +10439,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>437280</v>
+        <v>436990</v>
       </c>
       <c r="R97" t="n">
-        <v>7010923</v>
+        <v>7010703</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10483,57 +10501,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132341116</v>
+        <v>132341104</v>
       </c>
       <c r="B98" t="n">
-        <v>99117</v>
+        <v>92208</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437089</v>
+        <v>437280</v>
       </c>
       <c r="R98" t="n">
-        <v>7010576</v>
+        <v>7010923</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10568,18 +10574,12 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Rikligt, över 200</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -5200,10 +5200,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132341095</v>
+        <v>132341057</v>
       </c>
       <c r="B45" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5211,16 +5211,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437922</v>
+        <v>437606</v>
       </c>
       <c r="R45" t="n">
         <v>7011053</v>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5302,10 +5302,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132341057</v>
+        <v>132341095</v>
       </c>
       <c r="B46" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5313,16 +5313,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437606</v>
+        <v>437922</v>
       </c>
       <c r="R46" t="n">
         <v>7011053</v>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5404,10 +5404,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132341055</v>
+        <v>132340949</v>
       </c>
       <c r="B47" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5415,21 +5415,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437603</v>
+        <v>437092</v>
       </c>
       <c r="R47" t="n">
-        <v>7011097</v>
+        <v>7010575</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5475,11 +5475,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5506,10 +5501,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132340949</v>
+        <v>132341055</v>
       </c>
       <c r="B48" t="n">
-        <v>91909</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5517,21 +5512,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5541,10 +5536,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437092</v>
+        <v>437603</v>
       </c>
       <c r="R48" t="n">
-        <v>7010575</v>
+        <v>7011097</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5577,6 +5572,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5797,10 +5797,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132341027</v>
+        <v>132341108</v>
       </c>
       <c r="B51" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5808,21 +5808,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437678</v>
+        <v>437099</v>
       </c>
       <c r="R51" t="n">
-        <v>7010630</v>
+        <v>7010647</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5862,17 +5862,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5899,7 +5894,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132341062</v>
+        <v>132341027</v>
       </c>
       <c r="B52" t="n">
         <v>57953</v>
@@ -5934,10 +5929,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437538</v>
+        <v>437678</v>
       </c>
       <c r="R52" t="n">
-        <v>7010940</v>
+        <v>7010630</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5964,12 +5959,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6001,10 +5996,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132341108</v>
+        <v>132341062</v>
       </c>
       <c r="B53" t="n">
-        <v>92208</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6012,21 +6007,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6036,10 +6031,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>437099</v>
+        <v>437538</v>
       </c>
       <c r="R53" t="n">
-        <v>7010647</v>
+        <v>7010940</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6072,6 +6067,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6098,10 +6098,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132341119</v>
+        <v>132341094</v>
       </c>
       <c r="B54" t="n">
-        <v>57132</v>
+        <v>57950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6109,16 +6109,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6126,29 +6126,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437582</v>
+        <v>438128</v>
       </c>
       <c r="R54" t="n">
-        <v>7010573</v>
+        <v>7010852</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6175,12 +6163,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6207,10 +6200,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132341094</v>
+        <v>132341119</v>
       </c>
       <c r="B55" t="n">
-        <v>57950</v>
+        <v>57132</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6218,16 +6211,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6235,17 +6228,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>438128</v>
+        <v>437582</v>
       </c>
       <c r="R55" t="n">
-        <v>7010852</v>
+        <v>7010573</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6272,17 +6277,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6309,10 +6309,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132341112</v>
+        <v>132341103</v>
       </c>
       <c r="B56" t="n">
-        <v>80432</v>
+        <v>92208</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6320,21 +6320,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437518</v>
+        <v>437283</v>
       </c>
       <c r="R56" t="n">
-        <v>7010858</v>
+        <v>7010896</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132341136</v>
+        <v>132340935</v>
       </c>
       <c r="B57" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6417,21 +6417,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437640</v>
+        <v>437488</v>
       </c>
       <c r="R57" t="n">
-        <v>7010681</v>
+        <v>7010535</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6477,11 +6477,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6508,10 +6503,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132341103</v>
+        <v>132341131</v>
       </c>
       <c r="B58" t="n">
-        <v>92208</v>
+        <v>91905</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6519,21 +6514,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6543,10 +6538,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437283</v>
+        <v>437674</v>
       </c>
       <c r="R58" t="n">
-        <v>7010896</v>
+        <v>7011000</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6605,10 +6600,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132340935</v>
+        <v>132341109</v>
       </c>
       <c r="B59" t="n">
-        <v>91909</v>
+        <v>92208</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6616,21 +6611,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6640,10 +6635,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437488</v>
+        <v>437194</v>
       </c>
       <c r="R59" t="n">
-        <v>7010535</v>
+        <v>7010597</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6670,12 +6665,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6702,10 +6697,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341131</v>
+        <v>132341112</v>
       </c>
       <c r="B60" t="n">
-        <v>91905</v>
+        <v>80432</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6713,21 +6708,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6737,10 +6732,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437674</v>
+        <v>437518</v>
       </c>
       <c r="R60" t="n">
-        <v>7011000</v>
+        <v>7010858</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6799,10 +6794,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132341109</v>
+        <v>132341136</v>
       </c>
       <c r="B61" t="n">
-        <v>92208</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6810,21 +6805,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6834,10 +6829,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437194</v>
+        <v>437640</v>
       </c>
       <c r="R61" t="n">
-        <v>7010597</v>
+        <v>7010681</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6864,12 +6859,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7712,10 +7712,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132340946</v>
+        <v>132341053</v>
       </c>
       <c r="B70" t="n">
-        <v>91909</v>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7723,21 +7723,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437124</v>
+        <v>437740</v>
       </c>
       <c r="R70" t="n">
-        <v>7010689</v>
+        <v>7011063</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7783,6 +7783,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7809,10 +7814,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132341102</v>
+        <v>132341096</v>
       </c>
       <c r="B71" t="n">
-        <v>92208</v>
+        <v>57950</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7820,21 +7825,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7844,10 +7849,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437474</v>
+        <v>437096</v>
       </c>
       <c r="R71" t="n">
-        <v>7010882</v>
+        <v>7010572</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7880,6 +7885,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7906,7 +7916,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132340944</v>
+        <v>132340946</v>
       </c>
       <c r="B72" t="n">
         <v>91909</v>
@@ -7941,10 +7951,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437304</v>
+        <v>437124</v>
       </c>
       <c r="R72" t="n">
-        <v>7010986</v>
+        <v>7010689</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8003,10 +8013,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132341111</v>
+        <v>132341102</v>
       </c>
       <c r="B73" t="n">
-        <v>80432</v>
+        <v>92208</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8014,21 +8024,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8038,10 +8048,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437156</v>
+        <v>437474</v>
       </c>
       <c r="R73" t="n">
-        <v>7010645</v>
+        <v>7010882</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8068,12 +8078,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8100,10 +8110,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341053</v>
+        <v>132340944</v>
       </c>
       <c r="B74" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8111,21 +8121,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8135,10 +8145,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437740</v>
+        <v>437304</v>
       </c>
       <c r="R74" t="n">
-        <v>7011063</v>
+        <v>7010986</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8171,11 +8181,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8202,10 +8207,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341096</v>
+        <v>132341111</v>
       </c>
       <c r="B75" t="n">
-        <v>57950</v>
+        <v>80432</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8213,21 +8218,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8237,10 +8242,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437096</v>
+        <v>437156</v>
       </c>
       <c r="R75" t="n">
-        <v>7010572</v>
+        <v>7010645</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8267,17 +8272,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8304,10 +8304,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341059</v>
+        <v>132341106</v>
       </c>
       <c r="B76" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8315,21 +8315,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437567</v>
+        <v>437009</v>
       </c>
       <c r="R76" t="n">
-        <v>7010953</v>
+        <v>7010701</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8375,11 +8375,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8406,10 +8401,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341106</v>
+        <v>132341059</v>
       </c>
       <c r="B77" t="n">
-        <v>92208</v>
+        <v>57953</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8417,21 +8412,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8441,10 +8436,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437009</v>
+        <v>437567</v>
       </c>
       <c r="R77" t="n">
-        <v>7010701</v>
+        <v>7010953</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8477,6 +8472,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -2304,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132341110</v>
+        <v>132341033</v>
       </c>
       <c r="B16" t="n">
-        <v>92208</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,21 +2315,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437169</v>
+        <v>438033</v>
       </c>
       <c r="R16" t="n">
-        <v>7010552</v>
+        <v>7010948</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,6 +2375,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132341129</v>
+        <v>132341110</v>
       </c>
       <c r="B17" t="n">
-        <v>91905</v>
+        <v>92208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2412,21 +2417,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2436,10 +2441,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437750</v>
+        <v>437169</v>
       </c>
       <c r="R17" t="n">
-        <v>7010913</v>
+        <v>7010552</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2498,10 +2503,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132341033</v>
+        <v>132341129</v>
       </c>
       <c r="B18" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,21 +2514,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2533,10 +2538,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438033</v>
+        <v>437750</v>
       </c>
       <c r="R18" t="n">
-        <v>7010948</v>
+        <v>7010913</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2569,11 +2574,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3197,7 +3197,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132341060</v>
+        <v>132341064</v>
       </c>
       <c r="B25" t="n">
         <v>57953</v>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437611</v>
+        <v>437442</v>
       </c>
       <c r="R25" t="n">
-        <v>7010882</v>
+        <v>7010869</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3299,7 +3299,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132341064</v>
+        <v>132341060</v>
       </c>
       <c r="B26" t="n">
         <v>57953</v>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437442</v>
+        <v>437611</v>
       </c>
       <c r="R26" t="n">
-        <v>7010869</v>
+        <v>7010882</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3613,10 +3613,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132341132</v>
+        <v>132341040</v>
       </c>
       <c r="B29" t="n">
-        <v>91905</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,21 +3624,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437384</v>
+        <v>438088</v>
       </c>
       <c r="R29" t="n">
-        <v>7010958</v>
+        <v>7010817</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,6 +3684,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3710,7 +3715,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132341041</v>
+        <v>132341049</v>
       </c>
       <c r="B30" t="n">
         <v>57953</v>
@@ -3745,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437973</v>
+        <v>437804</v>
       </c>
       <c r="R30" t="n">
-        <v>7010845</v>
+        <v>7010729</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3812,7 +3817,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132341040</v>
+        <v>132341029</v>
       </c>
       <c r="B31" t="n">
         <v>57953</v>
@@ -3847,10 +3852,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438088</v>
+        <v>437342</v>
       </c>
       <c r="R31" t="n">
-        <v>7010817</v>
+        <v>7010780</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3877,17 +3882,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3914,7 +3919,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132341049</v>
+        <v>132341041</v>
       </c>
       <c r="B32" t="n">
         <v>57953</v>
@@ -3949,10 +3954,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437804</v>
+        <v>437973</v>
       </c>
       <c r="R32" t="n">
-        <v>7010729</v>
+        <v>7010845</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4016,10 +4021,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132341029</v>
+        <v>132341132</v>
       </c>
       <c r="B33" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4027,21 +4032,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4051,10 +4056,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437342</v>
+        <v>437384</v>
       </c>
       <c r="R33" t="n">
-        <v>7010780</v>
+        <v>7010958</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4081,17 +4086,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5797,10 +5797,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132341108</v>
+        <v>132341027</v>
       </c>
       <c r="B51" t="n">
-        <v>92208</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5808,21 +5808,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437099</v>
+        <v>437678</v>
       </c>
       <c r="R51" t="n">
-        <v>7010647</v>
+        <v>7010630</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5862,12 +5862,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5894,7 +5899,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132341027</v>
+        <v>132341062</v>
       </c>
       <c r="B52" t="n">
         <v>57953</v>
@@ -5929,10 +5934,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437678</v>
+        <v>437538</v>
       </c>
       <c r="R52" t="n">
-        <v>7010630</v>
+        <v>7010940</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5959,12 +5964,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -5996,10 +6001,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132341062</v>
+        <v>132341108</v>
       </c>
       <c r="B53" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6007,21 +6012,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6031,10 +6036,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>437538</v>
+        <v>437099</v>
       </c>
       <c r="R53" t="n">
-        <v>7010940</v>
+        <v>7010647</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6067,11 +6072,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6098,10 +6098,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132341094</v>
+        <v>132341119</v>
       </c>
       <c r="B54" t="n">
-        <v>57950</v>
+        <v>57132</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6109,16 +6109,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6126,17 +6126,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>438128</v>
+        <v>437582</v>
       </c>
       <c r="R54" t="n">
-        <v>7010852</v>
+        <v>7010573</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6163,17 +6175,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6200,10 +6207,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132341119</v>
+        <v>132341094</v>
       </c>
       <c r="B55" t="n">
-        <v>57132</v>
+        <v>57950</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6211,16 +6218,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6228,29 +6235,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437582</v>
+        <v>438128</v>
       </c>
       <c r="R55" t="n">
-        <v>7010573</v>
+        <v>7010852</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6277,12 +6272,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6896,7 +6896,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132341052</v>
+        <v>132341051</v>
       </c>
       <c r="B62" t="n">
         <v>57953</v>
@@ -6931,10 +6931,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437740</v>
+        <v>437746</v>
       </c>
       <c r="R62" t="n">
-        <v>7011055</v>
+        <v>7010946</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6998,7 +6998,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132341037</v>
+        <v>132341031</v>
       </c>
       <c r="B63" t="n">
         <v>57953</v>
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437926</v>
+        <v>438101</v>
       </c>
       <c r="R63" t="n">
-        <v>7011061</v>
+        <v>7010919</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7202,7 +7202,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132341032</v>
+        <v>132341052</v>
       </c>
       <c r="B65" t="n">
         <v>57953</v>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>438064</v>
+        <v>437740</v>
       </c>
       <c r="R65" t="n">
-        <v>7010908</v>
+        <v>7011055</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7304,7 +7304,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132341066</v>
+        <v>132341032</v>
       </c>
       <c r="B66" t="n">
         <v>57953</v>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436968</v>
+        <v>438064</v>
       </c>
       <c r="R66" t="n">
-        <v>7010599</v>
+        <v>7010908</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7406,7 +7406,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132341051</v>
+        <v>132341037</v>
       </c>
       <c r="B67" t="n">
         <v>57953</v>
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437746</v>
+        <v>437926</v>
       </c>
       <c r="R67" t="n">
-        <v>7010946</v>
+        <v>7011061</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7508,7 +7508,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132341031</v>
+        <v>132341066</v>
       </c>
       <c r="B68" t="n">
         <v>57953</v>
@@ -7543,10 +7543,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438101</v>
+        <v>436968</v>
       </c>
       <c r="R68" t="n">
-        <v>7010919</v>
+        <v>7010599</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7712,10 +7712,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132341053</v>
+        <v>132341111</v>
       </c>
       <c r="B70" t="n">
-        <v>57953</v>
+        <v>80432</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7723,21 +7723,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437740</v>
+        <v>437156</v>
       </c>
       <c r="R70" t="n">
-        <v>7011063</v>
+        <v>7010645</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7777,17 +7777,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7814,10 +7809,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132341096</v>
+        <v>132340946</v>
       </c>
       <c r="B71" t="n">
-        <v>57950</v>
+        <v>91909</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7825,21 +7820,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7849,10 +7844,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437096</v>
+        <v>437124</v>
       </c>
       <c r="R71" t="n">
-        <v>7010572</v>
+        <v>7010689</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7885,11 +7880,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7916,10 +7906,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132340946</v>
+        <v>132341102</v>
       </c>
       <c r="B72" t="n">
-        <v>91909</v>
+        <v>92208</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7927,21 +7917,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7951,10 +7941,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437124</v>
+        <v>437474</v>
       </c>
       <c r="R72" t="n">
-        <v>7010689</v>
+        <v>7010882</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8013,10 +8003,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132341102</v>
+        <v>132340944</v>
       </c>
       <c r="B73" t="n">
-        <v>92208</v>
+        <v>91909</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8024,21 +8014,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8048,10 +8038,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437474</v>
+        <v>437304</v>
       </c>
       <c r="R73" t="n">
-        <v>7010882</v>
+        <v>7010986</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8110,10 +8100,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132340944</v>
+        <v>132341096</v>
       </c>
       <c r="B74" t="n">
-        <v>91909</v>
+        <v>57950</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8121,21 +8111,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8145,10 +8135,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437304</v>
+        <v>437096</v>
       </c>
       <c r="R74" t="n">
-        <v>7010986</v>
+        <v>7010572</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8181,6 +8171,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8207,10 +8202,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341111</v>
+        <v>132341053</v>
       </c>
       <c r="B75" t="n">
-        <v>80432</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8218,21 +8213,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8242,10 +8237,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437156</v>
+        <v>437740</v>
       </c>
       <c r="R75" t="n">
-        <v>7010645</v>
+        <v>7011063</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8272,12 +8267,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8503,10 +8503,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132340942</v>
+        <v>132341063</v>
       </c>
       <c r="B78" t="n">
-        <v>91909</v>
+        <v>57953</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8514,21 +8514,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437287</v>
+        <v>437505</v>
       </c>
       <c r="R78" t="n">
-        <v>7010896</v>
+        <v>7010836</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8574,6 +8574,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8600,7 +8605,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132341065</v>
+        <v>132341045</v>
       </c>
       <c r="B79" t="n">
         <v>57953</v>
@@ -8635,10 +8640,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437074</v>
+        <v>437901</v>
       </c>
       <c r="R79" t="n">
-        <v>7010580</v>
+        <v>7010813</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8675,7 +8680,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8702,7 +8707,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132341045</v>
+        <v>132341030</v>
       </c>
       <c r="B80" t="n">
         <v>57953</v>
@@ -8737,10 +8742,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437901</v>
+        <v>438101</v>
       </c>
       <c r="R80" t="n">
-        <v>7010813</v>
+        <v>7010924</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8777,7 +8782,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8804,10 +8809,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132341030</v>
+        <v>132340942</v>
       </c>
       <c r="B81" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8815,21 +8820,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8839,10 +8844,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438101</v>
+        <v>437287</v>
       </c>
       <c r="R81" t="n">
-        <v>7010924</v>
+        <v>7010896</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8875,11 +8880,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8906,7 +8906,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132341063</v>
+        <v>132341065</v>
       </c>
       <c r="B82" t="n">
         <v>57953</v>
@@ -8941,10 +8941,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437505</v>
+        <v>437074</v>
       </c>
       <c r="R82" t="n">
-        <v>7010836</v>
+        <v>7010580</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9508,10 +9508,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132341028</v>
+        <v>132340948</v>
       </c>
       <c r="B88" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9519,21 +9519,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9543,10 +9543,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437583</v>
+        <v>437159</v>
       </c>
       <c r="R88" t="n">
-        <v>7010708</v>
+        <v>7010541</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9573,17 +9573,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9610,7 +9605,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132340948</v>
+        <v>132340943</v>
       </c>
       <c r="B89" t="n">
         <v>91909</v>
@@ -9645,10 +9640,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437159</v>
+        <v>437280</v>
       </c>
       <c r="R89" t="n">
-        <v>7010541</v>
+        <v>7010923</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9707,7 +9702,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132340943</v>
+        <v>132340938</v>
       </c>
       <c r="B90" t="n">
         <v>91909</v>
@@ -9742,10 +9737,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437280</v>
+        <v>437465</v>
       </c>
       <c r="R90" t="n">
-        <v>7010923</v>
+        <v>7010897</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9804,7 +9799,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132340938</v>
+        <v>132340947</v>
       </c>
       <c r="B91" t="n">
         <v>91909</v>
@@ -9839,10 +9834,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437465</v>
+        <v>437023</v>
       </c>
       <c r="R91" t="n">
-        <v>7010897</v>
+        <v>7010700</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9901,7 +9896,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132340947</v>
+        <v>132340939</v>
       </c>
       <c r="B92" t="n">
         <v>91909</v>
@@ -9936,10 +9931,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437023</v>
+        <v>437481</v>
       </c>
       <c r="R92" t="n">
-        <v>7010700</v>
+        <v>7010828</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9998,10 +9993,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132340939</v>
+        <v>132341097</v>
       </c>
       <c r="B93" t="n">
-        <v>91909</v>
+        <v>80433</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10009,21 +10004,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10033,10 +10028,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>437481</v>
+        <v>437011</v>
       </c>
       <c r="R93" t="n">
-        <v>7010828</v>
+        <v>7010575</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10192,10 +10187,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132341097</v>
+        <v>132341028</v>
       </c>
       <c r="B95" t="n">
-        <v>80433</v>
+        <v>57953</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10203,21 +10198,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10227,10 +10222,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>437011</v>
+        <v>437583</v>
       </c>
       <c r="R95" t="n">
-        <v>7010575</v>
+        <v>7010708</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10257,12 +10252,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10289,57 +10289,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132341116</v>
+        <v>132341107</v>
       </c>
       <c r="B96" t="n">
-        <v>99118</v>
+        <v>92208</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>437089</v>
+        <v>436990</v>
       </c>
       <c r="R96" t="n">
-        <v>7010576</v>
+        <v>7010703</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10374,18 +10362,12 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Rikligt, över 200</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10404,7 +10386,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132341107</v>
+        <v>132341104</v>
       </c>
       <c r="B97" t="n">
         <v>92208</v>
@@ -10439,10 +10421,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436990</v>
+        <v>437280</v>
       </c>
       <c r="R97" t="n">
-        <v>7010703</v>
+        <v>7010923</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10501,45 +10483,57 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132341104</v>
+        <v>132341116</v>
       </c>
       <c r="B98" t="n">
-        <v>92208</v>
+        <v>99118</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437280</v>
+        <v>437089</v>
       </c>
       <c r="R98" t="n">
-        <v>7010923</v>
+        <v>7010576</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10574,12 +10568,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rikligt, över 200</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -3613,10 +3613,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132341040</v>
+        <v>132341132</v>
       </c>
       <c r="B29" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,21 +3624,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438088</v>
+        <v>437384</v>
       </c>
       <c r="R29" t="n">
-        <v>7010817</v>
+        <v>7010958</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,11 +3684,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3715,7 +3710,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132341049</v>
+        <v>132341040</v>
       </c>
       <c r="B30" t="n">
         <v>57953</v>
@@ -3750,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437804</v>
+        <v>438088</v>
       </c>
       <c r="R30" t="n">
-        <v>7010729</v>
+        <v>7010817</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3790,7 +3785,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3817,7 +3812,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132341029</v>
+        <v>132341049</v>
       </c>
       <c r="B31" t="n">
         <v>57953</v>
@@ -3852,10 +3847,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437342</v>
+        <v>437804</v>
       </c>
       <c r="R31" t="n">
-        <v>7010780</v>
+        <v>7010729</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3882,12 +3877,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3919,7 +3914,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132341041</v>
+        <v>132341029</v>
       </c>
       <c r="B32" t="n">
         <v>57953</v>
@@ -3954,10 +3949,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437973</v>
+        <v>437342</v>
       </c>
       <c r="R32" t="n">
-        <v>7010845</v>
+        <v>7010780</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3984,12 +3979,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4021,10 +4016,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132341132</v>
+        <v>132341041</v>
       </c>
       <c r="B33" t="n">
-        <v>91905</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4032,21 +4027,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4056,10 +4051,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437384</v>
+        <v>437973</v>
       </c>
       <c r="R33" t="n">
-        <v>7010958</v>
+        <v>7010845</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4092,6 +4087,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4118,10 +4118,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132341047</v>
+        <v>132341138</v>
       </c>
       <c r="B34" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4129,21 +4129,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437918</v>
+        <v>437710</v>
       </c>
       <c r="R34" t="n">
-        <v>7010791</v>
+        <v>7010507</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4220,10 +4220,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132341138</v>
+        <v>132341047</v>
       </c>
       <c r="B35" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437710</v>
+        <v>437918</v>
       </c>
       <c r="R35" t="n">
-        <v>7010507</v>
+        <v>7010791</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -8503,10 +8503,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132341063</v>
+        <v>132340942</v>
       </c>
       <c r="B78" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8514,21 +8514,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437505</v>
+        <v>437287</v>
       </c>
       <c r="R78" t="n">
-        <v>7010836</v>
+        <v>7010896</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8574,11 +8574,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8605,7 +8600,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132341045</v>
+        <v>132341063</v>
       </c>
       <c r="B79" t="n">
         <v>57953</v>
@@ -8640,10 +8635,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437901</v>
+        <v>437505</v>
       </c>
       <c r="R79" t="n">
-        <v>7010813</v>
+        <v>7010836</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8680,7 +8675,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8707,7 +8702,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132341030</v>
+        <v>132341045</v>
       </c>
       <c r="B80" t="n">
         <v>57953</v>
@@ -8742,10 +8737,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438101</v>
+        <v>437901</v>
       </c>
       <c r="R80" t="n">
-        <v>7010924</v>
+        <v>7010813</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8782,7 +8777,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8809,10 +8804,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132340942</v>
+        <v>132341065</v>
       </c>
       <c r="B81" t="n">
-        <v>91909</v>
+        <v>57953</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8820,21 +8815,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8844,10 +8839,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437287</v>
+        <v>437074</v>
       </c>
       <c r="R81" t="n">
-        <v>7010896</v>
+        <v>7010580</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8880,6 +8875,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8906,7 +8906,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132341065</v>
+        <v>132341043</v>
       </c>
       <c r="B82" t="n">
         <v>57953</v>
@@ -8941,10 +8941,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437074</v>
+        <v>437872</v>
       </c>
       <c r="R82" t="n">
-        <v>7010580</v>
+        <v>7010932</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9008,7 +9008,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341043</v>
+        <v>132341030</v>
       </c>
       <c r="B83" t="n">
         <v>57953</v>
@@ -9043,10 +9043,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437872</v>
+        <v>438101</v>
       </c>
       <c r="R83" t="n">
-        <v>7010932</v>
+        <v>7010924</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9993,10 +9993,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132341097</v>
+        <v>132341101</v>
       </c>
       <c r="B93" t="n">
-        <v>80433</v>
+        <v>92208</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10004,21 +10004,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>437011</v>
+        <v>437486</v>
       </c>
       <c r="R93" t="n">
-        <v>7010575</v>
+        <v>7010537</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10090,10 +10090,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132341101</v>
+        <v>132341097</v>
       </c>
       <c r="B94" t="n">
-        <v>92208</v>
+        <v>80433</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10101,21 +10101,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437486</v>
+        <v>437011</v>
       </c>
       <c r="R94" t="n">
-        <v>7010537</v>
+        <v>7010575</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10155,12 +10155,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -2304,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132341033</v>
+        <v>132341110</v>
       </c>
       <c r="B16" t="n">
-        <v>57953</v>
+        <v>92209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,21 +2315,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438033</v>
+        <v>437169</v>
       </c>
       <c r="R16" t="n">
-        <v>7010948</v>
+        <v>7010552</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,11 +2375,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132341110</v>
+        <v>132341129</v>
       </c>
       <c r="B17" t="n">
-        <v>92208</v>
+        <v>91906</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,21 +2412,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2441,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437169</v>
+        <v>437750</v>
       </c>
       <c r="R17" t="n">
-        <v>7010552</v>
+        <v>7010913</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2503,10 +2498,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132341129</v>
+        <v>132341033</v>
       </c>
       <c r="B18" t="n">
-        <v>91905</v>
+        <v>57954</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2514,21 +2509,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2538,10 +2533,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437750</v>
+        <v>438033</v>
       </c>
       <c r="R18" t="n">
-        <v>7010913</v>
+        <v>7010948</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2574,6 +2569,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,10 +2600,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132341137</v>
+        <v>132341126</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>91906</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2611,21 +2611,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437632</v>
+        <v>437525</v>
       </c>
       <c r="R19" t="n">
-        <v>7010619</v>
+        <v>7010475</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2665,17 +2665,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2702,10 +2697,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132341126</v>
+        <v>132341137</v>
       </c>
       <c r="B20" t="n">
-        <v>91905</v>
+        <v>79328</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2713,21 +2708,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2737,10 +2732,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437525</v>
+        <v>437632</v>
       </c>
       <c r="R20" t="n">
-        <v>7010475</v>
+        <v>7010619</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2767,12 +2762,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2802,7 +2802,7 @@
         <v>132341048</v>
       </c>
       <c r="B21" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>132341058</v>
       </c>
       <c r="B22" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132340941</v>
+        <v>132341113</v>
       </c>
       <c r="B23" t="n">
-        <v>91909</v>
+        <v>80433</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437348</v>
+        <v>437053</v>
       </c>
       <c r="R23" t="n">
-        <v>7010989</v>
+        <v>7010706</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132341113</v>
+        <v>132340941</v>
       </c>
       <c r="B24" t="n">
-        <v>80432</v>
+        <v>91910</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437053</v>
+        <v>437348</v>
       </c>
       <c r="R24" t="n">
-        <v>7010706</v>
+        <v>7010989</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132341064</v>
+        <v>132341060</v>
       </c>
       <c r="B25" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437442</v>
+        <v>437611</v>
       </c>
       <c r="R25" t="n">
-        <v>7010869</v>
+        <v>7010882</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132341060</v>
+        <v>132341064</v>
       </c>
       <c r="B26" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437611</v>
+        <v>437442</v>
       </c>
       <c r="R26" t="n">
-        <v>7010882</v>
+        <v>7010869</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132341117</v>
+        <v>132341118</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3429,17 +3429,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437071</v>
+        <v>437059</v>
       </c>
       <c r="R27" t="n">
-        <v>7010578</v>
+        <v>7010572</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3474,12 +3486,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt över 200</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3498,10 +3516,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132341118</v>
+        <v>132341117</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3526,29 +3544,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437059</v>
+        <v>437071</v>
       </c>
       <c r="R28" t="n">
-        <v>7010572</v>
+        <v>7010578</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3583,18 +3589,12 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt över 200</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>132341132</v>
       </c>
       <c r="B29" t="n">
-        <v>91905</v>
+        <v>91906</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3710,10 +3710,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132341040</v>
+        <v>132341041</v>
       </c>
       <c r="B30" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438088</v>
+        <v>437973</v>
       </c>
       <c r="R30" t="n">
-        <v>7010817</v>
+        <v>7010845</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3812,10 +3812,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132341049</v>
+        <v>132341040</v>
       </c>
       <c r="B31" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437804</v>
+        <v>438088</v>
       </c>
       <c r="R31" t="n">
-        <v>7010729</v>
+        <v>7010817</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3914,10 +3914,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132341029</v>
+        <v>132341049</v>
       </c>
       <c r="B32" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437342</v>
+        <v>437804</v>
       </c>
       <c r="R32" t="n">
-        <v>7010780</v>
+        <v>7010729</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3979,12 +3979,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4016,10 +4016,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132341041</v>
+        <v>132341029</v>
       </c>
       <c r="B33" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437973</v>
+        <v>437342</v>
       </c>
       <c r="R33" t="n">
-        <v>7010845</v>
+        <v>7010780</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4081,12 +4081,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4118,10 +4118,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132341138</v>
+        <v>132341047</v>
       </c>
       <c r="B34" t="n">
-        <v>79327</v>
+        <v>57954</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4129,21 +4129,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437710</v>
+        <v>437918</v>
       </c>
       <c r="R34" t="n">
-        <v>7010507</v>
+        <v>7010791</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4220,10 +4220,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132341047</v>
+        <v>132341138</v>
       </c>
       <c r="B35" t="n">
-        <v>57953</v>
+        <v>79328</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437918</v>
+        <v>437710</v>
       </c>
       <c r="R35" t="n">
-        <v>7010791</v>
+        <v>7010507</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4325,7 +4325,7 @@
         <v>132341135</v>
       </c>
       <c r="B36" t="n">
-        <v>91923</v>
+        <v>91924</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>132340936</v>
       </c>
       <c r="B37" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>132341140</v>
       </c>
       <c r="B38" t="n">
-        <v>92605</v>
+        <v>92606</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4613,10 +4613,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132341100</v>
+        <v>132341128</v>
       </c>
       <c r="B39" t="n">
-        <v>92208</v>
+        <v>91906</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4624,21 +4624,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437623</v>
+        <v>437765</v>
       </c>
       <c r="R39" t="n">
-        <v>7010649</v>
+        <v>7010816</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4710,10 +4710,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132341128</v>
+        <v>132341100</v>
       </c>
       <c r="B40" t="n">
-        <v>91905</v>
+        <v>92209</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4721,21 +4721,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437765</v>
+        <v>437623</v>
       </c>
       <c r="R40" t="n">
-        <v>7010816</v>
+        <v>7010649</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4807,10 +4807,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132341054</v>
+        <v>132340940</v>
       </c>
       <c r="B41" t="n">
-        <v>57953</v>
+        <v>91910</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4818,21 +4818,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437637</v>
+        <v>437350</v>
       </c>
       <c r="R41" t="n">
-        <v>7011098</v>
+        <v>7010948</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4878,11 +4878,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4909,10 +4904,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132340940</v>
+        <v>132341134</v>
       </c>
       <c r="B42" t="n">
-        <v>91909</v>
+        <v>91924</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4920,21 +4915,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4944,10 +4939,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437350</v>
+        <v>437611</v>
       </c>
       <c r="R42" t="n">
-        <v>7010948</v>
+        <v>7011053</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5006,10 +5001,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132341134</v>
+        <v>132341105</v>
       </c>
       <c r="B43" t="n">
-        <v>91923</v>
+        <v>92209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5017,21 +5012,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5041,10 +5036,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437611</v>
+        <v>437027</v>
       </c>
       <c r="R43" t="n">
-        <v>7011053</v>
+        <v>7010698</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5103,10 +5098,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132341105</v>
+        <v>132341054</v>
       </c>
       <c r="B44" t="n">
-        <v>92208</v>
+        <v>57954</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5114,21 +5109,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5138,10 +5133,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437027</v>
+        <v>437637</v>
       </c>
       <c r="R44" t="n">
-        <v>7010698</v>
+        <v>7011098</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5174,6 +5169,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5203,7 +5203,7 @@
         <v>132341057</v>
       </c>
       <c r="B45" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>132341095</v>
       </c>
       <c r="B46" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5404,10 +5404,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132340949</v>
+        <v>132341055</v>
       </c>
       <c r="B47" t="n">
-        <v>91909</v>
+        <v>57954</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5415,21 +5415,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437092</v>
+        <v>437603</v>
       </c>
       <c r="R47" t="n">
-        <v>7010575</v>
+        <v>7011097</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5475,6 +5475,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5501,10 +5506,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132341055</v>
+        <v>132340949</v>
       </c>
       <c r="B48" t="n">
-        <v>57953</v>
+        <v>91910</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5512,21 +5517,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5536,10 +5541,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437603</v>
+        <v>437092</v>
       </c>
       <c r="R48" t="n">
-        <v>7011097</v>
+        <v>7010575</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5572,11 +5577,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5606,7 +5606,7 @@
         <v>132341127</v>
       </c>
       <c r="B49" t="n">
-        <v>91905</v>
+        <v>91906</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>132341125</v>
       </c>
       <c r="B50" t="n">
-        <v>91905</v>
+        <v>91906</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132341027</v>
+        <v>132341108</v>
       </c>
       <c r="B51" t="n">
-        <v>57953</v>
+        <v>92209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5808,21 +5808,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437678</v>
+        <v>437099</v>
       </c>
       <c r="R51" t="n">
-        <v>7010630</v>
+        <v>7010647</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5862,17 +5862,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5899,10 +5894,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132341062</v>
+        <v>132341027</v>
       </c>
       <c r="B52" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5934,10 +5929,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437538</v>
+        <v>437678</v>
       </c>
       <c r="R52" t="n">
-        <v>7010940</v>
+        <v>7010630</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5964,12 +5959,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6001,10 +5996,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132341108</v>
+        <v>132341062</v>
       </c>
       <c r="B53" t="n">
-        <v>92208</v>
+        <v>57954</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6012,21 +6007,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6036,10 +6031,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>437099</v>
+        <v>437538</v>
       </c>
       <c r="R53" t="n">
-        <v>7010647</v>
+        <v>7010940</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6072,6 +6067,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6098,10 +6098,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132341119</v>
+        <v>132341094</v>
       </c>
       <c r="B54" t="n">
-        <v>57132</v>
+        <v>57951</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6109,16 +6109,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6126,29 +6126,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437582</v>
+        <v>438128</v>
       </c>
       <c r="R54" t="n">
-        <v>7010573</v>
+        <v>7010852</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6175,12 +6163,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6207,10 +6200,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132341094</v>
+        <v>132341119</v>
       </c>
       <c r="B55" t="n">
-        <v>57950</v>
+        <v>57133</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6218,16 +6211,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6235,17 +6228,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>438128</v>
+        <v>437582</v>
       </c>
       <c r="R55" t="n">
-        <v>7010852</v>
+        <v>7010573</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6272,17 +6277,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6309,10 +6309,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132341103</v>
+        <v>132341136</v>
       </c>
       <c r="B56" t="n">
-        <v>92208</v>
+        <v>79328</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6320,21 +6320,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437283</v>
+        <v>437640</v>
       </c>
       <c r="R56" t="n">
-        <v>7010896</v>
+        <v>7010681</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6374,12 +6374,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6409,7 +6414,7 @@
         <v>132340935</v>
       </c>
       <c r="B57" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6506,7 +6511,7 @@
         <v>132341131</v>
       </c>
       <c r="B58" t="n">
-        <v>91905</v>
+        <v>91906</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6600,10 +6605,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132341109</v>
+        <v>132341052</v>
       </c>
       <c r="B59" t="n">
-        <v>92208</v>
+        <v>57954</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6611,21 +6616,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6635,10 +6640,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437194</v>
+        <v>437740</v>
       </c>
       <c r="R59" t="n">
-        <v>7010597</v>
+        <v>7011055</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6671,6 +6676,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6697,10 +6707,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341112</v>
+        <v>132341037</v>
       </c>
       <c r="B60" t="n">
-        <v>80432</v>
+        <v>57954</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6708,21 +6718,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6732,10 +6742,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437518</v>
+        <v>437926</v>
       </c>
       <c r="R60" t="n">
-        <v>7010858</v>
+        <v>7011061</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6768,6 +6778,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6794,10 +6809,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132341136</v>
+        <v>132341056</v>
       </c>
       <c r="B61" t="n">
-        <v>79327</v>
+        <v>57954</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6805,21 +6820,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6829,10 +6844,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437640</v>
+        <v>437578</v>
       </c>
       <c r="R61" t="n">
-        <v>7010681</v>
+        <v>7011118</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6859,17 +6874,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6896,10 +6911,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132341051</v>
+        <v>132341032</v>
       </c>
       <c r="B62" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6931,10 +6946,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437746</v>
+        <v>438064</v>
       </c>
       <c r="R62" t="n">
-        <v>7010946</v>
+        <v>7010908</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6971,7 +6986,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6998,10 +7013,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132341031</v>
+        <v>132341066</v>
       </c>
       <c r="B63" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7033,10 +7048,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>438101</v>
+        <v>436968</v>
       </c>
       <c r="R63" t="n">
-        <v>7010919</v>
+        <v>7010599</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7100,10 +7115,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132341056</v>
+        <v>132341051</v>
       </c>
       <c r="B64" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7135,10 +7150,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>437578</v>
+        <v>437746</v>
       </c>
       <c r="R64" t="n">
-        <v>7011118</v>
+        <v>7010946</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7202,10 +7217,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132341052</v>
+        <v>132341031</v>
       </c>
       <c r="B65" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7237,10 +7252,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>437740</v>
+        <v>438101</v>
       </c>
       <c r="R65" t="n">
-        <v>7011055</v>
+        <v>7010919</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7304,10 +7319,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132341032</v>
+        <v>132341034</v>
       </c>
       <c r="B66" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7339,10 +7354,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>438064</v>
+        <v>437908</v>
       </c>
       <c r="R66" t="n">
-        <v>7010908</v>
+        <v>7011073</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7379,7 +7394,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7406,10 +7421,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132341037</v>
+        <v>132341112</v>
       </c>
       <c r="B67" t="n">
-        <v>57953</v>
+        <v>80433</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7417,21 +7432,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7441,10 +7456,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437926</v>
+        <v>437518</v>
       </c>
       <c r="R67" t="n">
-        <v>7011061</v>
+        <v>7010858</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,11 +7492,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7508,10 +7518,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132341066</v>
+        <v>132341109</v>
       </c>
       <c r="B68" t="n">
-        <v>57953</v>
+        <v>92209</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7519,21 +7529,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7543,10 +7553,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436968</v>
+        <v>437194</v>
       </c>
       <c r="R68" t="n">
-        <v>7010599</v>
+        <v>7010597</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,11 +7589,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7610,10 +7615,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132341034</v>
+        <v>132341103</v>
       </c>
       <c r="B69" t="n">
-        <v>57953</v>
+        <v>92209</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7621,21 +7626,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7645,10 +7650,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437908</v>
+        <v>437283</v>
       </c>
       <c r="R69" t="n">
-        <v>7011073</v>
+        <v>7010896</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,11 +7686,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7712,10 +7712,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132341111</v>
+        <v>132340946</v>
       </c>
       <c r="B70" t="n">
-        <v>80432</v>
+        <v>91910</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7723,21 +7723,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437156</v>
+        <v>437124</v>
       </c>
       <c r="R70" t="n">
-        <v>7010645</v>
+        <v>7010689</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7777,12 +7777,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7809,10 +7809,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132340946</v>
+        <v>132340944</v>
       </c>
       <c r="B71" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7844,10 +7844,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437124</v>
+        <v>437304</v>
       </c>
       <c r="R71" t="n">
-        <v>7010689</v>
+        <v>7010986</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7906,10 +7906,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132341102</v>
+        <v>132341053</v>
       </c>
       <c r="B72" t="n">
-        <v>92208</v>
+        <v>57954</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7917,21 +7917,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437474</v>
+        <v>437740</v>
       </c>
       <c r="R72" t="n">
-        <v>7010882</v>
+        <v>7011063</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7977,6 +7977,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8003,10 +8008,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132340944</v>
+        <v>132341111</v>
       </c>
       <c r="B73" t="n">
-        <v>91909</v>
+        <v>80433</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8014,21 +8019,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8038,10 +8043,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437304</v>
+        <v>437156</v>
       </c>
       <c r="R73" t="n">
-        <v>7010986</v>
+        <v>7010645</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8068,12 +8073,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8100,10 +8105,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341096</v>
+        <v>132341102</v>
       </c>
       <c r="B74" t="n">
-        <v>57950</v>
+        <v>92209</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8111,21 +8116,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8135,10 +8140,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437096</v>
+        <v>437474</v>
       </c>
       <c r="R74" t="n">
-        <v>7010572</v>
+        <v>7010882</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8171,11 +8176,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8202,10 +8202,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341053</v>
+        <v>132341096</v>
       </c>
       <c r="B75" t="n">
-        <v>57953</v>
+        <v>57951</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8213,16 +8213,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8237,10 +8237,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437740</v>
+        <v>437096</v>
       </c>
       <c r="R75" t="n">
-        <v>7011063</v>
+        <v>7010572</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8307,7 +8307,7 @@
         <v>132341106</v>
       </c>
       <c r="B76" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>132341059</v>
       </c>
       <c r="B77" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>132340942</v>
       </c>
       <c r="B78" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8600,10 +8600,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132341063</v>
+        <v>132341065</v>
       </c>
       <c r="B79" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8635,10 +8635,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437505</v>
+        <v>437074</v>
       </c>
       <c r="R79" t="n">
-        <v>7010836</v>
+        <v>7010580</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8705,7 +8705,7 @@
         <v>132341045</v>
       </c>
       <c r="B80" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8804,10 +8804,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132341065</v>
+        <v>132341030</v>
       </c>
       <c r="B81" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8839,10 +8839,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437074</v>
+        <v>438101</v>
       </c>
       <c r="R81" t="n">
-        <v>7010580</v>
+        <v>7010924</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8906,10 +8906,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132341043</v>
+        <v>132341063</v>
       </c>
       <c r="B82" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8941,10 +8941,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437872</v>
+        <v>437505</v>
       </c>
       <c r="R82" t="n">
-        <v>7010932</v>
+        <v>7010836</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9008,10 +9008,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341030</v>
+        <v>132341043</v>
       </c>
       <c r="B83" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9043,10 +9043,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>438101</v>
+        <v>437872</v>
       </c>
       <c r="R83" t="n">
-        <v>7010924</v>
+        <v>7010932</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9113,7 +9113,7 @@
         <v>132341115</v>
       </c>
       <c r="B84" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9207,10 +9207,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132341114</v>
+        <v>132341046</v>
       </c>
       <c r="B85" t="n">
-        <v>80432</v>
+        <v>57954</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9218,21 +9218,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437012</v>
+        <v>437902</v>
       </c>
       <c r="R85" t="n">
-        <v>7010575</v>
+        <v>7010811</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9278,6 +9278,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9304,10 +9309,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132341046</v>
+        <v>132341061</v>
       </c>
       <c r="B86" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9339,10 +9344,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>437902</v>
+        <v>437535</v>
       </c>
       <c r="R86" t="n">
-        <v>7010811</v>
+        <v>7010929</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9379,7 +9384,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9406,10 +9411,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132341061</v>
+        <v>132341114</v>
       </c>
       <c r="B87" t="n">
-        <v>57953</v>
+        <v>80433</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9417,21 +9422,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9441,10 +9446,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437535</v>
+        <v>437012</v>
       </c>
       <c r="R87" t="n">
-        <v>7010929</v>
+        <v>7010575</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9477,11 +9482,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9508,10 +9508,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132340948</v>
+        <v>132341101</v>
       </c>
       <c r="B88" t="n">
-        <v>91909</v>
+        <v>92209</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9519,21 +9519,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9543,10 +9543,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437159</v>
+        <v>437486</v>
       </c>
       <c r="R88" t="n">
-        <v>7010541</v>
+        <v>7010537</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9573,12 +9573,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9605,10 +9605,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132340943</v>
+        <v>132340948</v>
       </c>
       <c r="B89" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9640,10 +9640,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437280</v>
+        <v>437159</v>
       </c>
       <c r="R89" t="n">
-        <v>7010923</v>
+        <v>7010541</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9702,10 +9702,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132340938</v>
+        <v>132340943</v>
       </c>
       <c r="B90" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437465</v>
+        <v>437280</v>
       </c>
       <c r="R90" t="n">
-        <v>7010897</v>
+        <v>7010923</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9799,10 +9799,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132340947</v>
+        <v>132340938</v>
       </c>
       <c r="B91" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9834,10 +9834,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437023</v>
+        <v>437465</v>
       </c>
       <c r="R91" t="n">
-        <v>7010700</v>
+        <v>7010897</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9896,10 +9896,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132340939</v>
+        <v>132340947</v>
       </c>
       <c r="B92" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9931,10 +9931,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437481</v>
+        <v>437023</v>
       </c>
       <c r="R92" t="n">
-        <v>7010828</v>
+        <v>7010700</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9993,10 +9993,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132341101</v>
+        <v>132340939</v>
       </c>
       <c r="B93" t="n">
-        <v>92208</v>
+        <v>91910</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10004,21 +10004,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>437486</v>
+        <v>437481</v>
       </c>
       <c r="R93" t="n">
-        <v>7010537</v>
+        <v>7010828</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10093,7 +10093,7 @@
         <v>132341097</v>
       </c>
       <c r="B94" t="n">
-        <v>80433</v>
+        <v>80434</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>132341028</v>
       </c>
       <c r="B95" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10289,10 +10289,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132341107</v>
+        <v>132341104</v>
       </c>
       <c r="B96" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10324,10 +10324,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436990</v>
+        <v>437280</v>
       </c>
       <c r="R96" t="n">
-        <v>7010703</v>
+        <v>7010923</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10386,10 +10386,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132341104</v>
+        <v>132341107</v>
       </c>
       <c r="B97" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10421,10 +10421,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>437280</v>
+        <v>436990</v>
       </c>
       <c r="R97" t="n">
-        <v>7010923</v>
+        <v>7010703</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10486,7 +10486,7 @@
         <v>132341116</v>
       </c>
       <c r="B98" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY98"/>
+  <dimension ref="A1:AY103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89596053</v>
+        <v>89596032</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437328.9039109705</v>
+        <v>437193</v>
       </c>
       <c r="R2" t="n">
-        <v>7010703.867621542</v>
+        <v>7010602</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>89596044</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,12 +796,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437128.0405921418</v>
+        <v>437128</v>
       </c>
       <c r="R3" t="n">
-        <v>7010548.991128696</v>
+        <v>7010549</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89596037</v>
+        <v>89596066</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437302.8641984189</v>
+        <v>437318</v>
       </c>
       <c r="R4" t="n">
-        <v>7010712.042040182</v>
+        <v>7010698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89596047</v>
+        <v>132341100</v>
       </c>
       <c r="B5" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,34 +989,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437317.1028106239</v>
+        <v>437623</v>
       </c>
       <c r="R5" t="n">
-        <v>7010700.939341374</v>
+        <v>7010649</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,22 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,31 +1063,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89596049</v>
+        <v>132341101</v>
       </c>
       <c r="B6" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,25 +1095,25 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438072.969544878</v>
+        <v>437486</v>
       </c>
       <c r="R6" t="n">
-        <v>7010757.158633715</v>
+        <v>7010537</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,22 +1140,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,31 +1160,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89596069</v>
+        <v>132341102</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,34 +1183,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438073.8899007687</v>
+        <v>437474</v>
       </c>
       <c r="R7" t="n">
-        <v>7010758.043105891</v>
+        <v>7010882</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,22 +1237,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,31 +1257,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89596058</v>
+        <v>132341103</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,34 +1280,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437133.0691709509</v>
+        <v>437283</v>
       </c>
       <c r="R8" t="n">
-        <v>7010552.050864005</v>
+        <v>7010896</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,22 +1334,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,31 +1354,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89596052</v>
+        <v>132341104</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,34 +1377,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437329.175489146</v>
+        <v>437280</v>
       </c>
       <c r="R9" t="n">
-        <v>7010717.845878438</v>
+        <v>7010923</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,22 +1431,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,31 +1451,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89596036</v>
+        <v>132341105</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,34 +1474,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437215.9934702101</v>
+        <v>437027</v>
       </c>
       <c r="R10" t="n">
-        <v>7010611.785554641</v>
+        <v>7010698</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,22 +1528,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,31 +1548,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89596066</v>
+        <v>132341106</v>
       </c>
       <c r="B11" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,25 +1580,25 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437317.9532975566</v>
+        <v>437009</v>
       </c>
       <c r="R11" t="n">
-        <v>7010698.216314465</v>
+        <v>7010701</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,22 +1625,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,31 +1645,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89596032</v>
+        <v>132341107</v>
       </c>
       <c r="B12" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,25 +1677,25 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437193.214423712</v>
+        <v>436990</v>
       </c>
       <c r="R12" t="n">
-        <v>7010601.853750248</v>
+        <v>7010703</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,22 +1722,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,31 +1742,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89596065</v>
+        <v>132341108</v>
       </c>
       <c r="B13" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,34 +1765,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437252.0379228034</v>
+        <v>437099</v>
       </c>
       <c r="R13" t="n">
-        <v>7010607.024358855</v>
+        <v>7010647</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,22 +1819,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,31 +1839,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89596033</v>
+        <v>132341109</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,34 +1862,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437859.0706488402</v>
+        <v>437194</v>
       </c>
       <c r="R14" t="n">
-        <v>7010837.953475563</v>
+        <v>7010597</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,22 +1916,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,31 +1936,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89596035</v>
+        <v>132341110</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,34 +1959,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437643.0697792526</v>
+        <v>437169</v>
       </c>
       <c r="R15" t="n">
-        <v>7011113.198644138</v>
+        <v>7010552</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2253,27 +2013,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,48 +2033,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132341110</v>
+        <v>132341140</v>
       </c>
       <c r="B16" t="n">
-        <v>92215</v>
+        <v>92689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2339,10 +2080,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437169</v>
+        <v>437481</v>
       </c>
       <c r="R16" t="n">
-        <v>7010552</v>
+        <v>7010829</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2401,10 +2142,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132341129</v>
+        <v>132341125</v>
       </c>
       <c r="B17" t="n">
-        <v>91912</v>
+        <v>91970</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2436,10 +2177,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437750</v>
+        <v>437485</v>
       </c>
       <c r="R17" t="n">
-        <v>7010913</v>
+        <v>7010552</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2466,12 +2207,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,10 +2239,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132341033</v>
+        <v>132341126</v>
       </c>
       <c r="B18" t="n">
-        <v>57957</v>
+        <v>91970</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,21 +2250,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2533,10 +2274,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438033</v>
+        <v>437525</v>
       </c>
       <c r="R18" t="n">
-        <v>7010948</v>
+        <v>7010475</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2569,11 +2310,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,10 +2336,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132341126</v>
+        <v>132341128</v>
       </c>
       <c r="B19" t="n">
-        <v>91912</v>
+        <v>91970</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2635,10 +2371,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437525</v>
+        <v>437765</v>
       </c>
       <c r="R19" t="n">
-        <v>7010475</v>
+        <v>7010816</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2697,10 +2433,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132341137</v>
+        <v>132341129</v>
       </c>
       <c r="B20" t="n">
-        <v>79332</v>
+        <v>91970</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,21 +2444,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2732,10 +2468,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437632</v>
+        <v>437750</v>
       </c>
       <c r="R20" t="n">
-        <v>7010619</v>
+        <v>7010913</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2762,17 +2498,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2799,10 +2530,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132341048</v>
+        <v>132341131</v>
       </c>
       <c r="B21" t="n">
-        <v>57957</v>
+        <v>91970</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,21 +2541,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2834,10 +2565,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437910</v>
+        <v>437674</v>
       </c>
       <c r="R21" t="n">
-        <v>7010779</v>
+        <v>7011000</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,11 +2601,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2901,10 +2627,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132341058</v>
+        <v>132341132</v>
       </c>
       <c r="B22" t="n">
-        <v>57957</v>
+        <v>91970</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2912,21 +2638,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2936,10 +2662,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437635</v>
+        <v>437384</v>
       </c>
       <c r="R22" t="n">
-        <v>7011011</v>
+        <v>7010958</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2972,11 +2698,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3003,10 +2724,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132340941</v>
+        <v>89596037</v>
       </c>
       <c r="B23" t="n">
-        <v>91916</v>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3034,14 +2755,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437348</v>
+        <v>437303</v>
       </c>
       <c r="R23" t="n">
-        <v>7010989</v>
+        <v>7010712</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3068,12 +2789,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3088,22 +2809,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132341064</v>
+        <v>89596053</v>
       </c>
       <c r="B24" t="n">
-        <v>57957</v>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3111,34 +2836,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437442</v>
+        <v>437329</v>
       </c>
       <c r="R24" t="n">
-        <v>7010869</v>
+        <v>7010704</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3165,17 +2890,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3190,22 +2910,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132341060</v>
+        <v>89596058</v>
       </c>
       <c r="B25" t="n">
-        <v>57957</v>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3213,34 +2937,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437611</v>
+        <v>437133</v>
       </c>
       <c r="R25" t="n">
-        <v>7010882</v>
+        <v>7010552</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3267,17 +2991,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3292,44 +3011,48 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132341117</v>
+        <v>132340935</v>
       </c>
       <c r="B26" t="n">
-        <v>99125</v>
+        <v>91974</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3339,10 +3062,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437071</v>
+        <v>437488</v>
       </c>
       <c r="R26" t="n">
-        <v>7010578</v>
+        <v>7010535</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3369,12 +3092,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3401,57 +3124,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132341118</v>
+        <v>132340936</v>
       </c>
       <c r="B27" t="n">
-        <v>99125</v>
+        <v>91974</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437059</v>
+        <v>437369</v>
       </c>
       <c r="R27" t="n">
-        <v>7010572</v>
+        <v>7010787</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3478,17 +3189,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt över 200</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3497,7 +3203,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3516,10 +3221,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132341113</v>
+        <v>132340938</v>
       </c>
       <c r="B28" t="n">
-        <v>80437</v>
+        <v>91974</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,21 +3232,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3551,10 +3256,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437053</v>
+        <v>437465</v>
       </c>
       <c r="R28" t="n">
-        <v>7010706</v>
+        <v>7010897</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3613,10 +3318,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132341132</v>
+        <v>132340939</v>
       </c>
       <c r="B29" t="n">
-        <v>91912</v>
+        <v>91974</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,21 +3329,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3648,10 +3353,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437384</v>
+        <v>437481</v>
       </c>
       <c r="R29" t="n">
-        <v>7010958</v>
+        <v>7010828</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3710,10 +3415,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132341040</v>
+        <v>132340940</v>
       </c>
       <c r="B30" t="n">
-        <v>57957</v>
+        <v>91974</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3721,21 +3426,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,10 +3450,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438088</v>
+        <v>437350</v>
       </c>
       <c r="R30" t="n">
-        <v>7010817</v>
+        <v>7010948</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3781,11 +3486,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3812,10 +3512,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132341049</v>
+        <v>132340941</v>
       </c>
       <c r="B31" t="n">
-        <v>57957</v>
+        <v>91974</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3823,21 +3523,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3847,10 +3547,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437804</v>
+        <v>437348</v>
       </c>
       <c r="R31" t="n">
-        <v>7010729</v>
+        <v>7010989</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3883,11 +3583,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3914,10 +3609,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132341029</v>
+        <v>132340942</v>
       </c>
       <c r="B32" t="n">
-        <v>57957</v>
+        <v>91974</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3925,21 +3620,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3949,10 +3644,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437342</v>
+        <v>437287</v>
       </c>
       <c r="R32" t="n">
-        <v>7010780</v>
+        <v>7010896</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3979,17 +3674,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4016,10 +3706,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132341041</v>
+        <v>132340943</v>
       </c>
       <c r="B33" t="n">
-        <v>57957</v>
+        <v>91974</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4027,21 +3717,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4051,10 +3741,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437973</v>
+        <v>437280</v>
       </c>
       <c r="R33" t="n">
-        <v>7010845</v>
+        <v>7010923</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4087,11 +3777,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4118,10 +3803,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132341138</v>
+        <v>132340944</v>
       </c>
       <c r="B34" t="n">
-        <v>79332</v>
+        <v>91974</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4129,21 +3814,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4153,10 +3838,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437710</v>
+        <v>437304</v>
       </c>
       <c r="R34" t="n">
-        <v>7010507</v>
+        <v>7010986</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4189,11 +3874,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4220,10 +3900,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132341047</v>
+        <v>132340946</v>
       </c>
       <c r="B35" t="n">
-        <v>57957</v>
+        <v>91974</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4231,21 +3911,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4255,10 +3935,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437918</v>
+        <v>437124</v>
       </c>
       <c r="R35" t="n">
-        <v>7010791</v>
+        <v>7010689</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4291,11 +3971,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4322,10 +3997,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132341135</v>
+        <v>132340947</v>
       </c>
       <c r="B36" t="n">
-        <v>91930</v>
+        <v>91974</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4333,21 +4008,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4357,10 +4032,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>437113</v>
+        <v>437023</v>
       </c>
       <c r="R36" t="n">
-        <v>7010640</v>
+        <v>7010700</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4419,10 +4094,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132340936</v>
+        <v>132340948</v>
       </c>
       <c r="B37" t="n">
-        <v>91916</v>
+        <v>91974</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4454,10 +4129,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>437369</v>
+        <v>437159</v>
       </c>
       <c r="R37" t="n">
-        <v>7010787</v>
+        <v>7010541</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4484,12 +4159,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4516,32 +4191,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132341140</v>
+        <v>132340949</v>
       </c>
       <c r="B38" t="n">
-        <v>92612</v>
+        <v>91974</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4551,10 +4226,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437481</v>
+        <v>437092</v>
       </c>
       <c r="R38" t="n">
-        <v>7010829</v>
+        <v>7010575</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4613,45 +4288,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132341100</v>
+        <v>89596047</v>
       </c>
       <c r="B39" t="n">
-        <v>92215</v>
+        <v>91923</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437623</v>
+        <v>437317</v>
       </c>
       <c r="R39" t="n">
-        <v>7010649</v>
+        <v>7010701</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,12 +4353,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4698,44 +4373,48 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132341128</v>
+        <v>132341134</v>
       </c>
       <c r="B40" t="n">
-        <v>91912</v>
+        <v>91988</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4745,10 +4424,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437765</v>
+        <v>437611</v>
       </c>
       <c r="R40" t="n">
-        <v>7010816</v>
+        <v>7011053</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4807,32 +4486,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132340940</v>
+        <v>132341135</v>
       </c>
       <c r="B41" t="n">
-        <v>91916</v>
+        <v>91988</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4842,10 +4521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437350</v>
+        <v>437113</v>
       </c>
       <c r="R41" t="n">
-        <v>7010948</v>
+        <v>7010640</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4904,10 +4583,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132341134</v>
+        <v>89596065</v>
       </c>
       <c r="B42" t="n">
-        <v>91930</v>
+        <v>80433</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4915,34 +4594,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437611</v>
+        <v>437252</v>
       </c>
       <c r="R42" t="n">
-        <v>7011053</v>
+        <v>7010607</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4969,12 +4648,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4989,22 +4668,26 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132341105</v>
+        <v>132341097</v>
       </c>
       <c r="B43" t="n">
-        <v>92215</v>
+        <v>80489</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5012,21 +4695,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5036,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437027</v>
+        <v>437011</v>
       </c>
       <c r="R43" t="n">
-        <v>7010698</v>
+        <v>7010575</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5098,45 +4781,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132341054</v>
+        <v>89596033</v>
       </c>
       <c r="B44" t="n">
-        <v>57957</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437637</v>
+        <v>437859</v>
       </c>
       <c r="R44" t="n">
-        <v>7011098</v>
+        <v>7010838</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5163,17 +4846,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5188,57 +4866,61 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132341057</v>
+        <v>89596052</v>
       </c>
       <c r="B45" t="n">
-        <v>57957</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437606</v>
+        <v>437329</v>
       </c>
       <c r="R45" t="n">
-        <v>7011053</v>
+        <v>7010718</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5265,17 +4947,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5290,44 +4967,48 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132341095</v>
+        <v>132341136</v>
       </c>
       <c r="B46" t="n">
-        <v>57954</v>
+        <v>79373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5337,10 +5018,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437922</v>
+        <v>437640</v>
       </c>
       <c r="R46" t="n">
-        <v>7011053</v>
+        <v>7010681</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5367,17 +5048,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5404,32 +5085,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132340949</v>
+        <v>132341137</v>
       </c>
       <c r="B47" t="n">
-        <v>91916</v>
+        <v>79373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5439,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437092</v>
+        <v>437632</v>
       </c>
       <c r="R47" t="n">
-        <v>7010575</v>
+        <v>7010619</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5469,12 +5150,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5501,32 +5187,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132341055</v>
+        <v>132341138</v>
       </c>
       <c r="B48" t="n">
-        <v>57957</v>
+        <v>79373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5536,10 +5222,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437603</v>
+        <v>437710</v>
       </c>
       <c r="R48" t="n">
-        <v>7011097</v>
+        <v>7010507</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5576,7 +5262,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5603,10 +5289,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132341127</v>
+        <v>89596036</v>
       </c>
       <c r="B49" t="n">
-        <v>91912</v>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5614,34 +5300,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437941</v>
+        <v>437216</v>
       </c>
       <c r="R49" t="n">
-        <v>7010836</v>
+        <v>7010612</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5668,12 +5354,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5688,22 +5374,26 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132341125</v>
+        <v>132341111</v>
       </c>
       <c r="B50" t="n">
-        <v>91912</v>
+        <v>80488</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5711,21 +5401,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5735,10 +5425,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437485</v>
+        <v>437156</v>
       </c>
       <c r="R50" t="n">
-        <v>7010552</v>
+        <v>7010645</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5797,10 +5487,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132341108</v>
+        <v>132341112</v>
       </c>
       <c r="B51" t="n">
-        <v>92215</v>
+        <v>80488</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5808,21 +5498,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5522,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437099</v>
+        <v>437518</v>
       </c>
       <c r="R51" t="n">
-        <v>7010647</v>
+        <v>7010858</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5894,10 +5584,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132341027</v>
+        <v>132341113</v>
       </c>
       <c r="B52" t="n">
-        <v>57957</v>
+        <v>80488</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5905,21 +5595,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5929,10 +5619,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437678</v>
+        <v>437053</v>
       </c>
       <c r="R52" t="n">
-        <v>7010630</v>
+        <v>7010706</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5959,17 +5649,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5996,10 +5681,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132341062</v>
+        <v>132341114</v>
       </c>
       <c r="B53" t="n">
-        <v>57957</v>
+        <v>80488</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6007,21 +5692,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6031,10 +5716,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>437538</v>
+        <v>437012</v>
       </c>
       <c r="R53" t="n">
-        <v>7010940</v>
+        <v>7010575</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6067,11 +5752,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6098,14 +5778,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132341094</v>
+        <v>132341096</v>
       </c>
       <c r="B54" t="n">
-        <v>57954</v>
+        <v>57972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6133,10 +5813,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>438128</v>
+        <v>437096</v>
       </c>
       <c r="R54" t="n">
-        <v>7010852</v>
+        <v>7010572</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6173,7 +5853,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6200,10 +5880,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132341119</v>
+        <v>89596035</v>
       </c>
       <c r="B55" t="n">
-        <v>57136</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6211,16 +5891,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6228,29 +5908,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437582</v>
+        <v>437643</v>
       </c>
       <c r="R55" t="n">
-        <v>7010573</v>
+        <v>7011113</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6277,12 +5945,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6297,22 +5970,26 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132341103</v>
+        <v>132341027</v>
       </c>
       <c r="B56" t="n">
-        <v>92215</v>
+        <v>57975</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6320,21 +5997,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6344,10 +6021,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437283</v>
+        <v>437678</v>
       </c>
       <c r="R56" t="n">
-        <v>7010896</v>
+        <v>7010630</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6374,12 +6051,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6406,10 +6088,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132340935</v>
+        <v>132341028</v>
       </c>
       <c r="B57" t="n">
-        <v>91916</v>
+        <v>57975</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6417,21 +6099,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6441,10 +6123,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437488</v>
+        <v>437583</v>
       </c>
       <c r="R57" t="n">
-        <v>7010535</v>
+        <v>7010708</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6477,6 +6159,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6503,10 +6190,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132341131</v>
+        <v>132341029</v>
       </c>
       <c r="B58" t="n">
-        <v>91912</v>
+        <v>57975</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6514,21 +6201,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6538,10 +6225,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437674</v>
+        <v>437342</v>
       </c>
       <c r="R58" t="n">
-        <v>7011000</v>
+        <v>7010780</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6568,12 +6255,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6600,10 +6292,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132341109</v>
+        <v>132341034</v>
       </c>
       <c r="B59" t="n">
-        <v>92215</v>
+        <v>57975</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6611,21 +6303,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6635,10 +6327,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437194</v>
+        <v>437908</v>
       </c>
       <c r="R59" t="n">
-        <v>7010597</v>
+        <v>7011073</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6671,6 +6363,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6697,10 +6394,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341112</v>
+        <v>132341043</v>
       </c>
       <c r="B60" t="n">
-        <v>80437</v>
+        <v>57975</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6708,21 +6405,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6732,10 +6429,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437518</v>
+        <v>437872</v>
       </c>
       <c r="R60" t="n">
-        <v>7010858</v>
+        <v>7010932</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6768,6 +6465,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6794,10 +6496,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132341136</v>
+        <v>132341045</v>
       </c>
       <c r="B61" t="n">
-        <v>79332</v>
+        <v>57975</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6805,21 +6507,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6829,10 +6531,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437640</v>
+        <v>437901</v>
       </c>
       <c r="R61" t="n">
-        <v>7010681</v>
+        <v>7010813</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6859,17 +6561,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6896,10 +6598,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132341051</v>
+        <v>132341046</v>
       </c>
       <c r="B62" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6931,10 +6633,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437746</v>
+        <v>437902</v>
       </c>
       <c r="R62" t="n">
-        <v>7010946</v>
+        <v>7010811</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6971,7 +6673,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6998,10 +6700,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132341031</v>
+        <v>132341047</v>
       </c>
       <c r="B63" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7033,10 +6735,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>438101</v>
+        <v>437918</v>
       </c>
       <c r="R63" t="n">
-        <v>7010919</v>
+        <v>7010791</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7100,10 +6802,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132341056</v>
+        <v>132341048</v>
       </c>
       <c r="B64" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7135,10 +6837,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>437578</v>
+        <v>437910</v>
       </c>
       <c r="R64" t="n">
-        <v>7011118</v>
+        <v>7010779</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7175,7 +6877,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7202,10 +6904,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132341052</v>
+        <v>132341049</v>
       </c>
       <c r="B65" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7237,10 +6939,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>437740</v>
+        <v>437804</v>
       </c>
       <c r="R65" t="n">
-        <v>7011055</v>
+        <v>7010729</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7277,7 +6979,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7304,10 +7006,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132341032</v>
+        <v>132341051</v>
       </c>
       <c r="B66" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7339,10 +7041,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>438064</v>
+        <v>437746</v>
       </c>
       <c r="R66" t="n">
-        <v>7010908</v>
+        <v>7010946</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7379,7 +7081,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7406,10 +7108,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132341037</v>
+        <v>132341052</v>
       </c>
       <c r="B67" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7441,10 +7143,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437926</v>
+        <v>437740</v>
       </c>
       <c r="R67" t="n">
-        <v>7011061</v>
+        <v>7011055</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7508,10 +7210,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132341066</v>
+        <v>132341053</v>
       </c>
       <c r="B68" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7543,10 +7245,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436968</v>
+        <v>437740</v>
       </c>
       <c r="R68" t="n">
-        <v>7010599</v>
+        <v>7011063</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7583,7 +7285,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7610,10 +7312,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132341034</v>
+        <v>132341054</v>
       </c>
       <c r="B69" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7645,10 +7347,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437908</v>
+        <v>437637</v>
       </c>
       <c r="R69" t="n">
-        <v>7011073</v>
+        <v>7011098</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7712,10 +7414,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132340946</v>
+        <v>132341055</v>
       </c>
       <c r="B70" t="n">
-        <v>91916</v>
+        <v>57975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7723,21 +7425,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7747,10 +7449,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437124</v>
+        <v>437603</v>
       </c>
       <c r="R70" t="n">
-        <v>7010689</v>
+        <v>7011097</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7783,6 +7485,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7809,10 +7516,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132341102</v>
+        <v>132341056</v>
       </c>
       <c r="B71" t="n">
-        <v>92215</v>
+        <v>57975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7820,21 +7527,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7844,10 +7551,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437474</v>
+        <v>437578</v>
       </c>
       <c r="R71" t="n">
-        <v>7010882</v>
+        <v>7011118</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7880,6 +7587,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7906,10 +7618,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132340944</v>
+        <v>132341057</v>
       </c>
       <c r="B72" t="n">
-        <v>91916</v>
+        <v>57975</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7917,21 +7629,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7941,10 +7653,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437304</v>
+        <v>437606</v>
       </c>
       <c r="R72" t="n">
-        <v>7010986</v>
+        <v>7011053</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7977,6 +7689,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8003,10 +7720,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132341111</v>
+        <v>132341058</v>
       </c>
       <c r="B73" t="n">
-        <v>80437</v>
+        <v>57975</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8014,21 +7731,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8038,10 +7755,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437156</v>
+        <v>437635</v>
       </c>
       <c r="R73" t="n">
-        <v>7010645</v>
+        <v>7011011</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8068,12 +7785,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8100,10 +7822,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341096</v>
+        <v>132341059</v>
       </c>
       <c r="B74" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8111,16 +7833,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8135,10 +7857,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437096</v>
+        <v>437567</v>
       </c>
       <c r="R74" t="n">
-        <v>7010572</v>
+        <v>7010953</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8175,7 +7897,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8202,10 +7924,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341053</v>
+        <v>132341060</v>
       </c>
       <c r="B75" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8237,10 +7959,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437740</v>
+        <v>437611</v>
       </c>
       <c r="R75" t="n">
-        <v>7011063</v>
+        <v>7010882</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8277,7 +7999,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8304,10 +8026,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341106</v>
+        <v>132341061</v>
       </c>
       <c r="B76" t="n">
-        <v>92215</v>
+        <v>57975</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8315,21 +8037,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8339,10 +8061,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437009</v>
+        <v>437535</v>
       </c>
       <c r="R76" t="n">
-        <v>7010701</v>
+        <v>7010929</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8375,6 +8097,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8401,10 +8128,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341059</v>
+        <v>132341062</v>
       </c>
       <c r="B77" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8436,10 +8163,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437567</v>
+        <v>437538</v>
       </c>
       <c r="R77" t="n">
-        <v>7010953</v>
+        <v>7010940</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8503,10 +8230,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132340942</v>
+        <v>132341063</v>
       </c>
       <c r="B78" t="n">
-        <v>91916</v>
+        <v>57975</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8514,21 +8241,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8538,10 +8265,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437287</v>
+        <v>437505</v>
       </c>
       <c r="R78" t="n">
-        <v>7010896</v>
+        <v>7010836</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8574,6 +8301,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8600,10 +8332,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132341063</v>
+        <v>132341064</v>
       </c>
       <c r="B79" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8635,10 +8367,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437505</v>
+        <v>437442</v>
       </c>
       <c r="R79" t="n">
-        <v>7010836</v>
+        <v>7010869</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8702,10 +8434,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132341045</v>
+        <v>132341065</v>
       </c>
       <c r="B80" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8737,10 +8469,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437901</v>
+        <v>437074</v>
       </c>
       <c r="R80" t="n">
-        <v>7010813</v>
+        <v>7010580</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8777,7 +8509,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8804,10 +8536,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132341065</v>
+        <v>132341066</v>
       </c>
       <c r="B81" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8839,10 +8571,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437074</v>
+        <v>436968</v>
       </c>
       <c r="R81" t="n">
-        <v>7010580</v>
+        <v>7010599</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8879,7 +8611,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8906,10 +8638,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132341043</v>
+        <v>132796665</v>
       </c>
       <c r="B82" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8937,14 +8669,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437872</v>
+        <v>437176</v>
       </c>
       <c r="R82" t="n">
-        <v>7010932</v>
+        <v>7010505</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8971,17 +8703,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8996,39 +8733,39 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341030</v>
+        <v>132341119</v>
       </c>
       <c r="B83" t="n">
-        <v>57957</v>
+        <v>57153</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9036,17 +8773,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>438101</v>
+        <v>437582</v>
       </c>
       <c r="R83" t="n">
-        <v>7010924</v>
+        <v>7010573</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9073,17 +8822,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9110,45 +8854,61 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132341115</v>
+        <v>132340933</v>
       </c>
       <c r="B84" t="n">
-        <v>99125</v>
+        <v>56706</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>206046</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437101</v>
+        <v>437266</v>
       </c>
       <c r="R84" t="n">
-        <v>7010646</v>
+        <v>7010556</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9207,32 +8967,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132341114</v>
+        <v>132341115</v>
       </c>
       <c r="B85" t="n">
-        <v>80437</v>
+        <v>99195</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9242,10 +9002,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437012</v>
+        <v>437101</v>
       </c>
       <c r="R85" t="n">
-        <v>7010575</v>
+        <v>7010646</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9304,45 +9064,57 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132341046</v>
+        <v>132341116</v>
       </c>
       <c r="B86" t="n">
-        <v>57957</v>
+        <v>99195</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>437902</v>
+        <v>437089</v>
       </c>
       <c r="R86" t="n">
-        <v>7010811</v>
+        <v>7010576</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9379,7 +9151,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt, över 200</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9388,6 +9160,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9406,32 +9179,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132341061</v>
+        <v>132341117</v>
       </c>
       <c r="B87" t="n">
-        <v>57957</v>
+        <v>99195</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9441,10 +9214,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437535</v>
+        <v>437071</v>
       </c>
       <c r="R87" t="n">
-        <v>7010929</v>
+        <v>7010578</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9477,11 +9250,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9508,45 +9276,57 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132340948</v>
+        <v>132341118</v>
       </c>
       <c r="B88" t="n">
-        <v>91916</v>
+        <v>99195</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437159</v>
+        <v>437059</v>
       </c>
       <c r="R88" t="n">
-        <v>7010541</v>
+        <v>7010572</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9581,12 +9361,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Rikligt över 200</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9605,10 +9391,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132340943</v>
+        <v>89596049</v>
       </c>
       <c r="B89" t="n">
-        <v>91916</v>
+        <v>92208</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9616,34 +9402,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437280</v>
+        <v>438073</v>
       </c>
       <c r="R89" t="n">
-        <v>7010923</v>
+        <v>7010757</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9670,12 +9456,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9690,22 +9476,26 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132340938</v>
+        <v>132341127</v>
       </c>
       <c r="B90" t="n">
-        <v>91916</v>
+        <v>91970</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9713,21 +9503,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9737,10 +9527,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437465</v>
+        <v>437941</v>
       </c>
       <c r="R90" t="n">
-        <v>7010897</v>
+        <v>7010836</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9799,10 +9589,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132340947</v>
+        <v>89596069</v>
       </c>
       <c r="B91" t="n">
-        <v>91916</v>
+        <v>91909</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9830,14 +9620,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>437023</v>
+        <v>438074</v>
       </c>
       <c r="R91" t="n">
-        <v>7010700</v>
+        <v>7010758</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9864,12 +9654,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9884,57 +9674,61 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132340939</v>
+        <v>122773626</v>
       </c>
       <c r="B92" t="n">
-        <v>91916</v>
+        <v>79327</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>437481</v>
+        <v>438169</v>
       </c>
       <c r="R92" t="n">
-        <v>7010828</v>
+        <v>7010796</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9961,12 +9755,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9993,32 +9792,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132341101</v>
+        <v>132341094</v>
       </c>
       <c r="B93" t="n">
-        <v>92215</v>
+        <v>57972</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10028,10 +9827,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>437486</v>
+        <v>438128</v>
       </c>
       <c r="R93" t="n">
-        <v>7010537</v>
+        <v>7010852</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10058,12 +9857,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10090,32 +9894,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132341097</v>
+        <v>132341095</v>
       </c>
       <c r="B94" t="n">
-        <v>80438</v>
+        <v>57972</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10125,10 +9929,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>437011</v>
+        <v>437922</v>
       </c>
       <c r="R94" t="n">
-        <v>7010575</v>
+        <v>7011053</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10161,6 +9965,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10187,10 +9996,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132341028</v>
+        <v>122773595</v>
       </c>
       <c r="B95" t="n">
-        <v>57957</v>
+        <v>57953</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10218,14 +10027,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>437583</v>
+        <v>438193</v>
       </c>
       <c r="R95" t="n">
-        <v>7010708</v>
+        <v>7010800</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10252,12 +10061,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -10289,10 +10098,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132341107</v>
+        <v>132341030</v>
       </c>
       <c r="B96" t="n">
-        <v>92215</v>
+        <v>57975</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10300,21 +10109,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10324,10 +10133,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436990</v>
+        <v>438101</v>
       </c>
       <c r="R96" t="n">
-        <v>7010703</v>
+        <v>7010924</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10360,6 +10169,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10386,10 +10200,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132341104</v>
+        <v>132341031</v>
       </c>
       <c r="B97" t="n">
-        <v>92215</v>
+        <v>57975</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10397,21 +10211,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10421,10 +10235,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>437280</v>
+        <v>438101</v>
       </c>
       <c r="R97" t="n">
-        <v>7010923</v>
+        <v>7010919</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10457,6 +10271,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10483,57 +10302,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132341116</v>
+        <v>132341032</v>
       </c>
       <c r="B98" t="n">
-        <v>99125</v>
+        <v>57975</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>437089</v>
+        <v>438064</v>
       </c>
       <c r="R98" t="n">
-        <v>7010576</v>
+        <v>7010908</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10570,7 +10377,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Rikligt, över 200</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10579,7 +10386,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10595,6 +10401,515 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>132341033</v>
+      </c>
+      <c r="B99" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Sällsjön Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>438033</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7010948</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>132341037</v>
+      </c>
+      <c r="B100" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Sällsjön Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>437926</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7011061</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>132341040</v>
+      </c>
+      <c r="B101" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Sällsjön Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>438088</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7010817</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>132341041</v>
+      </c>
+      <c r="B102" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Sällsjön Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>437973</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7010845</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>89596054</v>
+      </c>
+      <c r="B103" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Baksjöhallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>438098</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7010725</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10604-2026 artfynd.xlsx
+++ b/artfynd/A 10604-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY103"/>
+  <dimension ref="A1:AZ103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596032</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596044</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596049</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596066</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341100</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341101</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341102</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1464,6 +1504,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341103</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1561,6 +1606,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341104</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1658,6 +1708,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341105</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1755,6 +1810,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341106</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1852,6 +1912,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341107</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1949,6 +2014,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341108</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2046,6 +2116,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341109</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2143,6 +2218,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341110</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2240,6 +2320,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341140</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2337,6 +2422,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341125</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2434,6 +2524,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341126</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2531,6 +2626,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341127</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2628,6 +2728,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341128</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2725,6 +2830,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341129</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2822,6 +2932,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341131</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2919,6 +3034,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341132</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3020,6 +3140,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596037</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3121,6 +3246,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596053</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3222,6 +3352,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596058</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3323,6 +3458,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596069</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3420,6 +3560,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340935</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3517,6 +3662,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340936</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3614,6 +3764,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340938</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3711,6 +3866,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340939</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3808,6 +3968,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340940</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3905,6 +4070,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340941</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4002,6 +4172,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340942</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4099,6 +4274,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340943</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4196,6 +4376,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340944</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4293,6 +4478,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340946</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4390,6 +4580,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340947</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4487,6 +4682,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340948</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4584,6 +4784,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340949</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4685,6 +4890,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596047</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4782,6 +4992,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341134</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4879,6 +5094,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341135</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4980,6 +5200,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596065</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5077,6 +5302,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341097</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5178,6 +5408,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596033</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5279,6 +5514,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596052</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5381,6 +5621,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773626</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5483,6 +5728,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341136</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5585,6 +5835,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341137</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5687,6 +5942,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341138</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5788,6 +6048,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596036</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5885,6 +6150,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341111</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5982,6 +6252,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341112</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6079,6 +6354,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341113</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6176,6 +6456,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341114</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6278,6 +6563,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341094</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6380,6 +6670,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341095</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6482,6 +6777,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341096</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6588,6 +6888,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596035</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6690,6 +6995,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773595</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6792,6 +7102,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341027</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6894,6 +7209,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341028</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6996,6 +7316,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341029</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7098,6 +7423,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341030</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7200,6 +7530,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341031</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7302,6 +7637,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341032</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7404,6 +7744,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341033</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7506,6 +7851,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341034</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7608,6 +7958,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341037</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7710,6 +8065,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341040</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7812,6 +8172,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341041</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7914,6 +8279,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341043</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8016,6 +8386,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341045</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8118,6 +8493,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341046</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8220,6 +8600,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341047</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8322,6 +8707,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341048</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8424,6 +8814,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341049</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8526,6 +8921,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341051</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8628,6 +9028,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341052</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8730,6 +9135,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341053</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8832,6 +9242,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341054</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8934,6 +9349,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341055</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9036,6 +9456,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341056</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9138,6 +9563,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341057</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9240,6 +9670,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341058</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9342,6 +9777,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341059</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9444,6 +9884,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341060</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9546,6 +9991,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341061</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9648,6 +10098,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341062</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9750,6 +10205,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341063</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9852,6 +10312,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341064</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9954,6 +10419,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341065</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10056,6 +10526,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341066</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10163,6 +10638,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132796665</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10264,6 +10744,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596054</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10373,6 +10858,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341119</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10486,6 +10976,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340933</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10583,6 +11078,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341115</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10698,6 +11198,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341116</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10795,6 +11300,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341117</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10910,8 +11420,117 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341118</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>